--- a/document/成果物ドキュメント_タスク詳細画面.xlsx
+++ b/document/成果物ドキュメント_タスク詳細画面.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-14\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAFBE11-F584-40E8-929C-F95E76617F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BBB2C1-3601-4F99-9C29-D87FF60AA547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,12 @@
     <sheet name="画面設計書" sheetId="5" r:id="rId5"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="93">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -374,10 +374,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>itemDeleteComfirm.jsp</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>コメントを投稿</t>
     <rPh sb="5" eb="7">
       <t>トウコウ</t>
@@ -390,6 +386,29 @@
   </si>
   <si>
     <t>TaskManager62システム</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>④</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>コメントを削除</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>comment-register-servlet</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>item-delete-confirm.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>comment-delete-confirm.jsp</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1436,146 +1455,197 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1592,89 +1662,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1764,22 +1783,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>745435</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>256761</xdr:rowOff>
+      <xdr:colOff>428090</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>72848</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>127344</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>41413</xdr:rowOff>
+      <xdr:colOff>717049</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>113015</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A12FE16-4227-15D8-9642-3126F36265C1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA8A1449-B79E-E4E9-4FF0-ED13ED764A2E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1802,8 +1821,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2882348" y="1548848"/>
-          <a:ext cx="2736366" cy="1888435"/>
+          <a:off x="2568539" y="1603269"/>
+          <a:ext cx="3628061" cy="2490982"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2032,85 +2051,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="45"/>
+      <c r="N4" s="45"/>
+      <c r="O4" s="45"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="52"/>
-      <c r="O6" s="52"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2130,46 +2149,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="69" t="s">
-        <v>88</v>
-      </c>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="52"/>
-      <c r="M8" s="52"/>
+      <c r="E8" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45"/>
+      <c r="M8" s="45"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="63" t="s">
+      <c r="G13" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="65"/>
-      <c r="I13" s="63" t="s">
+      <c r="H13" s="43"/>
+      <c r="I13" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="64"/>
-      <c r="K13" s="65"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="43"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="63"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="64"/>
-      <c r="K14" s="65"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="43"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="63"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="64"/>
-      <c r="K15" s="65"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="43"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2178,13 +2197,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="66" t="s">
+      <c r="G17" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="45"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3198,19 +3217,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="57" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="57" t="s">
+      <c r="E1" s="69"/>
+      <c r="F1" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="58"/>
+      <c r="G1" s="69"/>
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
@@ -3222,188 +3241,188 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="59" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="59" t="s">
+      <c r="E2" s="83"/>
+      <c r="F2" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="41">
+      <c r="G2" s="83"/>
+      <c r="H2" s="86">
         <v>46122</v>
       </c>
-      <c r="I2" s="44" t="s">
+      <c r="I2" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="45"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="46"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="54"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="47"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="85" t="s">
+      <c r="B5" s="53"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="86"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="54"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="71" t="s">
+      <c r="A6" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="72" t="s">
+      <c r="B6" s="42"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="73"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="56"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="72" t="s">
+      <c r="B7" s="42"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="73"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="56"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="64"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="72" t="s">
+      <c r="B8" s="42"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="55" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="73"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="56"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="80" t="s">
+      <c r="A9" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="70" t="s">
+      <c r="B9" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="65"/>
-      <c r="D9" s="87" t="s">
+      <c r="C9" s="43"/>
+      <c r="D9" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="73"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="56"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="81"/>
-      <c r="B10" s="70" t="s">
+      <c r="A10" s="72"/>
+      <c r="B10" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="73"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="56"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="82"/>
-      <c r="B11" s="70" t="s">
+      <c r="A11" s="73"/>
+      <c r="B11" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="73"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="56"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="71" t="s">
+      <c r="A12" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="64"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="72" t="s">
+      <c r="B12" s="42"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="73"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="56"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="74" t="s">
+      <c r="A13" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="75"/>
-      <c r="C13" s="76"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="84"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="51"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4394,6 +4413,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -4402,25 +4440,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4439,19 +4458,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="57" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="57" t="s">
+      <c r="E1" s="69"/>
+      <c r="F1" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="58"/>
+      <c r="G1" s="69"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -4463,48 +4482,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="59" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="59" t="s">
+      <c r="E2" s="83"/>
+      <c r="F2" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="41">
+      <c r="G2" s="83"/>
+      <c r="H2" s="86">
         <v>46120</v>
       </c>
-      <c r="I2" s="44" t="s">
+      <c r="I2" s="75" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="45"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="46"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="54"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="47"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5859,19 +5878,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="57" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="57" t="s">
+      <c r="E1" s="69"/>
+      <c r="F1" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="58"/>
+      <c r="G1" s="69"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -5883,48 +5902,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="59" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="59" t="s">
+      <c r="E2" s="83"/>
+      <c r="F2" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="41">
+      <c r="G2" s="83"/>
+      <c r="H2" s="86">
         <v>46122</v>
       </c>
-      <c r="I2" s="44" t="s">
+      <c r="I2" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="45"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="46"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="54"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="47"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7265,7 +7284,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1001"/>
+  <dimension ref="A1:J997"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -7274,19 +7293,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="57" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="57" t="s">
+      <c r="E1" s="69"/>
+      <c r="F1" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="58"/>
+      <c r="G1" s="69"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -7298,190 +7317,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="59" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="59" t="s">
+      <c r="E2" s="83"/>
+      <c r="F2" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="41">
+      <c r="G2" s="83"/>
+      <c r="H2" s="86">
         <v>46122</v>
       </c>
-      <c r="I2" s="44" t="s">
+      <c r="I2" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="45"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="46"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="46"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="79"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="105" t="s">
+      <c r="A5" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="106" t="s">
+      <c r="B5" s="53"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="86"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="54"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="73"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="56"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="107"/>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="108"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="109"/>
+      <c r="A7" s="98"/>
+      <c r="B7" s="99"/>
+      <c r="C7" s="99"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="100"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="51"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="110"/>
+      <c r="A8" s="63"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="101"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="51"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="110"/>
+      <c r="A9" s="63"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="101"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="51"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="110"/>
+      <c r="A10" s="63"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="45"/>
+      <c r="I10" s="45"/>
+      <c r="J10" s="101"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="51"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="110"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="51"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="110"/>
+      <c r="A11" s="63"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="101"/>
+    </row>
+    <row r="12" spans="1:10" ht="87.75" customHeight="1">
+      <c r="A12" s="63"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="101"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="51"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="110"/>
+      <c r="A13" s="63"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="101"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="98" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="73"/>
+      <c r="A14" s="97" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="56"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="98" t="s">
+      <c r="A15" s="97" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="72" t="s">
+      <c r="B15" s="42"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="55" t="s">
         <v>78</v>
       </c>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="65"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="43"/>
       <c r="I15" s="15" t="s">
         <v>27</v>
       </c>
@@ -7490,11 +7509,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="98" t="s">
+      <c r="A16" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="65"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="43"/>
       <c r="D16" s="15" t="s">
         <v>29</v>
       </c>
@@ -7507,18 +7526,18 @@
       <c r="G16" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="99" t="s">
+      <c r="H16" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="64"/>
-      <c r="J16" s="73"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="56"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="100" t="s">
+      <c r="A17" s="91" t="s">
         <v>79</v>
       </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="65"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="43"/>
       <c r="D17" s="17" t="s">
         <v>80</v>
       </c>
@@ -7529,276 +7548,317 @@
       <c r="G17" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="H17" s="72"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="73"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="100"/>
-      <c r="B18" s="64"/>
-      <c r="C18" s="65"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="73"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="56"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A18" s="92"/>
+      <c r="B18" s="93"/>
+      <c r="C18" s="94"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="93"/>
+      <c r="J18" s="96"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="100"/>
-      <c r="B19" s="64"/>
-      <c r="C19" s="65"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="73"/>
+      <c r="A19" s="103"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="90"/>
+      <c r="J19" s="90"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="100"/>
-      <c r="B20" s="64"/>
-      <c r="C20" s="65"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="72"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="73"/>
+      <c r="A20" s="105" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="106"/>
+      <c r="C20" s="106"/>
+      <c r="D20" s="106"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="106"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="106"/>
+      <c r="J20" s="106"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="100"/>
-      <c r="B21" s="64"/>
-      <c r="C21" s="65"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="72"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="73"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A22" s="96"/>
-      <c r="B22" s="94"/>
-      <c r="C22" s="97"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="93"/>
-      <c r="I22" s="94"/>
-      <c r="J22" s="95"/>
+      <c r="A21" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="108"/>
+      <c r="C21" s="109"/>
+      <c r="D21" s="107" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="108"/>
+      <c r="F21" s="108"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="38" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="97" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="88" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="42"/>
+      <c r="J22" s="56"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="101"/>
-      <c r="B23" s="102"/>
-      <c r="C23" s="102"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="103"/>
-      <c r="I23" s="102"/>
-      <c r="J23" s="102"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="88" t="s">
+      <c r="A23" s="91" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="42"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H23" s="55"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="56"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A24" s="92"/>
+      <c r="B24" s="93"/>
+      <c r="C24" s="94"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="95"/>
+      <c r="I24" s="93"/>
+      <c r="J24" s="96"/>
+    </row>
+    <row r="25" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A25" s="103"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="90"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="90"/>
+    </row>
+    <row r="26" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A26" s="105" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="89"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="89"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="89"/>
-    </row>
-    <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="104" t="s">
+      <c r="B26" s="106"/>
+      <c r="C26" s="106"/>
+      <c r="D26" s="106"/>
+      <c r="E26" s="106"/>
+      <c r="F26" s="106"/>
+      <c r="G26" s="106"/>
+      <c r="H26" s="106"/>
+      <c r="I26" s="106"/>
+      <c r="J26" s="106"/>
+    </row>
+    <row r="27" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A27" s="110" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="91"/>
-      <c r="C25" s="92"/>
-      <c r="D25" s="90" t="s">
+      <c r="B27" s="108"/>
+      <c r="C27" s="109"/>
+      <c r="D27" s="107" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" s="108"/>
+      <c r="F27" s="108"/>
+      <c r="G27" s="108"/>
+      <c r="H27" s="109"/>
+      <c r="I27" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="J27" s="38" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A28" s="97" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="42"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H28" s="88" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" s="42"/>
+      <c r="J28" s="56"/>
+    </row>
+    <row r="29" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A29" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="42"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E25" s="91"/>
-      <c r="F25" s="91"/>
-      <c r="G25" s="91"/>
-      <c r="H25" s="92"/>
-      <c r="I25" s="37" t="s">
+      <c r="E29" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="H29" s="55"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="56"/>
+    </row>
+    <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A30" s="92"/>
+      <c r="B30" s="93"/>
+      <c r="C30" s="94"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="95"/>
+      <c r="I30" s="93"/>
+      <c r="J30" s="96"/>
+    </row>
+    <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="32" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A32" s="105" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="106"/>
+      <c r="C32" s="106"/>
+      <c r="D32" s="106"/>
+      <c r="E32" s="106"/>
+      <c r="F32" s="106"/>
+      <c r="G32" s="106"/>
+      <c r="H32" s="106"/>
+      <c r="I32" s="106"/>
+      <c r="J32" s="106"/>
+    </row>
+    <row r="33" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A33" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" s="108"/>
+      <c r="C33" s="109"/>
+      <c r="D33" s="107" t="s">
+        <v>92</v>
+      </c>
+      <c r="E33" s="108"/>
+      <c r="F33" s="108"/>
+      <c r="G33" s="108"/>
+      <c r="H33" s="109"/>
+      <c r="I33" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="J25" s="38" t="s">
+      <c r="J33" s="38" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="98" t="s">
+    <row r="34" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A34" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="64"/>
-      <c r="C26" s="65"/>
-      <c r="D26" s="15" t="s">
+      <c r="B34" s="42"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E34" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="15" t="s">
+      <c r="F34" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G26" s="15" t="s">
+      <c r="G34" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H26" s="99" t="s">
+      <c r="H34" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="I26" s="64"/>
-      <c r="J26" s="73"/>
-    </row>
-    <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="100" t="s">
-        <v>82</v>
-      </c>
-      <c r="B27" s="64"/>
-      <c r="C27" s="65"/>
-      <c r="D27" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="E27" s="17" t="s">
+      <c r="I34" s="42"/>
+      <c r="J34" s="56"/>
+    </row>
+    <row r="35" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A35" s="91" t="s">
+        <v>88</v>
+      </c>
+      <c r="B35" s="42"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E35" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="H27" s="72"/>
-      <c r="I27" s="64"/>
-      <c r="J27" s="73"/>
-    </row>
-    <row r="28" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A28" s="96"/>
-      <c r="B28" s="94"/>
-      <c r="C28" s="97"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="93"/>
-      <c r="I28" s="94"/>
-      <c r="J28" s="95"/>
-    </row>
-    <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="101"/>
-      <c r="B29" s="102"/>
-      <c r="C29" s="102"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="103"/>
-      <c r="I29" s="102"/>
-      <c r="J29" s="102"/>
-    </row>
-    <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="88" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="89"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="89"/>
-    </row>
-    <row r="31" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A31" s="104" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="91"/>
-      <c r="C31" s="92"/>
-      <c r="D31" s="90" t="s">
-        <v>85</v>
-      </c>
-      <c r="E31" s="91"/>
-      <c r="F31" s="91"/>
-      <c r="G31" s="91"/>
-      <c r="H31" s="92"/>
-      <c r="I31" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="J31" s="38" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="98" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="64"/>
-      <c r="C32" s="65"/>
-      <c r="D32" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G32" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="H32" s="99" t="s">
-        <v>19</v>
-      </c>
-      <c r="I32" s="64"/>
-      <c r="J32" s="73"/>
-    </row>
-    <row r="33" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A33" s="100" t="s">
-        <v>84</v>
-      </c>
-      <c r="B33" s="64"/>
-      <c r="C33" s="65"/>
-      <c r="D33" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="H33" s="72"/>
-      <c r="I33" s="64"/>
-      <c r="J33" s="73"/>
-    </row>
-    <row r="34" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A34" s="96"/>
-      <c r="B34" s="94"/>
-      <c r="C34" s="97"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="93"/>
-      <c r="I34" s="94"/>
-      <c r="J34" s="95"/>
-    </row>
-    <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="36" spans="1:10" ht="12.75" customHeight="1"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="H35" s="55"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="56"/>
+    </row>
+    <row r="36" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A36" s="92"/>
+      <c r="B36" s="93"/>
+      <c r="C36" s="94"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="95"/>
+      <c r="I36" s="93"/>
+      <c r="J36" s="96"/>
+    </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="38" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="39" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8760,35 +8820,32 @@
     <row r="995" ht="12.75" customHeight="1"/>
     <row r="996" ht="12.75" customHeight="1"/>
     <row r="997" ht="12.75" customHeight="1"/>
-    <row r="998" ht="12.75" customHeight="1"/>
-    <row r="999" ht="12.75" customHeight="1"/>
-    <row r="1000" ht="12.75" customHeight="1"/>
-    <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="51">
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="D2:E4"/>
+  <mergeCells count="52">
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
@@ -8797,26 +8854,26 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8836,182 +8893,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="57" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="57" t="s">
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="57" t="s">
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="81" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="57" t="s">
+      <c r="P1" s="69"/>
+      <c r="Q1" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="58"/>
-      <c r="S1" s="57" t="s">
+      <c r="R1" s="69"/>
+      <c r="S1" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="86"/>
+      <c r="T1" s="54"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="108"/>
-      <c r="M2" s="108"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="109"/>
+      <c r="A2" s="63"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="83"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="83"/>
+      <c r="Q2" s="82"/>
+      <c r="R2" s="83"/>
+      <c r="S2" s="82"/>
+      <c r="T2" s="100"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="61"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="61"/>
-      <c r="P3" s="53"/>
-      <c r="Q3" s="61"/>
-      <c r="R3" s="53"/>
-      <c r="S3" s="61"/>
-      <c r="T3" s="110"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="84"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="84"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="84"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="84"/>
+      <c r="T3" s="101"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="54"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="62"/>
-      <c r="R4" s="56"/>
-      <c r="S4" s="62"/>
-      <c r="T4" s="115"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="66"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="85"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="85"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="85"/>
+      <c r="T4" s="119"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="105" t="s">
+      <c r="A5" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="85" t="s">
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="79"/>
-      <c r="K5" s="79"/>
-      <c r="L5" s="79"/>
-      <c r="M5" s="79"/>
-      <c r="N5" s="79"/>
-      <c r="O5" s="79"/>
-      <c r="P5" s="79"/>
-      <c r="Q5" s="79"/>
-      <c r="R5" s="79"/>
-      <c r="S5" s="79"/>
-      <c r="T5" s="86"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="53"/>
+      <c r="N5" s="53"/>
+      <c r="O5" s="53"/>
+      <c r="P5" s="53"/>
+      <c r="Q5" s="53"/>
+      <c r="R5" s="53"/>
+      <c r="S5" s="53"/>
+      <c r="T5" s="54"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="97" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="72" t="s">
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="64"/>
-      <c r="P6" s="64"/>
-      <c r="Q6" s="64"/>
-      <c r="R6" s="64"/>
-      <c r="S6" s="64"/>
-      <c r="T6" s="73"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
+      <c r="P6" s="42"/>
+      <c r="Q6" s="42"/>
+      <c r="R6" s="42"/>
+      <c r="S6" s="42"/>
+      <c r="T6" s="56"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="98" t="s">
+      <c r="A7" s="97" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="72" t="s">
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="64"/>
-      <c r="Q7" s="64"/>
-      <c r="R7" s="64"/>
-      <c r="S7" s="64"/>
-      <c r="T7" s="73"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="42"/>
+      <c r="S7" s="42"/>
+      <c r="T7" s="56"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9210,37 +9267,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="98" t="s">
+      <c r="A15" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="65"/>
+      <c r="B15" s="43"/>
       <c r="C15" s="118" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="65"/>
-      <c r="E15" s="99" t="s">
+      <c r="D15" s="43"/>
+      <c r="E15" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="99" t="s">
+      <c r="F15" s="43"/>
+      <c r="G15" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="64"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="99" t="s">
+      <c r="H15" s="42"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="65"/>
-      <c r="L15" s="99" t="s">
+      <c r="K15" s="43"/>
+      <c r="L15" s="88" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="64"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="99" t="s">
+      <c r="M15" s="42"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="64"/>
-      <c r="Q15" s="65"/>
+      <c r="P15" s="42"/>
+      <c r="Q15" s="43"/>
       <c r="R15" s="15" t="s">
         <v>51</v>
       </c>
@@ -9252,37 +9309,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="116">
+      <c r="A16" s="111">
         <v>1</v>
       </c>
-      <c r="B16" s="65"/>
-      <c r="C16" s="117" t="s">
+      <c r="B16" s="43"/>
+      <c r="C16" s="112" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="117" t="s">
+      <c r="D16" s="43"/>
+      <c r="E16" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="65"/>
-      <c r="G16" s="111" t="s">
+      <c r="F16" s="43"/>
+      <c r="G16" s="117" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="64"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="111" t="s">
+      <c r="H16" s="42"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="117" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="65"/>
-      <c r="L16" s="113" t="s">
+      <c r="K16" s="43"/>
+      <c r="L16" s="115" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="64"/>
-      <c r="N16" s="65"/>
-      <c r="O16" s="113" t="s">
+      <c r="M16" s="42"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="115" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="64"/>
-      <c r="Q16" s="65"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="43"/>
       <c r="R16" s="31"/>
       <c r="S16" s="31"/>
       <c r="T16" s="32"/>
@@ -9294,37 +9351,37 @@
       <c r="Z16" s="33"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="116">
+      <c r="A17" s="111">
         <v>2</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="117" t="s">
+      <c r="B17" s="43"/>
+      <c r="C17" s="112" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="65"/>
-      <c r="E17" s="117" t="s">
+      <c r="D17" s="43"/>
+      <c r="E17" s="112" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="65"/>
-      <c r="G17" s="111" t="s">
+      <c r="F17" s="43"/>
+      <c r="G17" s="117" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="64"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="111" t="s">
+      <c r="H17" s="42"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="117" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="65"/>
-      <c r="L17" s="113" t="s">
+      <c r="K17" s="43"/>
+      <c r="L17" s="115" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="64"/>
-      <c r="N17" s="65"/>
-      <c r="O17" s="113" t="s">
+      <c r="M17" s="42"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="P17" s="64"/>
-      <c r="Q17" s="65"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="43"/>
       <c r="R17" s="31"/>
       <c r="S17" s="31"/>
       <c r="T17" s="32"/>
@@ -9336,23 +9393,23 @@
       <c r="Z17" s="33"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="116"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="117"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="111"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="111"/>
-      <c r="K18" s="65"/>
-      <c r="L18" s="113"/>
-      <c r="M18" s="64"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="113"/>
-      <c r="P18" s="64"/>
-      <c r="Q18" s="65"/>
+      <c r="A18" s="111"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="112"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="115"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="43"/>
+      <c r="O18" s="115"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="43"/>
       <c r="R18" s="31"/>
       <c r="S18" s="31"/>
       <c r="T18" s="32"/>
@@ -9364,23 +9421,23 @@
       <c r="Z18" s="33"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="116"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="117"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="111"/>
-      <c r="K19" s="65"/>
-      <c r="L19" s="113"/>
-      <c r="M19" s="64"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="113"/>
-      <c r="P19" s="64"/>
-      <c r="Q19" s="65"/>
+      <c r="A19" s="111"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="112"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="117"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="117"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="115"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="43"/>
+      <c r="O19" s="115"/>
+      <c r="P19" s="42"/>
+      <c r="Q19" s="43"/>
       <c r="R19" s="31"/>
       <c r="S19" s="31"/>
       <c r="T19" s="32"/>
@@ -9392,23 +9449,23 @@
       <c r="Z19" s="33"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="116"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="117"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="117"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="111"/>
-      <c r="K20" s="65"/>
-      <c r="L20" s="113"/>
-      <c r="M20" s="64"/>
-      <c r="N20" s="65"/>
-      <c r="O20" s="113"/>
-      <c r="P20" s="64"/>
-      <c r="Q20" s="65"/>
+      <c r="A20" s="111"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="112"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="112"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="117"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="115"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="115"/>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="43"/>
       <c r="R20" s="31"/>
       <c r="S20" s="31"/>
       <c r="T20" s="32"/>
@@ -9420,23 +9477,23 @@
       <c r="Z20" s="33"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="116"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="117"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="117"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="111"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="113"/>
-      <c r="M21" s="64"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="113"/>
-      <c r="P21" s="64"/>
-      <c r="Q21" s="65"/>
+      <c r="A21" s="111"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="112"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="117"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="117"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="115"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="115"/>
+      <c r="P21" s="42"/>
+      <c r="Q21" s="43"/>
       <c r="R21" s="31"/>
       <c r="S21" s="31"/>
       <c r="T21" s="32"/>
@@ -9448,23 +9505,23 @@
       <c r="Z21" s="33"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="116"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="117"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="111"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="111"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="113"/>
-      <c r="M22" s="64"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="113"/>
-      <c r="P22" s="64"/>
-      <c r="Q22" s="65"/>
+      <c r="A22" s="111"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="112"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="115"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="43"/>
+      <c r="O22" s="115"/>
+      <c r="P22" s="42"/>
+      <c r="Q22" s="43"/>
       <c r="R22" s="31"/>
       <c r="S22" s="31"/>
       <c r="T22" s="32"/>
@@ -9476,23 +9533,23 @@
       <c r="Z22" s="33"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="116"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="117"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="117"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="111"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="111"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="113"/>
-      <c r="M23" s="64"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="113"/>
-      <c r="P23" s="64"/>
-      <c r="Q23" s="65"/>
+      <c r="A23" s="111"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="112"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="112"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="117"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="115"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="115"/>
+      <c r="P23" s="42"/>
+      <c r="Q23" s="43"/>
       <c r="R23" s="31"/>
       <c r="S23" s="31"/>
       <c r="T23" s="32"/>
@@ -9504,23 +9561,23 @@
       <c r="Z23" s="33"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="116"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="117"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="111"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="111"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="113"/>
-      <c r="M24" s="64"/>
-      <c r="N24" s="65"/>
-      <c r="O24" s="113"/>
-      <c r="P24" s="64"/>
-      <c r="Q24" s="65"/>
+      <c r="A24" s="111"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="112"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="112"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="117"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="117"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="115"/>
+      <c r="M24" s="42"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="115"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="43"/>
       <c r="R24" s="31"/>
       <c r="S24" s="31"/>
       <c r="T24" s="32"/>
@@ -9532,23 +9589,23 @@
       <c r="Z24" s="33"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="116"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="117"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="117"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="111"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="111"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="113"/>
-      <c r="M25" s="64"/>
-      <c r="N25" s="65"/>
-      <c r="O25" s="113"/>
-      <c r="P25" s="64"/>
-      <c r="Q25" s="65"/>
+      <c r="A25" s="111"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="112"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="117"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="117"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="115"/>
+      <c r="M25" s="42"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="115"/>
+      <c r="P25" s="42"/>
+      <c r="Q25" s="43"/>
       <c r="R25" s="31"/>
       <c r="S25" s="31"/>
       <c r="T25" s="32"/>
@@ -9560,23 +9617,23 @@
       <c r="Z25" s="33"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="116"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="117"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="117"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="111"/>
-      <c r="H26" s="64"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="111"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="113"/>
-      <c r="M26" s="64"/>
-      <c r="N26" s="65"/>
-      <c r="O26" s="113"/>
-      <c r="P26" s="64"/>
-      <c r="Q26" s="65"/>
+      <c r="A26" s="111"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="112"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="112"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="117"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="115"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="115"/>
+      <c r="P26" s="42"/>
+      <c r="Q26" s="43"/>
       <c r="R26" s="31"/>
       <c r="S26" s="31"/>
       <c r="T26" s="32"/>
@@ -9588,23 +9645,23 @@
       <c r="Z26" s="33"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="116"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="117"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="117"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="111"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="111"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="113"/>
-      <c r="M27" s="64"/>
-      <c r="N27" s="65"/>
-      <c r="O27" s="113"/>
-      <c r="P27" s="64"/>
-      <c r="Q27" s="65"/>
+      <c r="A27" s="111"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="112"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="117"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="117"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="115"/>
+      <c r="M27" s="42"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="115"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="43"/>
       <c r="R27" s="31"/>
       <c r="S27" s="31"/>
       <c r="T27" s="32"/>
@@ -9616,23 +9673,23 @@
       <c r="Z27" s="33"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="116"/>
-      <c r="B28" s="65"/>
-      <c r="C28" s="117"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="117"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="111"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="111"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="113"/>
-      <c r="M28" s="64"/>
-      <c r="N28" s="65"/>
-      <c r="O28" s="113"/>
-      <c r="P28" s="64"/>
-      <c r="Q28" s="65"/>
+      <c r="A28" s="111"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="112"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="117"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="117"/>
+      <c r="K28" s="43"/>
+      <c r="L28" s="115"/>
+      <c r="M28" s="42"/>
+      <c r="N28" s="43"/>
+      <c r="O28" s="115"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="43"/>
       <c r="R28" s="31"/>
       <c r="S28" s="31"/>
       <c r="T28" s="32"/>
@@ -9644,23 +9701,23 @@
       <c r="Z28" s="33"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="116"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="117"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="117"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="111"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="111"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="113"/>
-      <c r="M29" s="64"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="113"/>
-      <c r="P29" s="64"/>
-      <c r="Q29" s="65"/>
+      <c r="A29" s="111"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="112"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="117"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="117"/>
+      <c r="K29" s="43"/>
+      <c r="L29" s="115"/>
+      <c r="M29" s="42"/>
+      <c r="N29" s="43"/>
+      <c r="O29" s="115"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="43"/>
       <c r="R29" s="31"/>
       <c r="S29" s="31"/>
       <c r="T29" s="32"/>
@@ -9672,23 +9729,23 @@
       <c r="Z29" s="33"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="116"/>
-      <c r="B30" s="65"/>
-      <c r="C30" s="117"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="117"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="111"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="111"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="113"/>
-      <c r="M30" s="64"/>
-      <c r="N30" s="65"/>
-      <c r="O30" s="113"/>
-      <c r="P30" s="64"/>
-      <c r="Q30" s="65"/>
+      <c r="A30" s="111"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="112"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="112"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="117"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="117"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="115"/>
+      <c r="M30" s="42"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="115"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="43"/>
       <c r="R30" s="31"/>
       <c r="S30" s="31"/>
       <c r="T30" s="32"/>
@@ -9700,23 +9757,23 @@
       <c r="Z30" s="33"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="119"/>
-      <c r="B31" s="76"/>
-      <c r="C31" s="120"/>
-      <c r="D31" s="76"/>
-      <c r="E31" s="120"/>
-      <c r="F31" s="76"/>
-      <c r="G31" s="112"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="76"/>
-      <c r="J31" s="112"/>
-      <c r="K31" s="76"/>
-      <c r="L31" s="114"/>
-      <c r="M31" s="75"/>
-      <c r="N31" s="76"/>
-      <c r="O31" s="114"/>
-      <c r="P31" s="75"/>
-      <c r="Q31" s="76"/>
+      <c r="A31" s="113"/>
+      <c r="B31" s="59"/>
+      <c r="C31" s="114"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="114"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="120"/>
+      <c r="H31" s="50"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="120"/>
+      <c r="K31" s="59"/>
+      <c r="L31" s="116"/>
+      <c r="M31" s="50"/>
+      <c r="N31" s="59"/>
+      <c r="O31" s="116"/>
+      <c r="P31" s="50"/>
+      <c r="Q31" s="59"/>
       <c r="R31" s="34"/>
       <c r="S31" s="34"/>
       <c r="T31" s="35"/>
@@ -10714,6 +10771,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -10738,118 +10907,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_タスク詳細画面.xlsx
+++ b/document/成果物ドキュメント_タスク詳細画面.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-14\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-14\Documents\project\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{104874C0-C74F-43DB-BC9E-75ABDFAE68F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B39778-3D0D-4E47-B625-2F12D82124FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10245" yWindow="0" windowWidth="10245" windowHeight="10920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -275,53 +275,9 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク詳細を表示し編集、削除、コメント投稿、コメント削除画面へのボタンを表示</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>タスクが登録済みであること</t>
     <rPh sb="4" eb="7">
       <t>トウロクズ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1.ユーザーがタスク一覧画面からタスクの詳細ボタンを押下する
-2.システムが押下されたタスクの詳細画面を表示する
-3.システムがタスクの名前、カテゴリ、期限、担当者情報、ステータス情報、メモ、コメントを表示する。
-</t>
-    <rPh sb="10" eb="14">
-      <t>イチランガメン</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="47" eb="51">
-      <t>ショウサイガメン</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="68" eb="70">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="79" eb="84">
-      <t>タントウシャジョウホウ</t>
-    </rPh>
-    <rPh sb="90" eb="92">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="101" eb="103">
-      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -394,6 +350,50 @@
   </si>
   <si>
     <t>なし</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.ユーザーがタスク一覧画面からタスクの詳細ボタンを選択する
+2.システムが押下されたタスクの詳細画面を表示する
+3.システムがタスクの名前、カテゴリ、期限、担当者情報、ステータス情報、メモ、コメントを表示する。
+</t>
+    <rPh sb="10" eb="14">
+      <t>イチランガメン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="47" eb="51">
+      <t>ショウサイガメン</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="79" eb="84">
+      <t>タントウシャジョウホウ</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="101" eb="103">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>システムがタスク詳細を表示し編集、削除、コメント投稿、コメント削除画面へのボタンを表示すること</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1440,6 +1440,207 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1449,236 +1650,35 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2102,85 +2102,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="88" t="s">
+      <c r="C2" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="75"/>
-      <c r="L3" s="75"/>
-      <c r="M3" s="75"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
-      <c r="K4" s="75"/>
-      <c r="L4" s="75"/>
-      <c r="M4" s="75"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="75"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="75"/>
-      <c r="K5" s="75"/>
-      <c r="L5" s="75"/>
-      <c r="M5" s="75"/>
-      <c r="N5" s="75"/>
-      <c r="O5" s="75"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="75"/>
-      <c r="K6" s="75"/>
-      <c r="L6" s="75"/>
-      <c r="M6" s="75"/>
-      <c r="N6" s="75"/>
-      <c r="O6" s="75"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="57"/>
+      <c r="M6" s="57"/>
+      <c r="N6" s="57"/>
+      <c r="O6" s="57"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2200,46 +2200,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="90" t="s">
-        <v>88</v>
-      </c>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
-      <c r="J8" s="75"/>
-      <c r="K8" s="75"/>
-      <c r="L8" s="75"/>
-      <c r="M8" s="75"/>
+      <c r="E8" s="86" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="86" t="s">
+      <c r="G13" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="53"/>
-      <c r="I13" s="86" t="s">
+      <c r="H13" s="65"/>
+      <c r="I13" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="52"/>
-      <c r="K13" s="53"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="65"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="86"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="86"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="53"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="65"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="86"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="86"/>
-      <c r="J15" s="52"/>
-      <c r="K15" s="53"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="82"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="65"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2248,13 +2248,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="87" t="s">
+      <c r="G17" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="75"/>
-      <c r="I17" s="75"/>
-      <c r="J17" s="75"/>
-      <c r="K17" s="75"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3268,19 +3268,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="78"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="78"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
@@ -3292,192 +3292,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
-      <c r="B2" s="75"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="62" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="63"/>
-      <c r="F2" s="62" t="s">
+      <c r="E2" s="78"/>
+      <c r="F2" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="63"/>
-      <c r="H2" s="66">
+      <c r="G2" s="78"/>
+      <c r="H2" s="81">
         <v>46122</v>
       </c>
-      <c r="I2" s="68" t="s">
+      <c r="I2" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="69"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="70"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="92"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="92"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="94"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="103" t="s">
+      <c r="A5" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="77"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="109" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="81"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="46"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="96" t="s">
+      <c r="A6" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="57" t="s">
+      <c r="B6" s="48"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="55"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="49"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="96" t="s">
+      <c r="A7" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="57" t="s">
+      <c r="B7" s="48"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="55"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="49"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="96" t="s">
+      <c r="A8" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="57" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="55"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="49"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="104" t="s">
+      <c r="A9" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="95" t="s">
+      <c r="B9" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="53"/>
-      <c r="D9" s="110" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="55"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="50" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="49"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="105"/>
-      <c r="B10" s="95" t="s">
+      <c r="A10" s="67"/>
+      <c r="B10" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="53"/>
-      <c r="D10" s="57" t="s">
+      <c r="C10" s="65"/>
+      <c r="D10" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="49"/>
+    </row>
+    <row r="11" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A11" s="68"/>
+      <c r="B11" s="69" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="65"/>
+      <c r="D11" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="49"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="64" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="48"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="55"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="106"/>
-      <c r="B11" s="95" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="53"/>
-      <c r="D11" s="57" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="55"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="96" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="52"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="57" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="55"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="49"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="97" t="s">
+      <c r="A13" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="98"/>
-      <c r="C13" s="99"/>
-      <c r="D13" s="107"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="98"/>
-      <c r="H13" s="98"/>
-      <c r="I13" s="98"/>
-      <c r="J13" s="108"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="43"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4468,6 +4468,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -4476,25 +4495,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4513,19 +4513,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="78"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="78"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -4537,48 +4537,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
-      <c r="B2" s="75"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="62" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="63"/>
-      <c r="F2" s="62" t="s">
+      <c r="E2" s="78"/>
+      <c r="F2" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="63"/>
-      <c r="H2" s="66">
+      <c r="G2" s="78"/>
+      <c r="H2" s="81">
         <v>46120</v>
       </c>
-      <c r="I2" s="68" t="s">
+      <c r="I2" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="69"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="70"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="92"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="92"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="94"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5933,19 +5933,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="78"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="78"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -5957,48 +5957,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
-      <c r="B2" s="75"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="62" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="63"/>
-      <c r="F2" s="62" t="s">
+      <c r="E2" s="78"/>
+      <c r="F2" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="63"/>
-      <c r="H2" s="66">
+      <c r="G2" s="78"/>
+      <c r="H2" s="81">
         <v>46122</v>
       </c>
-      <c r="I2" s="68" t="s">
+      <c r="I2" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="69"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="70"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="92"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="92"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="94"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7348,19 +7348,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="78"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="78"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -7372,203 +7372,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
-      <c r="B2" s="75"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="62" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="63"/>
-      <c r="F2" s="62" t="s">
+      <c r="E2" s="78"/>
+      <c r="F2" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="63"/>
-      <c r="H2" s="66">
+      <c r="G2" s="78"/>
+      <c r="H2" s="81">
         <v>46122</v>
       </c>
-      <c r="I2" s="68" t="s">
+      <c r="I2" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="69"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="70"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="74"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="70"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="74"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="77"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="80" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="81"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="107" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="46"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="96" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="55"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="49"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="82"/>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="84"/>
+      <c r="A7" s="97"/>
+      <c r="B7" s="98"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="98"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="98"/>
+      <c r="H7" s="98"/>
+      <c r="I7" s="98"/>
+      <c r="J7" s="99"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="74"/>
-      <c r="B8" s="75"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
-      <c r="J8" s="85"/>
+      <c r="A8" s="56"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="100"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="74"/>
-      <c r="B9" s="75"/>
-      <c r="C9" s="75"/>
-      <c r="D9" s="75"/>
-      <c r="E9" s="75"/>
-      <c r="F9" s="75"/>
-      <c r="G9" s="75"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="75"/>
-      <c r="J9" s="85"/>
+      <c r="A9" s="56"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="100"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="74"/>
-      <c r="B10" s="75"/>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
-      <c r="E10" s="75"/>
-      <c r="F10" s="75"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="75"/>
-      <c r="J10" s="85"/>
+      <c r="A10" s="56"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="100"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="74"/>
-      <c r="B11" s="75"/>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
-      <c r="J11" s="85"/>
+      <c r="A11" s="56"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="100"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="74"/>
-      <c r="B12" s="75"/>
-      <c r="C12" s="75"/>
-      <c r="D12" s="75"/>
-      <c r="E12" s="75"/>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="75"/>
-      <c r="J12" s="85"/>
+      <c r="A12" s="56"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="100"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="74"/>
-      <c r="B13" s="75"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="85"/>
+      <c r="A13" s="56"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="100"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="52"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="55"/>
+      <c r="A14" s="96" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="49"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="52"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="57" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" s="52"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="53"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="15" t="s">
         <v>27</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="51" t="s">
+      <c r="A16" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="52"/>
-      <c r="C16" s="53"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="15" t="s">
         <v>29</v>
       </c>
@@ -7581,144 +7581,144 @@
       <c r="G16" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="54" t="s">
+      <c r="H16" s="101" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="52"/>
-      <c r="J16" s="55"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="49"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="90" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="48"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="17" t="s">
         <v>79</v>
-      </c>
-      <c r="B17" s="52"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>81</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17" s="57"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="55"/>
+        <v>78</v>
+      </c>
+      <c r="H17" s="47"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="49"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="56"/>
-      <c r="B18" s="52"/>
-      <c r="C18" s="53"/>
+      <c r="A18" s="90"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="65"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="55"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="49"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="56"/>
-      <c r="B19" s="52"/>
-      <c r="C19" s="53"/>
+      <c r="A19" s="90"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="65"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="55"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="49"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="56"/>
-      <c r="B20" s="52"/>
-      <c r="C20" s="53"/>
+      <c r="A20" s="90"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="65"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="55"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="49"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="56"/>
-      <c r="B21" s="52"/>
-      <c r="C21" s="53"/>
+      <c r="A21" s="90"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="65"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="55"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="49"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A22" s="49"/>
-      <c r="B22" s="47"/>
-      <c r="C22" s="50"/>
+      <c r="A22" s="91"/>
+      <c r="B22" s="92"/>
+      <c r="C22" s="93"/>
       <c r="D22" s="39"/>
       <c r="E22" s="39"/>
       <c r="F22" s="40"/>
       <c r="G22" s="40"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="48"/>
+      <c r="H22" s="94"/>
+      <c r="I22" s="92"/>
+      <c r="J22" s="95"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="58"/>
-      <c r="B23" s="59"/>
-      <c r="C23" s="59"/>
+      <c r="A23" s="106"/>
+      <c r="B23" s="89"/>
+      <c r="C23" s="89"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="59"/>
+      <c r="H23" s="88"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="89"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="41" t="s">
+      <c r="A24" s="108" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="42"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="42"/>
+      <c r="B24" s="109"/>
+      <c r="C24" s="109"/>
+      <c r="D24" s="109"/>
+      <c r="E24" s="109"/>
+      <c r="F24" s="109"/>
+      <c r="G24" s="109"/>
+      <c r="H24" s="109"/>
+      <c r="I24" s="109"/>
+      <c r="J24" s="109"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="61" t="s">
+      <c r="A25" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="44"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="43" t="s">
-        <v>85</v>
-      </c>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="45"/>
+      <c r="B25" s="103"/>
+      <c r="C25" s="104"/>
+      <c r="D25" s="110" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" s="103"/>
+      <c r="F25" s="103"/>
+      <c r="G25" s="103"/>
+      <c r="H25" s="104"/>
       <c r="I25" s="37" t="s">
         <v>27</v>
       </c>
       <c r="J25" s="38" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="51" t="s">
+      <c r="A26" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="52"/>
-      <c r="C26" s="53"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="65"/>
       <c r="D26" s="15" t="s">
         <v>29</v>
       </c>
@@ -7731,96 +7731,96 @@
       <c r="G26" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H26" s="54" t="s">
+      <c r="H26" s="101" t="s">
         <v>19</v>
       </c>
-      <c r="I26" s="52"/>
-      <c r="J26" s="55"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="49"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="56" t="s">
-        <v>82</v>
-      </c>
-      <c r="B27" s="52"/>
-      <c r="C27" s="53"/>
+      <c r="A27" s="90" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" s="48"/>
+      <c r="C27" s="65"/>
       <c r="D27" s="17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F27" s="18"/>
       <c r="G27" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="H27" s="57"/>
-      <c r="I27" s="52"/>
-      <c r="J27" s="55"/>
+        <v>81</v>
+      </c>
+      <c r="H27" s="47"/>
+      <c r="I27" s="48"/>
+      <c r="J27" s="49"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A28" s="49"/>
-      <c r="B28" s="47"/>
-      <c r="C28" s="50"/>
+      <c r="A28" s="91"/>
+      <c r="B28" s="92"/>
+      <c r="C28" s="93"/>
       <c r="D28" s="39"/>
       <c r="E28" s="39"/>
       <c r="F28" s="40"/>
       <c r="G28" s="40"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="48"/>
+      <c r="H28" s="94"/>
+      <c r="I28" s="92"/>
+      <c r="J28" s="95"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="58"/>
-      <c r="B29" s="59"/>
-      <c r="C29" s="59"/>
+      <c r="A29" s="106"/>
+      <c r="B29" s="89"/>
+      <c r="C29" s="89"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
-      <c r="H29" s="60"/>
-      <c r="I29" s="59"/>
-      <c r="J29" s="59"/>
+      <c r="H29" s="88"/>
+      <c r="I29" s="89"/>
+      <c r="J29" s="89"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="41" t="s">
+      <c r="A30" s="108" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="42"/>
-      <c r="C30" s="42"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="42"/>
-      <c r="J30" s="42"/>
+      <c r="B30" s="109"/>
+      <c r="C30" s="109"/>
+      <c r="D30" s="109"/>
+      <c r="E30" s="109"/>
+      <c r="F30" s="109"/>
+      <c r="G30" s="109"/>
+      <c r="H30" s="109"/>
+      <c r="I30" s="109"/>
+      <c r="J30" s="109"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A31" s="61" t="s">
+      <c r="A31" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="44"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="43" t="s">
-        <v>85</v>
-      </c>
-      <c r="E31" s="44"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="44"/>
-      <c r="H31" s="45"/>
+      <c r="B31" s="103"/>
+      <c r="C31" s="104"/>
+      <c r="D31" s="110" t="s">
+        <v>83</v>
+      </c>
+      <c r="E31" s="103"/>
+      <c r="F31" s="103"/>
+      <c r="G31" s="103"/>
+      <c r="H31" s="104"/>
       <c r="I31" s="37" t="s">
         <v>27</v>
       </c>
       <c r="J31" s="38" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="51" t="s">
+      <c r="A32" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="52"/>
-      <c r="C32" s="53"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="65"/>
       <c r="D32" s="15" t="s">
         <v>29</v>
       </c>
@@ -7833,43 +7833,43 @@
       <c r="G32" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H32" s="54" t="s">
+      <c r="H32" s="101" t="s">
         <v>19</v>
       </c>
-      <c r="I32" s="52"/>
-      <c r="J32" s="55"/>
+      <c r="I32" s="48"/>
+      <c r="J32" s="49"/>
     </row>
     <row r="33" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A33" s="56" t="s">
+      <c r="A33" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="48"/>
+      <c r="C33" s="65"/>
+      <c r="D33" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="B33" s="52"/>
-      <c r="C33" s="53"/>
-      <c r="D33" s="17" t="s">
-        <v>86</v>
-      </c>
       <c r="E33" s="17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F33" s="18"/>
       <c r="G33" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="H33" s="57"/>
-      <c r="I33" s="52"/>
-      <c r="J33" s="55"/>
+        <v>84</v>
+      </c>
+      <c r="H33" s="47"/>
+      <c r="I33" s="48"/>
+      <c r="J33" s="49"/>
     </row>
     <row r="34" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A34" s="49"/>
-      <c r="B34" s="47"/>
-      <c r="C34" s="50"/>
+      <c r="A34" s="91"/>
+      <c r="B34" s="92"/>
+      <c r="C34" s="93"/>
       <c r="D34" s="39"/>
       <c r="E34" s="39"/>
       <c r="F34" s="40"/>
       <c r="G34" s="40"/>
-      <c r="H34" s="46"/>
-      <c r="I34" s="47"/>
-      <c r="J34" s="48"/>
+      <c r="H34" s="94"/>
+      <c r="I34" s="92"/>
+      <c r="J34" s="95"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="36" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8840,6 +8840,41 @@
     <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="51">
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="A18:C18"/>
@@ -8856,41 +8891,6 @@
     <mergeCell ref="A7:J13"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A31:C31"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8910,182 +8910,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="79" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="79" t="s">
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="79" t="s">
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="79" t="s">
+      <c r="P1" s="63"/>
+      <c r="Q1" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="78"/>
-      <c r="S1" s="79" t="s">
+      <c r="R1" s="63"/>
+      <c r="S1" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="81"/>
+      <c r="T1" s="46"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
-      <c r="B2" s="75"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="63"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="83"/>
-      <c r="N2" s="63"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="63"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="63"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="84"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="99"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="75"/>
-      <c r="M3" s="75"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="85"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="58"/>
+      <c r="O3" s="79"/>
+      <c r="P3" s="58"/>
+      <c r="Q3" s="79"/>
+      <c r="R3" s="58"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="100"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="92"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="92"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="102"/>
-      <c r="M4" s="102"/>
-      <c r="N4" s="92"/>
-      <c r="O4" s="91"/>
-      <c r="P4" s="92"/>
-      <c r="Q4" s="91"/>
-      <c r="R4" s="92"/>
-      <c r="S4" s="91"/>
-      <c r="T4" s="115"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="80"/>
+      <c r="R4" s="61"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="119"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="109" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
-      <c r="L5" s="77"/>
-      <c r="M5" s="77"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="81"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
+      <c r="P5" s="45"/>
+      <c r="Q5" s="45"/>
+      <c r="R5" s="45"/>
+      <c r="S5" s="45"/>
+      <c r="T5" s="46"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="96" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="57" t="s">
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="52"/>
-      <c r="O6" s="52"/>
-      <c r="P6" s="52"/>
-      <c r="Q6" s="52"/>
-      <c r="R6" s="52"/>
-      <c r="S6" s="52"/>
-      <c r="T6" s="55"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="48"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="48"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="49"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="57" t="s">
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="52"/>
-      <c r="M7" s="52"/>
-      <c r="N7" s="52"/>
-      <c r="O7" s="52"/>
-      <c r="P7" s="52"/>
-      <c r="Q7" s="52"/>
-      <c r="R7" s="52"/>
-      <c r="S7" s="52"/>
-      <c r="T7" s="55"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="48"/>
+      <c r="R7" s="48"/>
+      <c r="S7" s="48"/>
+      <c r="T7" s="49"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9284,37 +9284,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="96" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="53"/>
+      <c r="B15" s="65"/>
       <c r="C15" s="118" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="53"/>
-      <c r="E15" s="54" t="s">
+      <c r="D15" s="65"/>
+      <c r="E15" s="101" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="53"/>
-      <c r="G15" s="54" t="s">
+      <c r="F15" s="65"/>
+      <c r="G15" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="52"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="54" t="s">
+      <c r="H15" s="48"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="101" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="53"/>
-      <c r="L15" s="54" t="s">
+      <c r="K15" s="65"/>
+      <c r="L15" s="101" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="52"/>
-      <c r="N15" s="53"/>
-      <c r="O15" s="54" t="s">
+      <c r="M15" s="48"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="101" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="52"/>
-      <c r="Q15" s="53"/>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="65"/>
       <c r="R15" s="15" t="s">
         <v>51</v>
       </c>
@@ -9326,37 +9326,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="116">
+      <c r="A16" s="111">
         <v>1</v>
       </c>
-      <c r="B16" s="53"/>
-      <c r="C16" s="117" t="s">
+      <c r="B16" s="65"/>
+      <c r="C16" s="112" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="53"/>
-      <c r="E16" s="117" t="s">
+      <c r="D16" s="65"/>
+      <c r="E16" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="53"/>
-      <c r="G16" s="111" t="s">
+      <c r="F16" s="65"/>
+      <c r="G16" s="117" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="52"/>
-      <c r="I16" s="53"/>
-      <c r="J16" s="111" t="s">
+      <c r="H16" s="48"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="117" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="53"/>
-      <c r="L16" s="113" t="s">
+      <c r="K16" s="65"/>
+      <c r="L16" s="115" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="52"/>
-      <c r="N16" s="53"/>
-      <c r="O16" s="113" t="s">
+      <c r="M16" s="48"/>
+      <c r="N16" s="65"/>
+      <c r="O16" s="115" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="52"/>
-      <c r="Q16" s="53"/>
+      <c r="P16" s="48"/>
+      <c r="Q16" s="65"/>
       <c r="R16" s="31"/>
       <c r="S16" s="31"/>
       <c r="T16" s="32"/>
@@ -9368,37 +9368,37 @@
       <c r="Z16" s="33"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="116">
+      <c r="A17" s="111">
         <v>2</v>
       </c>
-      <c r="B17" s="53"/>
-      <c r="C17" s="117" t="s">
+      <c r="B17" s="65"/>
+      <c r="C17" s="112" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="53"/>
-      <c r="E17" s="117" t="s">
+      <c r="D17" s="65"/>
+      <c r="E17" s="112" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="53"/>
-      <c r="G17" s="111" t="s">
+      <c r="F17" s="65"/>
+      <c r="G17" s="117" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="52"/>
-      <c r="I17" s="53"/>
-      <c r="J17" s="111" t="s">
+      <c r="H17" s="48"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="117" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="53"/>
-      <c r="L17" s="113" t="s">
+      <c r="K17" s="65"/>
+      <c r="L17" s="115" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="52"/>
-      <c r="N17" s="53"/>
-      <c r="O17" s="113" t="s">
+      <c r="M17" s="48"/>
+      <c r="N17" s="65"/>
+      <c r="O17" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="P17" s="52"/>
-      <c r="Q17" s="53"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="65"/>
       <c r="R17" s="31"/>
       <c r="S17" s="31"/>
       <c r="T17" s="32"/>
@@ -9410,23 +9410,23 @@
       <c r="Z17" s="33"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="116"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="117"/>
-      <c r="F18" s="53"/>
-      <c r="G18" s="111"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="111"/>
-      <c r="K18" s="53"/>
-      <c r="L18" s="113"/>
-      <c r="M18" s="52"/>
-      <c r="N18" s="53"/>
-      <c r="O18" s="113"/>
-      <c r="P18" s="52"/>
-      <c r="Q18" s="53"/>
+      <c r="A18" s="111"/>
+      <c r="B18" s="65"/>
+      <c r="C18" s="112"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="115"/>
+      <c r="M18" s="48"/>
+      <c r="N18" s="65"/>
+      <c r="O18" s="115"/>
+      <c r="P18" s="48"/>
+      <c r="Q18" s="65"/>
       <c r="R18" s="31"/>
       <c r="S18" s="31"/>
       <c r="T18" s="32"/>
@@ -9438,23 +9438,23 @@
       <c r="Z18" s="33"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="116"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="117"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="111"/>
-      <c r="K19" s="53"/>
-      <c r="L19" s="113"/>
-      <c r="M19" s="52"/>
-      <c r="N19" s="53"/>
-      <c r="O19" s="113"/>
-      <c r="P19" s="52"/>
-      <c r="Q19" s="53"/>
+      <c r="A19" s="111"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="112"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="117"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="117"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="115"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="115"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="65"/>
       <c r="R19" s="31"/>
       <c r="S19" s="31"/>
       <c r="T19" s="32"/>
@@ -9466,23 +9466,23 @@
       <c r="Z19" s="33"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="116"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="117"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="117"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="111"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="113"/>
-      <c r="M20" s="52"/>
-      <c r="N20" s="53"/>
-      <c r="O20" s="113"/>
-      <c r="P20" s="52"/>
-      <c r="Q20" s="53"/>
+      <c r="A20" s="111"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="112"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="112"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="117"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="115"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="65"/>
+      <c r="O20" s="115"/>
+      <c r="P20" s="48"/>
+      <c r="Q20" s="65"/>
       <c r="R20" s="31"/>
       <c r="S20" s="31"/>
       <c r="T20" s="32"/>
@@ -9494,23 +9494,23 @@
       <c r="Z20" s="33"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="116"/>
-      <c r="B21" s="53"/>
-      <c r="C21" s="117"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="117"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="111"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="113"/>
-      <c r="M21" s="52"/>
-      <c r="N21" s="53"/>
-      <c r="O21" s="113"/>
-      <c r="P21" s="52"/>
-      <c r="Q21" s="53"/>
+      <c r="A21" s="111"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="112"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="117"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="117"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="115"/>
+      <c r="M21" s="48"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="115"/>
+      <c r="P21" s="48"/>
+      <c r="Q21" s="65"/>
       <c r="R21" s="31"/>
       <c r="S21" s="31"/>
       <c r="T21" s="32"/>
@@ -9522,23 +9522,23 @@
       <c r="Z21" s="33"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="116"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="117"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="111"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="111"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="113"/>
-      <c r="M22" s="52"/>
-      <c r="N22" s="53"/>
-      <c r="O22" s="113"/>
-      <c r="P22" s="52"/>
-      <c r="Q22" s="53"/>
+      <c r="A22" s="111"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="112"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="115"/>
+      <c r="M22" s="48"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="115"/>
+      <c r="P22" s="48"/>
+      <c r="Q22" s="65"/>
       <c r="R22" s="31"/>
       <c r="S22" s="31"/>
       <c r="T22" s="32"/>
@@ -9550,23 +9550,23 @@
       <c r="Z22" s="33"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="116"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="117"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="117"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="111"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="111"/>
-      <c r="K23" s="53"/>
-      <c r="L23" s="113"/>
-      <c r="M23" s="52"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="113"/>
-      <c r="P23" s="52"/>
-      <c r="Q23" s="53"/>
+      <c r="A23" s="111"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="112"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="112"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="117"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="115"/>
+      <c r="M23" s="48"/>
+      <c r="N23" s="65"/>
+      <c r="O23" s="115"/>
+      <c r="P23" s="48"/>
+      <c r="Q23" s="65"/>
       <c r="R23" s="31"/>
       <c r="S23" s="31"/>
       <c r="T23" s="32"/>
@@ -9578,23 +9578,23 @@
       <c r="Z23" s="33"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="116"/>
-      <c r="B24" s="53"/>
-      <c r="C24" s="117"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="111"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="111"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="113"/>
-      <c r="M24" s="52"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="113"/>
-      <c r="P24" s="52"/>
-      <c r="Q24" s="53"/>
+      <c r="A24" s="111"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="112"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="112"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="117"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="117"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="115"/>
+      <c r="M24" s="48"/>
+      <c r="N24" s="65"/>
+      <c r="O24" s="115"/>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="65"/>
       <c r="R24" s="31"/>
       <c r="S24" s="31"/>
       <c r="T24" s="32"/>
@@ -9606,23 +9606,23 @@
       <c r="Z24" s="33"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="116"/>
-      <c r="B25" s="53"/>
-      <c r="C25" s="117"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="117"/>
-      <c r="F25" s="53"/>
-      <c r="G25" s="111"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="53"/>
-      <c r="J25" s="111"/>
-      <c r="K25" s="53"/>
-      <c r="L25" s="113"/>
-      <c r="M25" s="52"/>
-      <c r="N25" s="53"/>
-      <c r="O25" s="113"/>
-      <c r="P25" s="52"/>
-      <c r="Q25" s="53"/>
+      <c r="A25" s="111"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="112"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="117"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="117"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="115"/>
+      <c r="M25" s="48"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="115"/>
+      <c r="P25" s="48"/>
+      <c r="Q25" s="65"/>
       <c r="R25" s="31"/>
       <c r="S25" s="31"/>
       <c r="T25" s="32"/>
@@ -9634,23 +9634,23 @@
       <c r="Z25" s="33"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="116"/>
-      <c r="B26" s="53"/>
-      <c r="C26" s="117"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="117"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="111"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="111"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="113"/>
-      <c r="M26" s="52"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="113"/>
-      <c r="P26" s="52"/>
-      <c r="Q26" s="53"/>
+      <c r="A26" s="111"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="112"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="112"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="117"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="115"/>
+      <c r="M26" s="48"/>
+      <c r="N26" s="65"/>
+      <c r="O26" s="115"/>
+      <c r="P26" s="48"/>
+      <c r="Q26" s="65"/>
       <c r="R26" s="31"/>
       <c r="S26" s="31"/>
       <c r="T26" s="32"/>
@@ -9662,23 +9662,23 @@
       <c r="Z26" s="33"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="116"/>
-      <c r="B27" s="53"/>
-      <c r="C27" s="117"/>
-      <c r="D27" s="53"/>
-      <c r="E27" s="117"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="111"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="111"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="113"/>
-      <c r="M27" s="52"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="113"/>
-      <c r="P27" s="52"/>
-      <c r="Q27" s="53"/>
+      <c r="A27" s="111"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="112"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="117"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="117"/>
+      <c r="K27" s="65"/>
+      <c r="L27" s="115"/>
+      <c r="M27" s="48"/>
+      <c r="N27" s="65"/>
+      <c r="O27" s="115"/>
+      <c r="P27" s="48"/>
+      <c r="Q27" s="65"/>
       <c r="R27" s="31"/>
       <c r="S27" s="31"/>
       <c r="T27" s="32"/>
@@ -9690,23 +9690,23 @@
       <c r="Z27" s="33"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="116"/>
-      <c r="B28" s="53"/>
-      <c r="C28" s="117"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="117"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="111"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="53"/>
-      <c r="J28" s="111"/>
-      <c r="K28" s="53"/>
-      <c r="L28" s="113"/>
-      <c r="M28" s="52"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="113"/>
-      <c r="P28" s="52"/>
-      <c r="Q28" s="53"/>
+      <c r="A28" s="111"/>
+      <c r="B28" s="65"/>
+      <c r="C28" s="112"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="117"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="117"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="115"/>
+      <c r="M28" s="48"/>
+      <c r="N28" s="65"/>
+      <c r="O28" s="115"/>
+      <c r="P28" s="48"/>
+      <c r="Q28" s="65"/>
       <c r="R28" s="31"/>
       <c r="S28" s="31"/>
       <c r="T28" s="32"/>
@@ -9718,23 +9718,23 @@
       <c r="Z28" s="33"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="116"/>
-      <c r="B29" s="53"/>
-      <c r="C29" s="117"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="117"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="111"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="53"/>
-      <c r="J29" s="111"/>
-      <c r="K29" s="53"/>
-      <c r="L29" s="113"/>
-      <c r="M29" s="52"/>
-      <c r="N29" s="53"/>
-      <c r="O29" s="113"/>
-      <c r="P29" s="52"/>
-      <c r="Q29" s="53"/>
+      <c r="A29" s="111"/>
+      <c r="B29" s="65"/>
+      <c r="C29" s="112"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="117"/>
+      <c r="H29" s="48"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="117"/>
+      <c r="K29" s="65"/>
+      <c r="L29" s="115"/>
+      <c r="M29" s="48"/>
+      <c r="N29" s="65"/>
+      <c r="O29" s="115"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="65"/>
       <c r="R29" s="31"/>
       <c r="S29" s="31"/>
       <c r="T29" s="32"/>
@@ -9746,23 +9746,23 @@
       <c r="Z29" s="33"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="116"/>
-      <c r="B30" s="53"/>
-      <c r="C30" s="117"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="117"/>
-      <c r="F30" s="53"/>
-      <c r="G30" s="111"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="53"/>
-      <c r="J30" s="111"/>
-      <c r="K30" s="53"/>
-      <c r="L30" s="113"/>
-      <c r="M30" s="52"/>
-      <c r="N30" s="53"/>
-      <c r="O30" s="113"/>
-      <c r="P30" s="52"/>
-      <c r="Q30" s="53"/>
+      <c r="A30" s="111"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="112"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="112"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="117"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="117"/>
+      <c r="K30" s="65"/>
+      <c r="L30" s="115"/>
+      <c r="M30" s="48"/>
+      <c r="N30" s="65"/>
+      <c r="O30" s="115"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="65"/>
       <c r="R30" s="31"/>
       <c r="S30" s="31"/>
       <c r="T30" s="32"/>
@@ -9774,23 +9774,23 @@
       <c r="Z30" s="33"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="119"/>
-      <c r="B31" s="99"/>
-      <c r="C31" s="120"/>
-      <c r="D31" s="99"/>
-      <c r="E31" s="120"/>
-      <c r="F31" s="99"/>
-      <c r="G31" s="112"/>
-      <c r="H31" s="98"/>
-      <c r="I31" s="99"/>
-      <c r="J31" s="112"/>
-      <c r="K31" s="99"/>
-      <c r="L31" s="114"/>
-      <c r="M31" s="98"/>
-      <c r="N31" s="99"/>
-      <c r="O31" s="114"/>
-      <c r="P31" s="98"/>
-      <c r="Q31" s="99"/>
+      <c r="A31" s="113"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="114"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="114"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="120"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="120"/>
+      <c r="K31" s="52"/>
+      <c r="L31" s="116"/>
+      <c r="M31" s="42"/>
+      <c r="N31" s="52"/>
+      <c r="O31" s="116"/>
+      <c r="P31" s="42"/>
+      <c r="Q31" s="52"/>
       <c r="R31" s="34"/>
       <c r="S31" s="34"/>
       <c r="T31" s="35"/>
@@ -10788,6 +10788,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -10812,118 +10924,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_タスク詳細画面.xlsx
+++ b/document/成果物ドキュメント_タスク詳細画面.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-14\Documents\project\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B39778-3D0D-4E47-B625-2F12D82124FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F663EC95-4457-4476-967A-BAE86EA821A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10245" yWindow="0" windowWidth="10245" windowHeight="10920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="99">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -330,10 +330,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>itemDeleteComfirm.jsp</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>コメントを投稿</t>
     <rPh sb="5" eb="7">
       <t>トウコウ</t>
@@ -353,47 +349,131 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t xml:space="preserve">1.ユーザーがタスク一覧画面からタスクの詳細ボタンを選択する
+    <t>システムがタスク詳細を表示し編集、削除、コメント投稿、コメント削除画面へのボタンを表示すること</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.ユーザーがタスク一覧画面からタスク詳細を選択する
 2.システムが押下されたタスクの詳細画面を表示する
-3.システムがタスクの名前、カテゴリ、期限、担当者情報、ステータス情報、メモ、コメントを表示する。
-</t>
+3.システムがタスクの名前、カテゴリ、期限、担当者情報、ステータス情報、メモ、コメントを表示する</t>
     <rPh sb="10" eb="14">
       <t>イチランガメン</t>
     </rPh>
-    <rPh sb="20" eb="22">
+    <rPh sb="19" eb="21">
       <t>ショウサイ</t>
     </rPh>
-    <rPh sb="26" eb="28">
+    <rPh sb="22" eb="24">
       <t>センタク</t>
     </rPh>
-    <rPh sb="38" eb="40">
+    <rPh sb="34" eb="36">
       <t>オウカ</t>
     </rPh>
-    <rPh sb="47" eb="51">
+    <rPh sb="43" eb="47">
       <t>ショウサイガメン</t>
     </rPh>
-    <rPh sb="52" eb="54">
+    <rPh sb="48" eb="50">
       <t>ヒョウジ</t>
     </rPh>
-    <rPh sb="68" eb="70">
+    <rPh sb="64" eb="66">
       <t>ナマエ</t>
     </rPh>
-    <rPh sb="76" eb="78">
+    <rPh sb="72" eb="74">
       <t>キゲン</t>
     </rPh>
-    <rPh sb="79" eb="84">
+    <rPh sb="75" eb="80">
       <t>タントウシャジョウホウ</t>
     </rPh>
-    <rPh sb="90" eb="92">
+    <rPh sb="86" eb="88">
       <t>ジョウホウ</t>
     </rPh>
-    <rPh sb="101" eb="103">
+    <rPh sb="97" eb="99">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>システムがタスク詳細を表示し編集、削除、コメント投稿、コメント削除画面へのボタンを表示すること</t>
+    <t>システムは詳細画面の時点でタスクの担当者以外は編集、削除を選択できないようにする</t>
+    <rPh sb="5" eb="9">
+      <t>ショウサイガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジテン</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログインユーザーと担当者が一致していた場合表示する</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>誰でも投稿可能</t>
+    <rPh sb="0" eb="1">
+      <t>ダレ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>task-delete-confirm.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>comment-post-form.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>comment-delete-servlet</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>コメントID</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>１～</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログインユーザーと投稿者が一致していた場合表示する</t>
+    <rPh sb="9" eb="12">
+      <t>トウコウシャ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログインユーザーと担当者が一致していた場合表示する</t>
+    <rPh sb="9" eb="12">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウジ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1316,7 +1396,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1440,128 +1520,128 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1581,32 +1661,62 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1620,35 +1730,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1656,29 +1751,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1834,60 +1929,49 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>745435</xdr:colOff>
+      <xdr:colOff>485775</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>256761</xdr:rowOff>
+      <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>127344</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1104900</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>41413</xdr:rowOff>
+      <xdr:rowOff>39874</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A12FE16-4227-15D8-9642-3126F36265C1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BD3D15D-1DAF-FC67-0158-D8F05738753E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="2882348" y="1548848"/>
-          <a:ext cx="2736366" cy="1888435"/>
+          <a:off x="2628900" y="1476375"/>
+          <a:ext cx="2847975" cy="1954399"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2120,67 +2204,67 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="69"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
-      <c r="N4" s="57"/>
-      <c r="O4" s="57"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="57"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="57"/>
-      <c r="O6" s="57"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2201,16 +2285,16 @@
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
       <c r="E8" s="86" t="s">
-        <v>86</v>
-      </c>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-      <c r="K8" s="57"/>
-      <c r="L8" s="57"/>
-      <c r="M8" s="57"/>
+        <v>85</v>
+      </c>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
@@ -2220,26 +2304,26 @@
       <c r="G13" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="65"/>
+      <c r="H13" s="57"/>
       <c r="I13" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="48"/>
-      <c r="K13" s="65"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="57"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="82"/>
-      <c r="H14" s="65"/>
+      <c r="H14" s="57"/>
       <c r="I14" s="82"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="65"/>
+      <c r="J14" s="59"/>
+      <c r="K14" s="57"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="82"/>
-      <c r="H15" s="65"/>
+      <c r="H15" s="57"/>
       <c r="I15" s="82"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="65"/>
+      <c r="J15" s="59"/>
+      <c r="K15" s="57"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2251,10 +2335,10 @@
       <c r="G17" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="57"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="69"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3268,19 +3352,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
@@ -3292,192 +3376,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="44"/>
+      <c r="F2" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="81">
-        <v>46122</v>
-      </c>
-      <c r="I2" s="70" t="s">
+      <c r="G2" s="44"/>
+      <c r="H2" s="125">
+        <v>46126</v>
+      </c>
+      <c r="I2" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="73"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="55"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="44" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="46"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="80"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="47" t="s">
+      <c r="B6" s="59"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="60" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="49"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="61"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="47" t="s">
+      <c r="B7" s="59"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="60" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="49"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="61"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="47" t="s">
+      <c r="B8" s="59"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="49"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="61"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="66" t="s">
+      <c r="A9" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="65"/>
-      <c r="D9" s="50" t="s">
+      <c r="C9" s="57"/>
+      <c r="D9" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="49"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="61"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="67"/>
-      <c r="B10" s="69" t="s">
+      <c r="A10" s="75"/>
+      <c r="B10" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="47" t="s">
+      <c r="C10" s="57"/>
+      <c r="D10" s="60" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="61"/>
+    </row>
+    <row r="11" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A11" s="76"/>
+      <c r="B11" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="57"/>
+      <c r="D11" s="60" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="61"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="59"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="60" t="s">
         <v>87</v>
       </c>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="49"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="68"/>
-      <c r="B11" s="69" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="49"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="64" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="48"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="47" t="s">
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="61"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A13" s="62" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="63"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="49"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="42"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="43"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="78"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4468,17 +4554,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4487,14 +4570,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4516,16 +4602,16 @@
       <c r="A1" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -4537,48 +4623,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="44"/>
+      <c r="F2" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="81">
+      <c r="G2" s="44"/>
+      <c r="H2" s="49">
         <v>46120</v>
       </c>
-      <c r="I2" s="70" t="s">
+      <c r="I2" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="73"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="55"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5936,16 +6022,16 @@
       <c r="A1" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -5957,48 +6043,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="44"/>
+      <c r="F2" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="81">
+      <c r="G2" s="44"/>
+      <c r="H2" s="49">
         <v>46122</v>
       </c>
-      <c r="I2" s="70" t="s">
+      <c r="I2" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="73"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="55"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7339,11 +7425,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1001"/>
+  <dimension ref="A1:J998"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
-    <col min="4" max="10" width="16.7109375" customWidth="1"/>
+    <col min="4" max="9" width="16.7109375" customWidth="1"/>
+    <col min="10" max="10" width="18.7109375" customWidth="1"/>
     <col min="11" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7351,16 +7438,16 @@
       <c r="A1" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -7372,190 +7459,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="44"/>
+      <c r="F2" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="81">
+      <c r="G2" s="44"/>
+      <c r="H2" s="49">
         <v>46122</v>
       </c>
-      <c r="I2" s="70" t="s">
+      <c r="I2" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="73"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="74"/>
+      <c r="A4" s="68"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
       <c r="A5" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="107" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="106" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="46"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="80"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="96" t="s">
+      <c r="A6" s="98" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="49"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="61"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="97"/>
-      <c r="B7" s="98"/>
-      <c r="C7" s="98"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="99"/>
+      <c r="A7" s="107"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="108"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="108"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="109"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="56"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="100"/>
+      <c r="A8" s="68"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="110"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="56"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="100"/>
+      <c r="A9" s="68"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="110"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="56"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="100"/>
+      <c r="A10" s="68"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="69"/>
+      <c r="J10" s="110"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="56"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="100"/>
+      <c r="A11" s="68"/>
+      <c r="B11" s="69"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="110"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="56"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="100"/>
+      <c r="A12" s="68"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="110"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="56"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="100"/>
+      <c r="A13" s="68"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="110"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="96" t="s">
-        <v>85</v>
-      </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="49"/>
+      <c r="A14" s="98" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="59"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="59"/>
+      <c r="J14" s="61"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="96" t="s">
+      <c r="A15" s="98" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="47" t="s">
+      <c r="B15" s="59"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="65"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="57"/>
       <c r="I15" s="15" t="s">
         <v>27</v>
       </c>
@@ -7564,11 +7651,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="96" t="s">
+      <c r="A16" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="65"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="57"/>
       <c r="D16" s="15" t="s">
         <v>29</v>
       </c>
@@ -7581,18 +7668,18 @@
       <c r="G16" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="101" t="s">
+      <c r="H16" s="99" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="48"/>
-      <c r="J16" s="49"/>
+      <c r="I16" s="59"/>
+      <c r="J16" s="61"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="90" t="s">
+      <c r="A17" s="100" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="48"/>
-      <c r="C17" s="65"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="57"/>
       <c r="D17" s="17" t="s">
         <v>78</v>
       </c>
@@ -7603,276 +7690,334 @@
       <c r="G17" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H17" s="47"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="49"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="90"/>
-      <c r="B18" s="48"/>
-      <c r="C18" s="65"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="49"/>
+      <c r="H17" s="60" t="s">
+        <v>98</v>
+      </c>
+      <c r="I17" s="59"/>
+      <c r="J17" s="61"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A18" s="96"/>
+      <c r="B18" s="94"/>
+      <c r="C18" s="97"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="94"/>
+      <c r="J18" s="95"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="90"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="65"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="49"/>
+      <c r="A19" s="101"/>
+      <c r="B19" s="102"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="103"/>
+      <c r="I19" s="102"/>
+      <c r="J19" s="102"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="90"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="65"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="49"/>
+      <c r="A20" s="88" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="89"/>
+      <c r="C20" s="89"/>
+      <c r="D20" s="89"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="89"/>
+      <c r="I20" s="89"/>
+      <c r="J20" s="89"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="90"/>
-      <c r="B21" s="48"/>
-      <c r="C21" s="65"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="48"/>
-      <c r="J21" s="49"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A22" s="91"/>
-      <c r="B22" s="92"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="94"/>
-      <c r="I22" s="92"/>
-      <c r="J22" s="95"/>
+      <c r="A21" s="104" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="91"/>
+      <c r="C21" s="92"/>
+      <c r="D21" s="90" t="s">
+        <v>92</v>
+      </c>
+      <c r="E21" s="91"/>
+      <c r="F21" s="91"/>
+      <c r="G21" s="91"/>
+      <c r="H21" s="92"/>
+      <c r="I21" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="38" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="98" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="59"/>
+      <c r="C22" s="57"/>
+      <c r="D22" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="99" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="59"/>
+      <c r="J22" s="61"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="106"/>
-      <c r="B23" s="89"/>
-      <c r="C23" s="89"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="88"/>
-      <c r="I23" s="89"/>
-      <c r="J23" s="89"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="108" t="s">
+      <c r="A23" s="100" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="59"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="I23" s="59"/>
+      <c r="J23" s="61"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A24" s="96"/>
+      <c r="B24" s="94"/>
+      <c r="C24" s="97"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="94"/>
+      <c r="J24" s="95"/>
+    </row>
+    <row r="25" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A25" s="101"/>
+      <c r="B25" s="102"/>
+      <c r="C25" s="102"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="103"/>
+      <c r="I25" s="102"/>
+      <c r="J25" s="102"/>
+    </row>
+    <row r="26" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A26" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="109"/>
-      <c r="C24" s="109"/>
-      <c r="D24" s="109"/>
-      <c r="E24" s="109"/>
-      <c r="F24" s="109"/>
-      <c r="G24" s="109"/>
-      <c r="H24" s="109"/>
-      <c r="I24" s="109"/>
-      <c r="J24" s="109"/>
-    </row>
-    <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="102" t="s">
+      <c r="B26" s="89"/>
+      <c r="C26" s="89"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="89"/>
+      <c r="F26" s="89"/>
+      <c r="G26" s="89"/>
+      <c r="H26" s="89"/>
+      <c r="I26" s="89"/>
+      <c r="J26" s="89"/>
+    </row>
+    <row r="27" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A27" s="104" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="103"/>
-      <c r="C25" s="104"/>
-      <c r="D25" s="110" t="s">
+      <c r="B27" s="91"/>
+      <c r="C27" s="92"/>
+      <c r="D27" s="90" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="91"/>
+      <c r="F27" s="91"/>
+      <c r="G27" s="91"/>
+      <c r="H27" s="92"/>
+      <c r="I27" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="J27" s="38" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A28" s="98" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="59"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H28" s="99" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" s="59"/>
+      <c r="J28" s="61"/>
+    </row>
+    <row r="29" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A29" s="100" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="59"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E29" s="17"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="H29" s="60" t="s">
+        <v>97</v>
+      </c>
+      <c r="I29" s="59"/>
+      <c r="J29" s="61"/>
+    </row>
+    <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A30" s="96"/>
+      <c r="B30" s="94"/>
+      <c r="C30" s="97"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="94"/>
+      <c r="J30" s="95"/>
+    </row>
+    <row r="31" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A31" s="121"/>
+      <c r="B31" s="122"/>
+      <c r="C31" s="122"/>
+      <c r="D31" s="121"/>
+      <c r="E31" s="121"/>
+      <c r="F31" s="123"/>
+      <c r="G31" s="123"/>
+      <c r="H31" s="124"/>
+      <c r="I31" s="122"/>
+      <c r="J31" s="122"/>
+    </row>
+    <row r="32" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A32" s="88" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="89"/>
+      <c r="C32" s="89"/>
+      <c r="D32" s="89"/>
+      <c r="E32" s="89"/>
+      <c r="F32" s="89"/>
+      <c r="G32" s="89"/>
+      <c r="H32" s="89"/>
+      <c r="I32" s="89"/>
+      <c r="J32" s="89"/>
+    </row>
+    <row r="33" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A33" s="104" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" s="91"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="90" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" s="91"/>
+      <c r="F33" s="91"/>
+      <c r="G33" s="91"/>
+      <c r="H33" s="92"/>
+      <c r="I33" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="J33" s="38" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A34" s="98" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="59"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G34" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" s="99" t="s">
+        <v>19</v>
+      </c>
+      <c r="I34" s="59"/>
+      <c r="J34" s="61"/>
+    </row>
+    <row r="35" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A35" s="100" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="59"/>
+      <c r="C35" s="57"/>
+      <c r="D35" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="103"/>
-      <c r="F25" s="103"/>
-      <c r="G25" s="103"/>
-      <c r="H25" s="104"/>
-      <c r="I25" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="J25" s="38" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="96" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="48"/>
-      <c r="C26" s="65"/>
-      <c r="D26" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G26" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="H26" s="101" t="s">
-        <v>19</v>
-      </c>
-      <c r="I26" s="48"/>
-      <c r="J26" s="49"/>
-    </row>
-    <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="90" t="s">
-        <v>80</v>
-      </c>
-      <c r="B27" s="48"/>
-      <c r="C27" s="65"/>
-      <c r="D27" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E27" s="17" t="s">
+      <c r="E35" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="H27" s="47"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="49"/>
-    </row>
-    <row r="28" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A28" s="91"/>
-      <c r="B28" s="92"/>
-      <c r="C28" s="93"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="94"/>
-      <c r="I28" s="92"/>
-      <c r="J28" s="95"/>
-    </row>
-    <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="106"/>
-      <c r="B29" s="89"/>
-      <c r="C29" s="89"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="88"/>
-      <c r="I29" s="89"/>
-      <c r="J29" s="89"/>
-    </row>
-    <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="108" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="109"/>
-      <c r="C30" s="109"/>
-      <c r="D30" s="109"/>
-      <c r="E30" s="109"/>
-      <c r="F30" s="109"/>
-      <c r="G30" s="109"/>
-      <c r="H30" s="109"/>
-      <c r="I30" s="109"/>
-      <c r="J30" s="109"/>
-    </row>
-    <row r="31" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A31" s="102" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="103"/>
-      <c r="C31" s="104"/>
-      <c r="D31" s="110" t="s">
+      <c r="F35" s="18"/>
+      <c r="G35" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="E31" s="103"/>
-      <c r="F31" s="103"/>
-      <c r="G31" s="103"/>
-      <c r="H31" s="104"/>
-      <c r="I31" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="J31" s="38" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="96" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="48"/>
-      <c r="C32" s="65"/>
-      <c r="D32" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G32" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="H32" s="101" t="s">
-        <v>19</v>
-      </c>
-      <c r="I32" s="48"/>
-      <c r="J32" s="49"/>
-    </row>
-    <row r="33" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A33" s="90" t="s">
-        <v>82</v>
-      </c>
-      <c r="B33" s="48"/>
-      <c r="C33" s="65"/>
-      <c r="D33" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="H33" s="47"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="49"/>
-    </row>
-    <row r="34" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A34" s="91"/>
-      <c r="B34" s="92"/>
-      <c r="C34" s="93"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="94"/>
-      <c r="I34" s="92"/>
-      <c r="J34" s="95"/>
-    </row>
-    <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="36" spans="1:10" ht="12.75" customHeight="1"/>
+      <c r="H35" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="I35" s="59"/>
+      <c r="J35" s="61"/>
+    </row>
+    <row r="36" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A36" s="96"/>
+      <c r="B36" s="94"/>
+      <c r="C36" s="97"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="93"/>
+      <c r="I36" s="94"/>
+      <c r="J36" s="95"/>
+    </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="38" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="39" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8835,26 +8980,33 @@
     <row r="996" ht="12.75" customHeight="1"/>
     <row r="997" ht="12.75" customHeight="1"/>
     <row r="998" ht="12.75" customHeight="1"/>
-    <row r="999" ht="12.75" customHeight="1"/>
-    <row r="1000" ht="12.75" customHeight="1"/>
-    <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="51">
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="D31:H31"/>
+  <mergeCells count="52">
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="H34:J34"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
@@ -8863,34 +9015,25 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A27:C27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8910,182 +9053,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="76" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="76" t="s">
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="76" t="s">
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="76" t="s">
+      <c r="P1" s="42"/>
+      <c r="Q1" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="63"/>
-      <c r="S1" s="76" t="s">
+      <c r="R1" s="42"/>
+      <c r="S1" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="46"/>
+      <c r="T1" s="80"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="78"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="99"/>
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="108"/>
+      <c r="M2" s="108"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="109"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="58"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="58"/>
-      <c r="Q3" s="79"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="100"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="45"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="110"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="61"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="61"/>
-      <c r="Q4" s="80"/>
-      <c r="R4" s="61"/>
-      <c r="S4" s="80"/>
-      <c r="T4" s="119"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="47"/>
+      <c r="T4" s="115"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
       <c r="A5" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="44" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
-      <c r="R5" s="45"/>
-      <c r="S5" s="45"/>
-      <c r="T5" s="46"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
+      <c r="L5" s="73"/>
+      <c r="M5" s="73"/>
+      <c r="N5" s="73"/>
+      <c r="O5" s="73"/>
+      <c r="P5" s="73"/>
+      <c r="Q5" s="73"/>
+      <c r="R5" s="73"/>
+      <c r="S5" s="73"/>
+      <c r="T5" s="80"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="96" t="s">
+      <c r="A6" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="47" t="s">
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="48"/>
-      <c r="O6" s="48"/>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="48"/>
-      <c r="S6" s="48"/>
-      <c r="T6" s="49"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="59"/>
+      <c r="Q6" s="59"/>
+      <c r="R6" s="59"/>
+      <c r="S6" s="59"/>
+      <c r="T6" s="61"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="96" t="s">
+      <c r="A7" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="47" t="s">
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48"/>
-      <c r="N7" s="48"/>
-      <c r="O7" s="48"/>
-      <c r="P7" s="48"/>
-      <c r="Q7" s="48"/>
-      <c r="R7" s="48"/>
-      <c r="S7" s="48"/>
-      <c r="T7" s="49"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="59"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="59"/>
+      <c r="N7" s="59"/>
+      <c r="O7" s="59"/>
+      <c r="P7" s="59"/>
+      <c r="Q7" s="59"/>
+      <c r="R7" s="59"/>
+      <c r="S7" s="59"/>
+      <c r="T7" s="61"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9284,37 +9427,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="96" t="s">
+      <c r="A15" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="65"/>
+      <c r="B15" s="57"/>
       <c r="C15" s="118" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="65"/>
-      <c r="E15" s="101" t="s">
+      <c r="D15" s="57"/>
+      <c r="E15" s="99" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="101" t="s">
+      <c r="F15" s="57"/>
+      <c r="G15" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="48"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="101" t="s">
+      <c r="H15" s="59"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="99" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="65"/>
-      <c r="L15" s="101" t="s">
+      <c r="K15" s="57"/>
+      <c r="L15" s="99" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="48"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="101" t="s">
+      <c r="M15" s="59"/>
+      <c r="N15" s="57"/>
+      <c r="O15" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="48"/>
-      <c r="Q15" s="65"/>
+      <c r="P15" s="59"/>
+      <c r="Q15" s="57"/>
       <c r="R15" s="15" t="s">
         <v>51</v>
       </c>
@@ -9326,37 +9469,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="111">
+      <c r="A16" s="116">
         <v>1</v>
       </c>
-      <c r="B16" s="65"/>
-      <c r="C16" s="112" t="s">
+      <c r="B16" s="57"/>
+      <c r="C16" s="117" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="112" t="s">
+      <c r="D16" s="57"/>
+      <c r="E16" s="117" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="65"/>
-      <c r="G16" s="117" t="s">
+      <c r="F16" s="57"/>
+      <c r="G16" s="111" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="48"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="117" t="s">
+      <c r="H16" s="59"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="111" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="65"/>
-      <c r="L16" s="115" t="s">
+      <c r="K16" s="57"/>
+      <c r="L16" s="113" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="48"/>
-      <c r="N16" s="65"/>
-      <c r="O16" s="115" t="s">
+      <c r="M16" s="59"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="113" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="48"/>
-      <c r="Q16" s="65"/>
+      <c r="P16" s="59"/>
+      <c r="Q16" s="57"/>
       <c r="R16" s="31"/>
       <c r="S16" s="31"/>
       <c r="T16" s="32"/>
@@ -9368,37 +9511,37 @@
       <c r="Z16" s="33"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="111">
+      <c r="A17" s="116">
         <v>2</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="112" t="s">
+      <c r="B17" s="57"/>
+      <c r="C17" s="117" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="65"/>
-      <c r="E17" s="112" t="s">
+      <c r="D17" s="57"/>
+      <c r="E17" s="117" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="65"/>
-      <c r="G17" s="117" t="s">
+      <c r="F17" s="57"/>
+      <c r="G17" s="111" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="48"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="117" t="s">
+      <c r="H17" s="59"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="111" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="65"/>
-      <c r="L17" s="115" t="s">
+      <c r="K17" s="57"/>
+      <c r="L17" s="113" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="48"/>
-      <c r="N17" s="65"/>
-      <c r="O17" s="115" t="s">
+      <c r="M17" s="59"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="P17" s="48"/>
-      <c r="Q17" s="65"/>
+      <c r="P17" s="59"/>
+      <c r="Q17" s="57"/>
       <c r="R17" s="31"/>
       <c r="S17" s="31"/>
       <c r="T17" s="32"/>
@@ -9410,23 +9553,23 @@
       <c r="Z17" s="33"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="111"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="112"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="112"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="65"/>
-      <c r="L18" s="115"/>
-      <c r="M18" s="48"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="115"/>
-      <c r="P18" s="48"/>
-      <c r="Q18" s="65"/>
+      <c r="A18" s="116"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="111"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="113"/>
+      <c r="M18" s="59"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="113"/>
+      <c r="P18" s="59"/>
+      <c r="Q18" s="57"/>
       <c r="R18" s="31"/>
       <c r="S18" s="31"/>
       <c r="T18" s="32"/>
@@ -9438,23 +9581,23 @@
       <c r="Z18" s="33"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="111"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="112"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="112"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="117"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="117"/>
-      <c r="K19" s="65"/>
-      <c r="L19" s="115"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="115"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="65"/>
+      <c r="A19" s="116"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="111"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="113"/>
+      <c r="M19" s="59"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="113"/>
+      <c r="P19" s="59"/>
+      <c r="Q19" s="57"/>
       <c r="R19" s="31"/>
       <c r="S19" s="31"/>
       <c r="T19" s="32"/>
@@ -9466,23 +9609,23 @@
       <c r="Z19" s="33"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="111"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="112"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="112"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="117"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="117"/>
-      <c r="K20" s="65"/>
-      <c r="L20" s="115"/>
-      <c r="M20" s="48"/>
-      <c r="N20" s="65"/>
-      <c r="O20" s="115"/>
-      <c r="P20" s="48"/>
-      <c r="Q20" s="65"/>
+      <c r="A20" s="116"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="111"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="113"/>
+      <c r="M20" s="59"/>
+      <c r="N20" s="57"/>
+      <c r="O20" s="113"/>
+      <c r="P20" s="59"/>
+      <c r="Q20" s="57"/>
       <c r="R20" s="31"/>
       <c r="S20" s="31"/>
       <c r="T20" s="32"/>
@@ -9494,23 +9637,23 @@
       <c r="Z20" s="33"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="111"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="112"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="112"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="117"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="117"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="115"/>
-      <c r="M21" s="48"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="115"/>
-      <c r="P21" s="48"/>
-      <c r="Q21" s="65"/>
+      <c r="A21" s="116"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="117"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="117"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="111"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="113"/>
+      <c r="M21" s="59"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="113"/>
+      <c r="P21" s="59"/>
+      <c r="Q21" s="57"/>
       <c r="R21" s="31"/>
       <c r="S21" s="31"/>
       <c r="T21" s="32"/>
@@ -9522,23 +9665,23 @@
       <c r="Z21" s="33"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="111"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="112"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="112"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="117"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="117"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="115"/>
-      <c r="M22" s="48"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="115"/>
-      <c r="P22" s="48"/>
-      <c r="Q22" s="65"/>
+      <c r="A22" s="116"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="111"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="111"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="113"/>
+      <c r="M22" s="59"/>
+      <c r="N22" s="57"/>
+      <c r="O22" s="113"/>
+      <c r="P22" s="59"/>
+      <c r="Q22" s="57"/>
       <c r="R22" s="31"/>
       <c r="S22" s="31"/>
       <c r="T22" s="32"/>
@@ -9550,23 +9693,23 @@
       <c r="Z22" s="33"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="111"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="112"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="112"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="117"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="117"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="115"/>
-      <c r="M23" s="48"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="115"/>
-      <c r="P23" s="48"/>
-      <c r="Q23" s="65"/>
+      <c r="A23" s="116"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="117"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="111"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="111"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="113"/>
+      <c r="M23" s="59"/>
+      <c r="N23" s="57"/>
+      <c r="O23" s="113"/>
+      <c r="P23" s="59"/>
+      <c r="Q23" s="57"/>
       <c r="R23" s="31"/>
       <c r="S23" s="31"/>
       <c r="T23" s="32"/>
@@ -9578,23 +9721,23 @@
       <c r="Z23" s="33"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="111"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="112"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="112"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="117"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="117"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="115"/>
-      <c r="M24" s="48"/>
-      <c r="N24" s="65"/>
-      <c r="O24" s="115"/>
-      <c r="P24" s="48"/>
-      <c r="Q24" s="65"/>
+      <c r="A24" s="116"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="111"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="111"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="113"/>
+      <c r="M24" s="59"/>
+      <c r="N24" s="57"/>
+      <c r="O24" s="113"/>
+      <c r="P24" s="59"/>
+      <c r="Q24" s="57"/>
       <c r="R24" s="31"/>
       <c r="S24" s="31"/>
       <c r="T24" s="32"/>
@@ -9606,23 +9749,23 @@
       <c r="Z24" s="33"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="111"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="112"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="112"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="117"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="117"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="115"/>
-      <c r="M25" s="48"/>
-      <c r="N25" s="65"/>
-      <c r="O25" s="115"/>
-      <c r="P25" s="48"/>
-      <c r="Q25" s="65"/>
+      <c r="A25" s="116"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="117"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="111"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="111"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="113"/>
+      <c r="M25" s="59"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="113"/>
+      <c r="P25" s="59"/>
+      <c r="Q25" s="57"/>
       <c r="R25" s="31"/>
       <c r="S25" s="31"/>
       <c r="T25" s="32"/>
@@ -9634,23 +9777,23 @@
       <c r="Z25" s="33"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="111"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="112"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="112"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="117"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="117"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="115"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="65"/>
-      <c r="O26" s="115"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="65"/>
+      <c r="A26" s="116"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="111"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="111"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="113"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="113"/>
+      <c r="P26" s="59"/>
+      <c r="Q26" s="57"/>
       <c r="R26" s="31"/>
       <c r="S26" s="31"/>
       <c r="T26" s="32"/>
@@ -9662,23 +9805,23 @@
       <c r="Z26" s="33"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="111"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="112"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="112"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="117"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="117"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="115"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="65"/>
-      <c r="O27" s="115"/>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="65"/>
+      <c r="A27" s="116"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="117"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="117"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="111"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="111"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="113"/>
+      <c r="M27" s="59"/>
+      <c r="N27" s="57"/>
+      <c r="O27" s="113"/>
+      <c r="P27" s="59"/>
+      <c r="Q27" s="57"/>
       <c r="R27" s="31"/>
       <c r="S27" s="31"/>
       <c r="T27" s="32"/>
@@ -9690,23 +9833,23 @@
       <c r="Z27" s="33"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="111"/>
-      <c r="B28" s="65"/>
-      <c r="C28" s="112"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="112"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="117"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="117"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="115"/>
-      <c r="M28" s="48"/>
-      <c r="N28" s="65"/>
-      <c r="O28" s="115"/>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="65"/>
+      <c r="A28" s="116"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="111"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="111"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="113"/>
+      <c r="M28" s="59"/>
+      <c r="N28" s="57"/>
+      <c r="O28" s="113"/>
+      <c r="P28" s="59"/>
+      <c r="Q28" s="57"/>
       <c r="R28" s="31"/>
       <c r="S28" s="31"/>
       <c r="T28" s="32"/>
@@ -9718,23 +9861,23 @@
       <c r="Z28" s="33"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="111"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="112"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="112"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="117"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="117"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="115"/>
-      <c r="M29" s="48"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="115"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="65"/>
+      <c r="A29" s="116"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="117"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="117"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="111"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="111"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="113"/>
+      <c r="M29" s="59"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="113"/>
+      <c r="P29" s="59"/>
+      <c r="Q29" s="57"/>
       <c r="R29" s="31"/>
       <c r="S29" s="31"/>
       <c r="T29" s="32"/>
@@ -9746,23 +9889,23 @@
       <c r="Z29" s="33"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="111"/>
-      <c r="B30" s="65"/>
-      <c r="C30" s="112"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="112"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="117"/>
-      <c r="H30" s="48"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="117"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="115"/>
-      <c r="M30" s="48"/>
-      <c r="N30" s="65"/>
-      <c r="O30" s="115"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="65"/>
+      <c r="A30" s="116"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="111"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="111"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="113"/>
+      <c r="M30" s="59"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="113"/>
+      <c r="P30" s="59"/>
+      <c r="Q30" s="57"/>
       <c r="R30" s="31"/>
       <c r="S30" s="31"/>
       <c r="T30" s="32"/>
@@ -9774,23 +9917,23 @@
       <c r="Z30" s="33"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="113"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="114"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="114"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="120"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="120"/>
-      <c r="K31" s="52"/>
-      <c r="L31" s="116"/>
-      <c r="M31" s="42"/>
-      <c r="N31" s="52"/>
-      <c r="O31" s="116"/>
-      <c r="P31" s="42"/>
-      <c r="Q31" s="52"/>
+      <c r="A31" s="119"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="120"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="120"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="112"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="64"/>
+      <c r="J31" s="112"/>
+      <c r="K31" s="64"/>
+      <c r="L31" s="114"/>
+      <c r="M31" s="63"/>
+      <c r="N31" s="64"/>
+      <c r="O31" s="114"/>
+      <c r="P31" s="63"/>
+      <c r="Q31" s="64"/>
       <c r="R31" s="34"/>
       <c r="S31" s="34"/>
       <c r="T31" s="35"/>
@@ -10788,62 +10931,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -10868,62 +11011,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_タスク詳細画面.xlsx
+++ b/document/成果物ドキュメント_タスク詳細画面.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-14\Documents\project\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F663EC95-4457-4476-967A-BAE86EA821A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DCD7AA-3473-4C98-AF06-FC959821DC35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1396,7 +1396,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1520,260 +1520,254 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2186,85 +2180,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="84" t="s">
+      <c r="C2" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85"/>
-      <c r="O2" s="85"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+      <c r="N2" s="91"/>
+      <c r="O2" s="91"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="69"/>
-      <c r="K3" s="69"/>
-      <c r="L3" s="69"/>
-      <c r="M3" s="69"/>
-      <c r="N3" s="69"/>
-      <c r="O3" s="69"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+      <c r="O3" s="71"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="69"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="71"/>
+      <c r="O4" s="71"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="69"/>
-      <c r="K5" s="69"/>
-      <c r="L5" s="69"/>
-      <c r="M5" s="69"/>
-      <c r="N5" s="69"/>
-      <c r="O5" s="69"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="69"/>
-      <c r="O6" s="69"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="71"/>
+      <c r="O6" s="71"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2284,46 +2278,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="86" t="s">
+      <c r="E8" s="92" t="s">
         <v>85</v>
       </c>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="71"/>
+      <c r="K8" s="71"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="71"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="82" t="s">
+      <c r="G13" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="57"/>
-      <c r="I13" s="82" t="s">
+      <c r="H13" s="45"/>
+      <c r="I13" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="59"/>
-      <c r="K13" s="57"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="45"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="82"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="82"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="57"/>
+      <c r="G14" s="88"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="88"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="45"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="82"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="82"/>
-      <c r="J15" s="59"/>
-      <c r="K15" s="57"/>
+      <c r="G15" s="88"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="88"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="45"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2332,13 +2326,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="83" t="s">
+      <c r="G17" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="69"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3352,19 +3346,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="41" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="41" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="42"/>
+      <c r="G1" s="83"/>
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
@@ -3376,194 +3370,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="43" t="s">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="44"/>
-      <c r="F2" s="43" t="s">
+      <c r="E2" s="62"/>
+      <c r="F2" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="125">
+      <c r="G2" s="62"/>
+      <c r="H2" s="113">
         <v>46126</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="53"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="54"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="55"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="104" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="79" t="s">
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="96" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="80"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="87"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="60" t="s">
+      <c r="B6" s="44"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="61"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="47"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="60" t="s">
+      <c r="B7" s="44"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="61"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="47"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="60" t="s">
+      <c r="B8" s="44"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="61"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="47"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="74" t="s">
+      <c r="A9" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="109" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="57"/>
-      <c r="D9" s="81" t="s">
+      <c r="C9" s="45"/>
+      <c r="D9" s="97" t="s">
         <v>88</v>
       </c>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59"/>
-      <c r="J9" s="61"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="47"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="75"/>
-      <c r="B10" s="56" t="s">
+      <c r="A10" s="107"/>
+      <c r="B10" s="109" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="60" t="s">
+      <c r="C10" s="45"/>
+      <c r="D10" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="59"/>
-      <c r="J10" s="61"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="47"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="76"/>
-      <c r="B11" s="56" t="s">
+      <c r="A11" s="108"/>
+      <c r="B11" s="109" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="57"/>
-      <c r="D11" s="60" t="s">
+      <c r="C11" s="45"/>
+      <c r="D11" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="61"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="47"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="58" t="s">
+      <c r="A12" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="60" t="s">
+      <c r="B12" s="44"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
-      <c r="J12" s="61"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="47"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="98" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="63"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="77" t="s">
+      <c r="B13" s="94"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="78"/>
+      <c r="E13" s="94"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="95"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4554,6 +4548,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -4562,25 +4575,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4599,19 +4593,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="41" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="41" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="42"/>
+      <c r="G1" s="83"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -4623,48 +4617,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="43" t="s">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="44"/>
-      <c r="F2" s="43" t="s">
+      <c r="E2" s="62"/>
+      <c r="F2" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="49">
+      <c r="G2" s="62"/>
+      <c r="H2" s="73">
         <v>46120</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="75" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="53"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="54"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="55"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6019,19 +6013,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="41" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="41" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="42"/>
+      <c r="G1" s="83"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -6043,48 +6037,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="43" t="s">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="44"/>
-      <c r="F2" s="43" t="s">
+      <c r="E2" s="62"/>
+      <c r="F2" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="49">
+      <c r="G2" s="62"/>
+      <c r="H2" s="73">
         <v>46122</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="53"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="54"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="55"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7435,19 +7429,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="41" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="41" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="42"/>
+      <c r="G1" s="83"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -7459,190 +7453,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="43" t="s">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="44"/>
-      <c r="F2" s="43" t="s">
+      <c r="E2" s="62"/>
+      <c r="F2" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="49">
+      <c r="G2" s="62"/>
+      <c r="H2" s="73">
         <v>46122</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="53"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="54"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="68"/>
-      <c r="B4" s="69"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="54"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="105" t="s">
+      <c r="A5" s="81" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="106" t="s">
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="80"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="87"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="61"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="47"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="107"/>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="108"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="109"/>
+      <c r="A7" s="67"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="69"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="68"/>
-      <c r="B8" s="69"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="110"/>
+      <c r="A8" s="70"/>
+      <c r="B8" s="71"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="72"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="68"/>
-      <c r="B9" s="69"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="69"/>
-      <c r="J9" s="110"/>
+      <c r="A9" s="70"/>
+      <c r="B9" s="71"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="68"/>
-      <c r="B10" s="69"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="69"/>
-      <c r="J10" s="110"/>
+      <c r="A10" s="70"/>
+      <c r="B10" s="71"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="68"/>
-      <c r="B11" s="69"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="69"/>
-      <c r="J11" s="110"/>
+      <c r="A11" s="70"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="68"/>
-      <c r="B12" s="69"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="69"/>
-      <c r="J12" s="110"/>
+      <c r="A12" s="70"/>
+      <c r="B12" s="71"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="72"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="68"/>
-      <c r="B13" s="69"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="69"/>
-      <c r="J13" s="110"/>
+      <c r="A13" s="70"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="98" t="s">
+      <c r="A14" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="59"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="59"/>
-      <c r="J14" s="61"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="47"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="98" t="s">
+      <c r="A15" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="59"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="60" t="s">
+      <c r="B15" s="44"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="E15" s="59"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="57"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="45"/>
       <c r="I15" s="15" t="s">
         <v>27</v>
       </c>
@@ -7651,11 +7645,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="98" t="s">
+      <c r="A16" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="59"/>
-      <c r="C16" s="57"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="45"/>
       <c r="D16" s="15" t="s">
         <v>29</v>
       </c>
@@ -7668,18 +7662,18 @@
       <c r="G16" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="99" t="s">
+      <c r="H16" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="59"/>
-      <c r="J16" s="61"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="47"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="100" t="s">
+      <c r="A17" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="59"/>
-      <c r="C17" s="57"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="45"/>
       <c r="D17" s="17" t="s">
         <v>78</v>
       </c>
@@ -7690,63 +7684,63 @@
       <c r="G17" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H17" s="60" t="s">
+      <c r="H17" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="I17" s="59"/>
-      <c r="J17" s="61"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="47"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A18" s="96"/>
-      <c r="B18" s="94"/>
-      <c r="C18" s="97"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="50"/>
       <c r="D18" s="39"/>
       <c r="E18" s="39"/>
       <c r="F18" s="40"/>
       <c r="G18" s="40"/>
-      <c r="H18" s="93"/>
-      <c r="I18" s="94"/>
-      <c r="J18" s="95"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="52"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="101"/>
-      <c r="B19" s="102"/>
-      <c r="C19" s="102"/>
+      <c r="A19" s="85"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="66"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
-      <c r="H19" s="103"/>
-      <c r="I19" s="102"/>
-      <c r="J19" s="102"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="66"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="88" t="s">
+      <c r="A20" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="89"/>
-      <c r="D20" s="89"/>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="89"/>
-      <c r="J20" s="89"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="54"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="104" t="s">
+      <c r="A21" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="91"/>
-      <c r="C21" s="92"/>
-      <c r="D21" s="90" t="s">
+      <c r="B21" s="56"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="58" t="s">
         <v>92</v>
       </c>
-      <c r="E21" s="91"/>
-      <c r="F21" s="91"/>
-      <c r="G21" s="91"/>
-      <c r="H21" s="92"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="57"/>
       <c r="I21" s="37" t="s">
         <v>27</v>
       </c>
@@ -7755,11 +7749,11 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="98" t="s">
+      <c r="A22" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="59"/>
-      <c r="C22" s="57"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="45"/>
       <c r="D22" s="15" t="s">
         <v>29</v>
       </c>
@@ -7772,18 +7766,18 @@
       <c r="G22" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="99" t="s">
+      <c r="H22" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="59"/>
-      <c r="J22" s="61"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="47"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="100" t="s">
+      <c r="A23" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="59"/>
-      <c r="C23" s="57"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="45"/>
       <c r="D23" s="17" t="s">
         <v>81</v>
       </c>
@@ -7794,63 +7788,63 @@
       <c r="G23" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="H23" s="60" t="s">
+      <c r="H23" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="I23" s="59"/>
-      <c r="J23" s="61"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="47"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A24" s="96"/>
-      <c r="B24" s="94"/>
-      <c r="C24" s="97"/>
+      <c r="A24" s="48"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="50"/>
       <c r="D24" s="39"/>
       <c r="E24" s="39"/>
       <c r="F24" s="40"/>
       <c r="G24" s="40"/>
-      <c r="H24" s="93"/>
-      <c r="I24" s="94"/>
-      <c r="J24" s="95"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="52"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="101"/>
-      <c r="B25" s="102"/>
-      <c r="C25" s="102"/>
+      <c r="A25" s="85"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="66"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
-      <c r="H25" s="103"/>
-      <c r="I25" s="102"/>
-      <c r="J25" s="102"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="66"/>
+      <c r="J25" s="66"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="88" t="s">
+      <c r="A26" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="89"/>
-      <c r="C26" s="89"/>
-      <c r="D26" s="89"/>
-      <c r="E26" s="89"/>
-      <c r="F26" s="89"/>
-      <c r="G26" s="89"/>
-      <c r="H26" s="89"/>
-      <c r="I26" s="89"/>
-      <c r="J26" s="89"/>
+      <c r="B26" s="54"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="104" t="s">
+      <c r="A27" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="91"/>
-      <c r="C27" s="92"/>
-      <c r="D27" s="90" t="s">
+      <c r="B27" s="56"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="58" t="s">
         <v>94</v>
       </c>
-      <c r="E27" s="91"/>
-      <c r="F27" s="91"/>
-      <c r="G27" s="91"/>
-      <c r="H27" s="92"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="57"/>
       <c r="I27" s="37" t="s">
         <v>27</v>
       </c>
@@ -7859,11 +7853,11 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="98" t="s">
+      <c r="A28" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="59"/>
-      <c r="C28" s="57"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="45"/>
       <c r="D28" s="15" t="s">
         <v>29</v>
       </c>
@@ -7876,18 +7870,18 @@
       <c r="G28" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H28" s="99" t="s">
+      <c r="H28" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="I28" s="59"/>
-      <c r="J28" s="61"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="47"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="100" t="s">
+      <c r="A29" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="B29" s="59"/>
-      <c r="C29" s="57"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="45"/>
       <c r="D29" s="17" t="s">
         <v>95</v>
       </c>
@@ -7896,63 +7890,63 @@
       <c r="G29" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="H29" s="60" t="s">
+      <c r="H29" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="I29" s="59"/>
-      <c r="J29" s="61"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="47"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="96"/>
-      <c r="B30" s="94"/>
-      <c r="C30" s="97"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="50"/>
       <c r="D30" s="39"/>
       <c r="E30" s="39"/>
       <c r="F30" s="40"/>
       <c r="G30" s="40"/>
-      <c r="H30" s="93"/>
-      <c r="I30" s="94"/>
-      <c r="J30" s="95"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="49"/>
+      <c r="J30" s="52"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A31" s="121"/>
-      <c r="B31" s="122"/>
-      <c r="C31" s="122"/>
-      <c r="D31" s="121"/>
-      <c r="E31" s="121"/>
-      <c r="F31" s="123"/>
-      <c r="G31" s="123"/>
-      <c r="H31" s="124"/>
-      <c r="I31" s="122"/>
-      <c r="J31" s="122"/>
+      <c r="A31" s="3"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="41"/>
     </row>
     <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="88" t="s">
+      <c r="A32" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="89"/>
-      <c r="C32" s="89"/>
-      <c r="D32" s="89"/>
-      <c r="E32" s="89"/>
-      <c r="F32" s="89"/>
-      <c r="G32" s="89"/>
-      <c r="H32" s="89"/>
-      <c r="I32" s="89"/>
-      <c r="J32" s="89"/>
+      <c r="B32" s="54"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="54"/>
     </row>
     <row r="33" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A33" s="104" t="s">
+      <c r="A33" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="91"/>
-      <c r="C33" s="92"/>
-      <c r="D33" s="90" t="s">
+      <c r="B33" s="56"/>
+      <c r="C33" s="57"/>
+      <c r="D33" s="58" t="s">
         <v>93</v>
       </c>
-      <c r="E33" s="91"/>
-      <c r="F33" s="91"/>
-      <c r="G33" s="91"/>
-      <c r="H33" s="92"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="57"/>
       <c r="I33" s="37" t="s">
         <v>27</v>
       </c>
@@ -7961,11 +7955,11 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A34" s="98" t="s">
+      <c r="A34" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="59"/>
-      <c r="C34" s="57"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="45"/>
       <c r="D34" s="15" t="s">
         <v>29</v>
       </c>
@@ -7978,18 +7972,18 @@
       <c r="G34" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H34" s="99" t="s">
+      <c r="H34" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="I34" s="59"/>
-      <c r="J34" s="61"/>
+      <c r="I34" s="44"/>
+      <c r="J34" s="47"/>
     </row>
     <row r="35" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A35" s="100" t="s">
+      <c r="A35" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="B35" s="59"/>
-      <c r="C35" s="57"/>
+      <c r="B35" s="44"/>
+      <c r="C35" s="45"/>
       <c r="D35" s="17" t="s">
         <v>83</v>
       </c>
@@ -8000,23 +7994,23 @@
       <c r="G35" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="H35" s="60" t="s">
+      <c r="H35" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="I35" s="59"/>
-      <c r="J35" s="61"/>
+      <c r="I35" s="44"/>
+      <c r="J35" s="47"/>
     </row>
     <row r="36" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A36" s="96"/>
-      <c r="B36" s="94"/>
-      <c r="C36" s="97"/>
+      <c r="A36" s="48"/>
+      <c r="B36" s="49"/>
+      <c r="C36" s="50"/>
       <c r="D36" s="39"/>
       <c r="E36" s="39"/>
       <c r="F36" s="40"/>
       <c r="G36" s="40"/>
-      <c r="H36" s="93"/>
-      <c r="I36" s="94"/>
-      <c r="J36" s="95"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="49"/>
+      <c r="J36" s="52"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="38" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8982,29 +8976,19 @@
     <row r="998" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="F2:G4"/>
@@ -9021,19 +9005,29 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="D21:H21"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="H34:J34"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9053,182 +9047,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="100" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="41" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="41" t="s">
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="41" t="s">
+      <c r="L1" s="82"/>
+      <c r="M1" s="82"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="83"/>
+      <c r="Q1" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="42"/>
-      <c r="S1" s="41" t="s">
+      <c r="R1" s="83"/>
+      <c r="S1" s="84" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="80"/>
+      <c r="T1" s="87"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="108"/>
-      <c r="M2" s="108"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="44"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="109"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="69"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="69"/>
-      <c r="M3" s="69"/>
-      <c r="N3" s="46"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="46"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="46"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="110"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="63"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="72"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="115"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="102"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="103"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="103"/>
+      <c r="Q4" s="112"/>
+      <c r="R4" s="103"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="122"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="105" t="s">
+      <c r="A5" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="79" t="s">
+      <c r="B5" s="82"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="73"/>
-      <c r="L5" s="73"/>
-      <c r="M5" s="73"/>
-      <c r="N5" s="73"/>
-      <c r="O5" s="73"/>
-      <c r="P5" s="73"/>
-      <c r="Q5" s="73"/>
-      <c r="R5" s="73"/>
-      <c r="S5" s="73"/>
-      <c r="T5" s="80"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
+      <c r="L5" s="82"/>
+      <c r="M5" s="82"/>
+      <c r="N5" s="82"/>
+      <c r="O5" s="82"/>
+      <c r="P5" s="82"/>
+      <c r="Q5" s="82"/>
+      <c r="R5" s="82"/>
+      <c r="S5" s="82"/>
+      <c r="T5" s="87"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="60" t="s">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="59"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="59"/>
-      <c r="P6" s="59"/>
-      <c r="Q6" s="59"/>
-      <c r="R6" s="59"/>
-      <c r="S6" s="59"/>
-      <c r="T6" s="61"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="44"/>
+      <c r="R6" s="44"/>
+      <c r="S6" s="44"/>
+      <c r="T6" s="47"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="98" t="s">
+      <c r="A7" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="60" t="s">
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59"/>
-      <c r="K7" s="59"/>
-      <c r="L7" s="59"/>
-      <c r="M7" s="59"/>
-      <c r="N7" s="59"/>
-      <c r="O7" s="59"/>
-      <c r="P7" s="59"/>
-      <c r="Q7" s="59"/>
-      <c r="R7" s="59"/>
-      <c r="S7" s="59"/>
-      <c r="T7" s="61"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="44"/>
+      <c r="N7" s="44"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="44"/>
+      <c r="Q7" s="44"/>
+      <c r="R7" s="44"/>
+      <c r="S7" s="44"/>
+      <c r="T7" s="47"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9427,37 +9421,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="98" t="s">
+      <c r="A15" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="118" t="s">
+      <c r="B15" s="45"/>
+      <c r="C15" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="57"/>
-      <c r="E15" s="99" t="s">
+      <c r="D15" s="45"/>
+      <c r="E15" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="57"/>
-      <c r="G15" s="99" t="s">
+      <c r="F15" s="45"/>
+      <c r="G15" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="59"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="99" t="s">
+      <c r="H15" s="44"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="57"/>
-      <c r="L15" s="99" t="s">
+      <c r="K15" s="45"/>
+      <c r="L15" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="59"/>
-      <c r="N15" s="57"/>
-      <c r="O15" s="99" t="s">
+      <c r="M15" s="44"/>
+      <c r="N15" s="45"/>
+      <c r="O15" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="59"/>
-      <c r="Q15" s="57"/>
+      <c r="P15" s="44"/>
+      <c r="Q15" s="45"/>
       <c r="R15" s="15" t="s">
         <v>51</v>
       </c>
@@ -9469,37 +9463,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="116">
+      <c r="A16" s="114">
         <v>1</v>
       </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="117" t="s">
+      <c r="B16" s="45"/>
+      <c r="C16" s="115" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="57"/>
-      <c r="E16" s="117" t="s">
+      <c r="D16" s="45"/>
+      <c r="E16" s="115" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="57"/>
-      <c r="G16" s="111" t="s">
+      <c r="F16" s="45"/>
+      <c r="G16" s="120" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="59"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="111" t="s">
+      <c r="H16" s="44"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="120" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="57"/>
-      <c r="L16" s="113" t="s">
+      <c r="K16" s="45"/>
+      <c r="L16" s="118" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="59"/>
-      <c r="N16" s="57"/>
-      <c r="O16" s="113" t="s">
+      <c r="M16" s="44"/>
+      <c r="N16" s="45"/>
+      <c r="O16" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="59"/>
-      <c r="Q16" s="57"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="45"/>
       <c r="R16" s="31"/>
       <c r="S16" s="31"/>
       <c r="T16" s="32"/>
@@ -9511,37 +9505,37 @@
       <c r="Z16" s="33"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="116">
+      <c r="A17" s="114">
         <v>2</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="117" t="s">
+      <c r="B17" s="45"/>
+      <c r="C17" s="115" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="57"/>
-      <c r="E17" s="117" t="s">
+      <c r="D17" s="45"/>
+      <c r="E17" s="115" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="57"/>
-      <c r="G17" s="111" t="s">
+      <c r="F17" s="45"/>
+      <c r="G17" s="120" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="59"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="111" t="s">
+      <c r="H17" s="44"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="120" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="57"/>
-      <c r="L17" s="113" t="s">
+      <c r="K17" s="45"/>
+      <c r="L17" s="118" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="59"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="113" t="s">
+      <c r="M17" s="44"/>
+      <c r="N17" s="45"/>
+      <c r="O17" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="P17" s="59"/>
-      <c r="Q17" s="57"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="45"/>
       <c r="R17" s="31"/>
       <c r="S17" s="31"/>
       <c r="T17" s="32"/>
@@ -9553,23 +9547,23 @@
       <c r="Z17" s="33"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="116"/>
-      <c r="B18" s="57"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="117"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="111"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="111"/>
-      <c r="K18" s="57"/>
-      <c r="L18" s="113"/>
-      <c r="M18" s="59"/>
-      <c r="N18" s="57"/>
-      <c r="O18" s="113"/>
-      <c r="P18" s="59"/>
-      <c r="Q18" s="57"/>
+      <c r="A18" s="114"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="115"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="115"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="120"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="120"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="118"/>
+      <c r="M18" s="44"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="44"/>
+      <c r="Q18" s="45"/>
       <c r="R18" s="31"/>
       <c r="S18" s="31"/>
       <c r="T18" s="32"/>
@@ -9581,23 +9575,23 @@
       <c r="Z18" s="33"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="116"/>
-      <c r="B19" s="57"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="117"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="111"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="113"/>
-      <c r="M19" s="59"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="113"/>
-      <c r="P19" s="59"/>
-      <c r="Q19" s="57"/>
+      <c r="A19" s="114"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="115"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="115"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="120"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="120"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="118"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="45"/>
+      <c r="O19" s="118"/>
+      <c r="P19" s="44"/>
+      <c r="Q19" s="45"/>
       <c r="R19" s="31"/>
       <c r="S19" s="31"/>
       <c r="T19" s="32"/>
@@ -9609,23 +9603,23 @@
       <c r="Z19" s="33"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="116"/>
-      <c r="B20" s="57"/>
-      <c r="C20" s="117"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="117"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="111"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="113"/>
-      <c r="M20" s="59"/>
-      <c r="N20" s="57"/>
-      <c r="O20" s="113"/>
-      <c r="P20" s="59"/>
-      <c r="Q20" s="57"/>
+      <c r="A20" s="114"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="115"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="115"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="120"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="118"/>
+      <c r="M20" s="44"/>
+      <c r="N20" s="45"/>
+      <c r="O20" s="118"/>
+      <c r="P20" s="44"/>
+      <c r="Q20" s="45"/>
       <c r="R20" s="31"/>
       <c r="S20" s="31"/>
       <c r="T20" s="32"/>
@@ -9637,23 +9631,23 @@
       <c r="Z20" s="33"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="116"/>
-      <c r="B21" s="57"/>
-      <c r="C21" s="117"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="117"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="111"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="113"/>
-      <c r="M21" s="59"/>
-      <c r="N21" s="57"/>
-      <c r="O21" s="113"/>
-      <c r="P21" s="59"/>
-      <c r="Q21" s="57"/>
+      <c r="A21" s="114"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="115"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="115"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="120"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="120"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="118"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="45"/>
+      <c r="O21" s="118"/>
+      <c r="P21" s="44"/>
+      <c r="Q21" s="45"/>
       <c r="R21" s="31"/>
       <c r="S21" s="31"/>
       <c r="T21" s="32"/>
@@ -9665,23 +9659,23 @@
       <c r="Z21" s="33"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="116"/>
-      <c r="B22" s="57"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="117"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="111"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="111"/>
-      <c r="K22" s="57"/>
-      <c r="L22" s="113"/>
-      <c r="M22" s="59"/>
-      <c r="N22" s="57"/>
-      <c r="O22" s="113"/>
-      <c r="P22" s="59"/>
-      <c r="Q22" s="57"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="115"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="115"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="120"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="120"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="118"/>
+      <c r="M22" s="44"/>
+      <c r="N22" s="45"/>
+      <c r="O22" s="118"/>
+      <c r="P22" s="44"/>
+      <c r="Q22" s="45"/>
       <c r="R22" s="31"/>
       <c r="S22" s="31"/>
       <c r="T22" s="32"/>
@@ -9693,23 +9687,23 @@
       <c r="Z22" s="33"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="116"/>
-      <c r="B23" s="57"/>
-      <c r="C23" s="117"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="117"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="111"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="111"/>
-      <c r="K23" s="57"/>
-      <c r="L23" s="113"/>
-      <c r="M23" s="59"/>
-      <c r="N23" s="57"/>
-      <c r="O23" s="113"/>
-      <c r="P23" s="59"/>
-      <c r="Q23" s="57"/>
+      <c r="A23" s="114"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="115"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="115"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="120"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="120"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="118"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="118"/>
+      <c r="P23" s="44"/>
+      <c r="Q23" s="45"/>
       <c r="R23" s="31"/>
       <c r="S23" s="31"/>
       <c r="T23" s="32"/>
@@ -9721,23 +9715,23 @@
       <c r="Z23" s="33"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="116"/>
-      <c r="B24" s="57"/>
-      <c r="C24" s="117"/>
-      <c r="D24" s="57"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="111"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="111"/>
-      <c r="K24" s="57"/>
-      <c r="L24" s="113"/>
-      <c r="M24" s="59"/>
-      <c r="N24" s="57"/>
-      <c r="O24" s="113"/>
-      <c r="P24" s="59"/>
-      <c r="Q24" s="57"/>
+      <c r="A24" s="114"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="115"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="115"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="120"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="120"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="118"/>
+      <c r="M24" s="44"/>
+      <c r="N24" s="45"/>
+      <c r="O24" s="118"/>
+      <c r="P24" s="44"/>
+      <c r="Q24" s="45"/>
       <c r="R24" s="31"/>
       <c r="S24" s="31"/>
       <c r="T24" s="32"/>
@@ -9749,23 +9743,23 @@
       <c r="Z24" s="33"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="116"/>
-      <c r="B25" s="57"/>
-      <c r="C25" s="117"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="117"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="111"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="111"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="113"/>
-      <c r="M25" s="59"/>
-      <c r="N25" s="57"/>
-      <c r="O25" s="113"/>
-      <c r="P25" s="59"/>
-      <c r="Q25" s="57"/>
+      <c r="A25" s="114"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="115"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="115"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="120"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="120"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="118"/>
+      <c r="M25" s="44"/>
+      <c r="N25" s="45"/>
+      <c r="O25" s="118"/>
+      <c r="P25" s="44"/>
+      <c r="Q25" s="45"/>
       <c r="R25" s="31"/>
       <c r="S25" s="31"/>
       <c r="T25" s="32"/>
@@ -9777,23 +9771,23 @@
       <c r="Z25" s="33"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="116"/>
-      <c r="B26" s="57"/>
-      <c r="C26" s="117"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="117"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="111"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="111"/>
-      <c r="K26" s="57"/>
-      <c r="L26" s="113"/>
-      <c r="M26" s="59"/>
-      <c r="N26" s="57"/>
-      <c r="O26" s="113"/>
-      <c r="P26" s="59"/>
-      <c r="Q26" s="57"/>
+      <c r="A26" s="114"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="115"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="115"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="120"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="120"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="118"/>
+      <c r="M26" s="44"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="118"/>
+      <c r="P26" s="44"/>
+      <c r="Q26" s="45"/>
       <c r="R26" s="31"/>
       <c r="S26" s="31"/>
       <c r="T26" s="32"/>
@@ -9805,23 +9799,23 @@
       <c r="Z26" s="33"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="116"/>
-      <c r="B27" s="57"/>
-      <c r="C27" s="117"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="117"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="111"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="111"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="113"/>
-      <c r="M27" s="59"/>
-      <c r="N27" s="57"/>
-      <c r="O27" s="113"/>
-      <c r="P27" s="59"/>
-      <c r="Q27" s="57"/>
+      <c r="A27" s="114"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="115"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="120"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="120"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="118"/>
+      <c r="M27" s="44"/>
+      <c r="N27" s="45"/>
+      <c r="O27" s="118"/>
+      <c r="P27" s="44"/>
+      <c r="Q27" s="45"/>
       <c r="R27" s="31"/>
       <c r="S27" s="31"/>
       <c r="T27" s="32"/>
@@ -9833,23 +9827,23 @@
       <c r="Z27" s="33"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="116"/>
-      <c r="B28" s="57"/>
-      <c r="C28" s="117"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="117"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="111"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="111"/>
-      <c r="K28" s="57"/>
-      <c r="L28" s="113"/>
-      <c r="M28" s="59"/>
-      <c r="N28" s="57"/>
-      <c r="O28" s="113"/>
-      <c r="P28" s="59"/>
-      <c r="Q28" s="57"/>
+      <c r="A28" s="114"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="115"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="115"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="120"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="118"/>
+      <c r="M28" s="44"/>
+      <c r="N28" s="45"/>
+      <c r="O28" s="118"/>
+      <c r="P28" s="44"/>
+      <c r="Q28" s="45"/>
       <c r="R28" s="31"/>
       <c r="S28" s="31"/>
       <c r="T28" s="32"/>
@@ -9861,23 +9855,23 @@
       <c r="Z28" s="33"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="116"/>
-      <c r="B29" s="57"/>
-      <c r="C29" s="117"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="117"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="111"/>
-      <c r="H29" s="59"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="111"/>
-      <c r="K29" s="57"/>
-      <c r="L29" s="113"/>
-      <c r="M29" s="59"/>
-      <c r="N29" s="57"/>
-      <c r="O29" s="113"/>
-      <c r="P29" s="59"/>
-      <c r="Q29" s="57"/>
+      <c r="A29" s="114"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="115"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="115"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="120"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="120"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="118"/>
+      <c r="M29" s="44"/>
+      <c r="N29" s="45"/>
+      <c r="O29" s="118"/>
+      <c r="P29" s="44"/>
+      <c r="Q29" s="45"/>
       <c r="R29" s="31"/>
       <c r="S29" s="31"/>
       <c r="T29" s="32"/>
@@ -9889,23 +9883,23 @@
       <c r="Z29" s="33"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="116"/>
-      <c r="B30" s="57"/>
-      <c r="C30" s="117"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="117"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="111"/>
-      <c r="H30" s="59"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="111"/>
-      <c r="K30" s="57"/>
-      <c r="L30" s="113"/>
-      <c r="M30" s="59"/>
-      <c r="N30" s="57"/>
-      <c r="O30" s="113"/>
-      <c r="P30" s="59"/>
-      <c r="Q30" s="57"/>
+      <c r="A30" s="114"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="115"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="115"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="120"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="120"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="118"/>
+      <c r="M30" s="44"/>
+      <c r="N30" s="45"/>
+      <c r="O30" s="118"/>
+      <c r="P30" s="44"/>
+      <c r="Q30" s="45"/>
       <c r="R30" s="31"/>
       <c r="S30" s="31"/>
       <c r="T30" s="32"/>
@@ -9917,23 +9911,23 @@
       <c r="Z30" s="33"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="119"/>
-      <c r="B31" s="64"/>
-      <c r="C31" s="120"/>
-      <c r="D31" s="64"/>
-      <c r="E31" s="120"/>
-      <c r="F31" s="64"/>
-      <c r="G31" s="112"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="64"/>
-      <c r="J31" s="112"/>
-      <c r="K31" s="64"/>
-      <c r="L31" s="114"/>
-      <c r="M31" s="63"/>
-      <c r="N31" s="64"/>
-      <c r="O31" s="114"/>
-      <c r="P31" s="63"/>
-      <c r="Q31" s="64"/>
+      <c r="A31" s="116"/>
+      <c r="B31" s="99"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="99"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="99"/>
+      <c r="G31" s="123"/>
+      <c r="H31" s="94"/>
+      <c r="I31" s="99"/>
+      <c r="J31" s="123"/>
+      <c r="K31" s="99"/>
+      <c r="L31" s="119"/>
+      <c r="M31" s="94"/>
+      <c r="N31" s="99"/>
+      <c r="O31" s="119"/>
+      <c r="P31" s="94"/>
+      <c r="Q31" s="99"/>
       <c r="R31" s="34"/>
       <c r="S31" s="34"/>
       <c r="T31" s="35"/>
@@ -10931,6 +10925,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -10955,118 +11061,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_タスク詳細画面.xlsx
+++ b/document/成果物ドキュメント_タスク詳細画面.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-14\Documents\project\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DCD7AA-3473-4C98-AF06-FC959821DC35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7AA67B-0DDE-42BD-A5CD-1E9B634DF8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="100">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -476,6 +476,10 @@
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>④</t>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -1526,60 +1530,69 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1592,10 +1605,52 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1607,60 +1662,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1676,12 +1680,60 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1691,53 +1743,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1745,29 +1764,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1923,49 +1927,60 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
+      <xdr:colOff>470648</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
+      <xdr:rowOff>246529</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1104900</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>865233</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>39874</xdr:rowOff>
+      <xdr:rowOff>22412</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BD3D15D-1DAF-FC67-0158-D8F05738753E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{300B68EB-0754-B839-CC01-B4ED5BACBD30}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
+        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2628900" y="1476375"/>
-          <a:ext cx="2847975" cy="1954399"/>
+          <a:off x="2622177" y="1501588"/>
+          <a:ext cx="3722732" cy="2958353"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2198,67 +2213,67 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
-      <c r="L3" s="71"/>
-      <c r="M3" s="71"/>
-      <c r="N3" s="71"/>
-      <c r="O3" s="71"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="77"/>
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="71"/>
-      <c r="O4" s="71"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="77"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="71"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="77"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="71"/>
-      <c r="L6" s="71"/>
-      <c r="M6" s="71"/>
-      <c r="N6" s="71"/>
-      <c r="O6" s="71"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="77"/>
+      <c r="N6" s="77"/>
+      <c r="O6" s="77"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2281,14 +2296,14 @@
       <c r="E8" s="92" t="s">
         <v>85</v>
       </c>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="71"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="71"/>
-      <c r="M8" s="71"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="77"/>
+      <c r="K8" s="77"/>
+      <c r="L8" s="77"/>
+      <c r="M8" s="77"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
@@ -2298,26 +2313,26 @@
       <c r="G13" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="45"/>
+      <c r="H13" s="55"/>
       <c r="I13" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="44"/>
-      <c r="K13" s="45"/>
+      <c r="J13" s="54"/>
+      <c r="K13" s="55"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="88"/>
-      <c r="H14" s="45"/>
+      <c r="H14" s="55"/>
       <c r="I14" s="88"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="45"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="55"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="88"/>
-      <c r="H15" s="45"/>
+      <c r="H15" s="55"/>
       <c r="I15" s="88"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="45"/>
+      <c r="J15" s="54"/>
+      <c r="K15" s="55"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2329,10 +2344,10 @@
       <c r="G17" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="71"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="71"/>
+      <c r="H17" s="77"/>
+      <c r="I17" s="77"/>
+      <c r="J17" s="77"/>
+      <c r="K17" s="77"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3346,19 +3361,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="84" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84" t="s">
+      <c r="E1" s="80"/>
+      <c r="F1" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="83"/>
+      <c r="G1" s="80"/>
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
@@ -3370,194 +3385,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="61" t="s">
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="61" t="s">
+      <c r="E2" s="65"/>
+      <c r="F2" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="62"/>
-      <c r="H2" s="113">
+      <c r="G2" s="65"/>
+      <c r="H2" s="95">
         <v>46126</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="71"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="70"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="72"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
+      <c r="A4" s="104"/>
+      <c r="B4" s="105"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="97"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="104" t="s">
+      <c r="A5" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="96" t="s">
+      <c r="B5" s="79"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="112" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="87"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="83"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="105" t="s">
+      <c r="A6" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="46" t="s">
+      <c r="B6" s="54"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="59" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="47"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="57"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="105" t="s">
+      <c r="A7" s="99" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="46" t="s">
+      <c r="B7" s="54"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="59" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="47"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="57"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="105" t="s">
+      <c r="A8" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="46" t="s">
+      <c r="B8" s="54"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="59" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="47"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="57"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="106" t="s">
+      <c r="A9" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="109" t="s">
+      <c r="B9" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="97" t="s">
+      <c r="C9" s="55"/>
+      <c r="D9" s="113" t="s">
         <v>88</v>
       </c>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="47"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="57"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="107"/>
-      <c r="B10" s="109" t="s">
+      <c r="A10" s="108"/>
+      <c r="B10" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="46" t="s">
+      <c r="C10" s="55"/>
+      <c r="D10" s="59" t="s">
         <v>86</v>
       </c>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="47"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="57"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="108"/>
-      <c r="B11" s="109" t="s">
+      <c r="A11" s="109"/>
+      <c r="B11" s="98" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="46" t="s">
+      <c r="C11" s="55"/>
+      <c r="D11" s="59" t="s">
         <v>86</v>
       </c>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="47"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="57"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="105" t="s">
+      <c r="A12" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="44"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="46" t="s">
+      <c r="B12" s="54"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="59" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="47"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="57"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="98" t="s">
+      <c r="A13" s="100" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="94"/>
-      <c r="C13" s="99"/>
-      <c r="D13" s="93" t="s">
+      <c r="B13" s="101"/>
+      <c r="C13" s="102"/>
+      <c r="D13" s="110" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="95"/>
+      <c r="E13" s="101"/>
+      <c r="F13" s="101"/>
+      <c r="G13" s="101"/>
+      <c r="H13" s="101"/>
+      <c r="I13" s="101"/>
+      <c r="J13" s="111"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4548,17 +4563,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4567,14 +4579,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4593,19 +4608,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="84" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84" t="s">
+      <c r="E1" s="80"/>
+      <c r="F1" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="83"/>
+      <c r="G1" s="80"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -4617,48 +4632,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="61" t="s">
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="61" t="s">
+      <c r="E2" s="65"/>
+      <c r="F2" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="62"/>
-      <c r="H2" s="73">
+      <c r="G2" s="65"/>
+      <c r="H2" s="68">
         <v>46120</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="71"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="70"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="72"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
+      <c r="A4" s="104"/>
+      <c r="B4" s="105"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="97"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6013,19 +6028,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="84" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84" t="s">
+      <c r="E1" s="80"/>
+      <c r="F1" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="83"/>
+      <c r="G1" s="80"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -6037,48 +6052,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="61" t="s">
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="61" t="s">
+      <c r="E2" s="65"/>
+      <c r="F2" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="62"/>
-      <c r="H2" s="73">
+      <c r="G2" s="65"/>
+      <c r="H2" s="68">
         <v>46122</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="71"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="70"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="72"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
+      <c r="A4" s="104"/>
+      <c r="B4" s="105"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="97"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7429,19 +7444,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="84" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84" t="s">
+      <c r="E1" s="80"/>
+      <c r="F1" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="83"/>
+      <c r="G1" s="80"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -7453,190 +7468,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="61" t="s">
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="61" t="s">
+      <c r="E2" s="65"/>
+      <c r="F2" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="62"/>
-      <c r="H2" s="73">
+      <c r="G2" s="65"/>
+      <c r="H2" s="68">
         <v>46122</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="71"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="70"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="72"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="72"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="86" t="s">
+      <c r="B5" s="79"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="82" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="87"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="83"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="47"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="57"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="67"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="69"/>
+      <c r="A7" s="84"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="85"/>
+      <c r="J7" s="86"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="70"/>
-      <c r="B8" s="71"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="72"/>
+      <c r="A8" s="76"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="87"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="70"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="72"/>
+      <c r="A9" s="76"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="87"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="70"/>
-      <c r="B10" s="71"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="72"/>
+      <c r="A10" s="76"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="87"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="70"/>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="72"/>
+      <c r="A11" s="76"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="87"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="70"/>
-      <c r="B12" s="71"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="71"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="72"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="70"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="72"/>
+      <c r="A12" s="76"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="87"/>
+    </row>
+    <row r="13" spans="1:10" ht="102" customHeight="1">
+      <c r="A13" s="76"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="87"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="59" t="s">
+      <c r="A14" s="53" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="47"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="57"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="59" t="s">
+      <c r="A15" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="44"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="46" t="s">
+      <c r="B15" s="54"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="45"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="55"/>
       <c r="I15" s="15" t="s">
         <v>27</v>
       </c>
@@ -7645,11 +7660,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="45"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="55"/>
       <c r="D16" s="15" t="s">
         <v>29</v>
       </c>
@@ -7662,18 +7677,18 @@
       <c r="G16" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="60" t="s">
+      <c r="H16" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="44"/>
-      <c r="J16" s="47"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="57"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="43" t="s">
+      <c r="A17" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="45"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="55"/>
       <c r="D17" s="17" t="s">
         <v>78</v>
       </c>
@@ -7684,63 +7699,63 @@
       <c r="G17" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H17" s="46" t="s">
+      <c r="H17" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="I17" s="44"/>
-      <c r="J17" s="47"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="57"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A18" s="48"/>
+      <c r="A18" s="51"/>
       <c r="B18" s="49"/>
-      <c r="C18" s="50"/>
+      <c r="C18" s="52"/>
       <c r="D18" s="39"/>
       <c r="E18" s="39"/>
       <c r="F18" s="40"/>
       <c r="G18" s="40"/>
-      <c r="H18" s="51"/>
+      <c r="H18" s="48"/>
       <c r="I18" s="49"/>
-      <c r="J18" s="52"/>
+      <c r="J18" s="50"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="85"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="66"/>
+      <c r="A19" s="60"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="61"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
-      <c r="H19" s="65"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="66"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="61"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="53" t="s">
+      <c r="A20" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="54"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="55" t="s">
+      <c r="A21" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="56"/>
-      <c r="C21" s="57"/>
-      <c r="D21" s="58" t="s">
+      <c r="B21" s="46"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="57"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="47"/>
       <c r="I21" s="37" t="s">
         <v>27</v>
       </c>
@@ -7749,11 +7764,11 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="44"/>
-      <c r="C22" s="45"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="55"/>
       <c r="D22" s="15" t="s">
         <v>29</v>
       </c>
@@ -7766,18 +7781,18 @@
       <c r="G22" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="60" t="s">
+      <c r="H22" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="44"/>
-      <c r="J22" s="47"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="57"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="43" t="s">
+      <c r="A23" s="58" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="44"/>
-      <c r="C23" s="45"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="55"/>
       <c r="D23" s="17" t="s">
         <v>81</v>
       </c>
@@ -7788,63 +7803,63 @@
       <c r="G23" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="H23" s="46" t="s">
+      <c r="H23" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="I23" s="44"/>
-      <c r="J23" s="47"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="57"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A24" s="48"/>
+      <c r="A24" s="51"/>
       <c r="B24" s="49"/>
-      <c r="C24" s="50"/>
+      <c r="C24" s="52"/>
       <c r="D24" s="39"/>
       <c r="E24" s="39"/>
       <c r="F24" s="40"/>
       <c r="G24" s="40"/>
-      <c r="H24" s="51"/>
+      <c r="H24" s="48"/>
       <c r="I24" s="49"/>
-      <c r="J24" s="52"/>
+      <c r="J24" s="50"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="85"/>
-      <c r="B25" s="66"/>
-      <c r="C25" s="66"/>
+      <c r="A25" s="60"/>
+      <c r="B25" s="61"/>
+      <c r="C25" s="61"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
-      <c r="H25" s="65"/>
-      <c r="I25" s="66"/>
-      <c r="J25" s="66"/>
+      <c r="H25" s="62"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="61"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="53" t="s">
+      <c r="A26" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="54"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="54"/>
-      <c r="J26" s="54"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="44"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="55" t="s">
+      <c r="A27" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="56"/>
-      <c r="C27" s="57"/>
-      <c r="D27" s="58" t="s">
+      <c r="B27" s="46"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="E27" s="56"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="57"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="47"/>
       <c r="I27" s="37" t="s">
         <v>27</v>
       </c>
@@ -7853,11 +7868,11 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="59" t="s">
+      <c r="A28" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="44"/>
-      <c r="C28" s="45"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="55"/>
       <c r="D28" s="15" t="s">
         <v>29</v>
       </c>
@@ -7870,18 +7885,18 @@
       <c r="G28" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H28" s="60" t="s">
+      <c r="H28" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="I28" s="44"/>
-      <c r="J28" s="47"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="57"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="43" t="s">
+      <c r="A29" s="58" t="s">
         <v>82</v>
       </c>
-      <c r="B29" s="44"/>
-      <c r="C29" s="45"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="55"/>
       <c r="D29" s="17" t="s">
         <v>95</v>
       </c>
@@ -7890,23 +7905,23 @@
       <c r="G29" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="H29" s="46" t="s">
+      <c r="H29" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="I29" s="44"/>
-      <c r="J29" s="47"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="57"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="48"/>
+      <c r="A30" s="51"/>
       <c r="B30" s="49"/>
-      <c r="C30" s="50"/>
+      <c r="C30" s="52"/>
       <c r="D30" s="39"/>
       <c r="E30" s="39"/>
       <c r="F30" s="40"/>
       <c r="G30" s="40"/>
-      <c r="H30" s="51"/>
+      <c r="H30" s="48"/>
       <c r="I30" s="49"/>
-      <c r="J30" s="52"/>
+      <c r="J30" s="50"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1">
       <c r="A31" s="3"/>
@@ -7921,32 +7936,32 @@
       <c r="J31" s="41"/>
     </row>
     <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="53" t="s">
+      <c r="A32" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="54"/>
-      <c r="C32" s="54"/>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="54"/>
-      <c r="J32" s="54"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="44"/>
     </row>
     <row r="33" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A33" s="55" t="s">
+      <c r="A33" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="56"/>
-      <c r="C33" s="57"/>
-      <c r="D33" s="58" t="s">
+      <c r="B33" s="46"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="E33" s="56"/>
-      <c r="F33" s="56"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="57"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="47"/>
       <c r="I33" s="37" t="s">
         <v>27</v>
       </c>
@@ -7955,11 +7970,11 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A34" s="59" t="s">
+      <c r="A34" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="44"/>
-      <c r="C34" s="45"/>
+      <c r="B34" s="54"/>
+      <c r="C34" s="55"/>
       <c r="D34" s="15" t="s">
         <v>29</v>
       </c>
@@ -7972,18 +7987,18 @@
       <c r="G34" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H34" s="60" t="s">
+      <c r="H34" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="I34" s="44"/>
-      <c r="J34" s="47"/>
+      <c r="I34" s="54"/>
+      <c r="J34" s="57"/>
     </row>
     <row r="35" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A35" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="B35" s="44"/>
-      <c r="C35" s="45"/>
+      <c r="A35" s="58" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" s="54"/>
+      <c r="C35" s="55"/>
       <c r="D35" s="17" t="s">
         <v>83</v>
       </c>
@@ -7994,23 +8009,23 @@
       <c r="G35" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="H35" s="46" t="s">
+      <c r="H35" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="I35" s="44"/>
-      <c r="J35" s="47"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="57"/>
     </row>
     <row r="36" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A36" s="48"/>
+      <c r="A36" s="51"/>
       <c r="B36" s="49"/>
-      <c r="C36" s="50"/>
+      <c r="C36" s="52"/>
       <c r="D36" s="39"/>
       <c r="E36" s="39"/>
       <c r="F36" s="40"/>
       <c r="G36" s="40"/>
-      <c r="H36" s="51"/>
+      <c r="H36" s="48"/>
       <c r="I36" s="49"/>
-      <c r="J36" s="52"/>
+      <c r="J36" s="50"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="38" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8976,19 +8991,29 @@
     <row r="998" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="F2:G4"/>
@@ -9005,29 +9030,19 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="D21:H21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A27:C27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9047,182 +9062,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="84" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="84" t="s">
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="84" t="s">
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="80"/>
+      <c r="O1" s="81" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="84" t="s">
+      <c r="P1" s="80"/>
+      <c r="Q1" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="83"/>
-      <c r="S1" s="84" t="s">
+      <c r="R1" s="80"/>
+      <c r="S1" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="87"/>
+      <c r="T1" s="83"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="69"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="64"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="64"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="64"/>
+      <c r="T2" s="86"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="70"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="71"/>
-      <c r="M3" s="71"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="72"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="77"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="67"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="67"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="87"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="103"/>
-      <c r="K4" s="112"/>
-      <c r="L4" s="102"/>
-      <c r="M4" s="102"/>
-      <c r="N4" s="103"/>
-      <c r="O4" s="112"/>
-      <c r="P4" s="103"/>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="103"/>
-      <c r="S4" s="112"/>
-      <c r="T4" s="122"/>
+      <c r="A4" s="104"/>
+      <c r="B4" s="105"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="105"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="105"/>
+      <c r="M4" s="105"/>
+      <c r="N4" s="94"/>
+      <c r="O4" s="93"/>
+      <c r="P4" s="94"/>
+      <c r="Q4" s="93"/>
+      <c r="R4" s="94"/>
+      <c r="S4" s="93"/>
+      <c r="T4" s="118"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="96" t="s">
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="82"/>
-      <c r="K5" s="82"/>
-      <c r="L5" s="82"/>
-      <c r="M5" s="82"/>
-      <c r="N5" s="82"/>
-      <c r="O5" s="82"/>
-      <c r="P5" s="82"/>
-      <c r="Q5" s="82"/>
-      <c r="R5" s="82"/>
-      <c r="S5" s="82"/>
-      <c r="T5" s="87"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
+      <c r="K5" s="79"/>
+      <c r="L5" s="79"/>
+      <c r="M5" s="79"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="83"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="46" t="s">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="44"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="47"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="54"/>
+      <c r="O6" s="54"/>
+      <c r="P6" s="54"/>
+      <c r="Q6" s="54"/>
+      <c r="R6" s="54"/>
+      <c r="S6" s="54"/>
+      <c r="T6" s="57"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="46" t="s">
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="59" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="44"/>
-      <c r="S7" s="44"/>
-      <c r="T7" s="47"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="54"/>
+      <c r="N7" s="54"/>
+      <c r="O7" s="54"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="54"/>
+      <c r="T7" s="57"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9421,37 +9436,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="59" t="s">
+      <c r="A15" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="45"/>
+      <c r="B15" s="55"/>
       <c r="C15" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="45"/>
-      <c r="E15" s="60" t="s">
+      <c r="D15" s="55"/>
+      <c r="E15" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="45"/>
-      <c r="G15" s="60" t="s">
+      <c r="F15" s="55"/>
+      <c r="G15" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="44"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="60" t="s">
+      <c r="H15" s="54"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="45"/>
-      <c r="L15" s="60" t="s">
+      <c r="K15" s="55"/>
+      <c r="L15" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="44"/>
-      <c r="N15" s="45"/>
-      <c r="O15" s="60" t="s">
+      <c r="M15" s="54"/>
+      <c r="N15" s="55"/>
+      <c r="O15" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="44"/>
-      <c r="Q15" s="45"/>
+      <c r="P15" s="54"/>
+      <c r="Q15" s="55"/>
       <c r="R15" s="15" t="s">
         <v>51</v>
       </c>
@@ -9463,37 +9478,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="114">
+      <c r="A16" s="119">
         <v>1</v>
       </c>
-      <c r="B16" s="45"/>
-      <c r="C16" s="115" t="s">
+      <c r="B16" s="55"/>
+      <c r="C16" s="120" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="45"/>
-      <c r="E16" s="115" t="s">
+      <c r="D16" s="55"/>
+      <c r="E16" s="120" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="45"/>
-      <c r="G16" s="120" t="s">
+      <c r="F16" s="55"/>
+      <c r="G16" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="44"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="120" t="s">
+      <c r="H16" s="54"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="114" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="45"/>
-      <c r="L16" s="118" t="s">
+      <c r="K16" s="55"/>
+      <c r="L16" s="116" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="44"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="118" t="s">
+      <c r="M16" s="54"/>
+      <c r="N16" s="55"/>
+      <c r="O16" s="116" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="44"/>
-      <c r="Q16" s="45"/>
+      <c r="P16" s="54"/>
+      <c r="Q16" s="55"/>
       <c r="R16" s="31"/>
       <c r="S16" s="31"/>
       <c r="T16" s="32"/>
@@ -9505,37 +9520,37 @@
       <c r="Z16" s="33"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="114">
+      <c r="A17" s="119">
         <v>2</v>
       </c>
-      <c r="B17" s="45"/>
-      <c r="C17" s="115" t="s">
+      <c r="B17" s="55"/>
+      <c r="C17" s="120" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="45"/>
-      <c r="E17" s="115" t="s">
+      <c r="D17" s="55"/>
+      <c r="E17" s="120" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="45"/>
-      <c r="G17" s="120" t="s">
+      <c r="F17" s="55"/>
+      <c r="G17" s="114" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="44"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="120" t="s">
+      <c r="H17" s="54"/>
+      <c r="I17" s="55"/>
+      <c r="J17" s="114" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="45"/>
-      <c r="L17" s="118" t="s">
+      <c r="K17" s="55"/>
+      <c r="L17" s="116" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="44"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="118" t="s">
+      <c r="M17" s="54"/>
+      <c r="N17" s="55"/>
+      <c r="O17" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="P17" s="44"/>
-      <c r="Q17" s="45"/>
+      <c r="P17" s="54"/>
+      <c r="Q17" s="55"/>
       <c r="R17" s="31"/>
       <c r="S17" s="31"/>
       <c r="T17" s="32"/>
@@ -9547,23 +9562,23 @@
       <c r="Z17" s="33"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="114"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="115"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="115"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="120"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="120"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="44"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="44"/>
-      <c r="Q18" s="45"/>
+      <c r="A18" s="119"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="120"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="120"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="114"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="55"/>
+      <c r="J18" s="114"/>
+      <c r="K18" s="55"/>
+      <c r="L18" s="116"/>
+      <c r="M18" s="54"/>
+      <c r="N18" s="55"/>
+      <c r="O18" s="116"/>
+      <c r="P18" s="54"/>
+      <c r="Q18" s="55"/>
       <c r="R18" s="31"/>
       <c r="S18" s="31"/>
       <c r="T18" s="32"/>
@@ -9575,23 +9590,23 @@
       <c r="Z18" s="33"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="114"/>
-      <c r="B19" s="45"/>
-      <c r="C19" s="115"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="115"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="120"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="120"/>
-      <c r="K19" s="45"/>
-      <c r="L19" s="118"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="45"/>
-      <c r="O19" s="118"/>
-      <c r="P19" s="44"/>
-      <c r="Q19" s="45"/>
+      <c r="A19" s="119"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="120"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="114"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="114"/>
+      <c r="K19" s="55"/>
+      <c r="L19" s="116"/>
+      <c r="M19" s="54"/>
+      <c r="N19" s="55"/>
+      <c r="O19" s="116"/>
+      <c r="P19" s="54"/>
+      <c r="Q19" s="55"/>
       <c r="R19" s="31"/>
       <c r="S19" s="31"/>
       <c r="T19" s="32"/>
@@ -9603,23 +9618,23 @@
       <c r="Z19" s="33"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="114"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="115"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="115"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="120"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="120"/>
-      <c r="K20" s="45"/>
-      <c r="L20" s="118"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="45"/>
-      <c r="O20" s="118"/>
-      <c r="P20" s="44"/>
-      <c r="Q20" s="45"/>
+      <c r="A20" s="119"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="120"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="114"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="114"/>
+      <c r="K20" s="55"/>
+      <c r="L20" s="116"/>
+      <c r="M20" s="54"/>
+      <c r="N20" s="55"/>
+      <c r="O20" s="116"/>
+      <c r="P20" s="54"/>
+      <c r="Q20" s="55"/>
       <c r="R20" s="31"/>
       <c r="S20" s="31"/>
       <c r="T20" s="32"/>
@@ -9631,23 +9646,23 @@
       <c r="Z20" s="33"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="114"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="115"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="115"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="120"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="120"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="118"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="45"/>
-      <c r="O21" s="118"/>
-      <c r="P21" s="44"/>
-      <c r="Q21" s="45"/>
+      <c r="A21" s="119"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="120"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="120"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="114"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="114"/>
+      <c r="K21" s="55"/>
+      <c r="L21" s="116"/>
+      <c r="M21" s="54"/>
+      <c r="N21" s="55"/>
+      <c r="O21" s="116"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="55"/>
       <c r="R21" s="31"/>
       <c r="S21" s="31"/>
       <c r="T21" s="32"/>
@@ -9659,23 +9674,23 @@
       <c r="Z21" s="33"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="114"/>
-      <c r="B22" s="45"/>
-      <c r="C22" s="115"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="115"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="120"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="120"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="118"/>
-      <c r="M22" s="44"/>
-      <c r="N22" s="45"/>
-      <c r="O22" s="118"/>
-      <c r="P22" s="44"/>
-      <c r="Q22" s="45"/>
+      <c r="A22" s="119"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="120"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="120"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="114"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="114"/>
+      <c r="K22" s="55"/>
+      <c r="L22" s="116"/>
+      <c r="M22" s="54"/>
+      <c r="N22" s="55"/>
+      <c r="O22" s="116"/>
+      <c r="P22" s="54"/>
+      <c r="Q22" s="55"/>
       <c r="R22" s="31"/>
       <c r="S22" s="31"/>
       <c r="T22" s="32"/>
@@ -9687,23 +9702,23 @@
       <c r="Z22" s="33"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="114"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="115"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="115"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="120"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="120"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="118"/>
-      <c r="M23" s="44"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="118"/>
-      <c r="P23" s="44"/>
-      <c r="Q23" s="45"/>
+      <c r="A23" s="119"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="120"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="120"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="114"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="55"/>
+      <c r="J23" s="114"/>
+      <c r="K23" s="55"/>
+      <c r="L23" s="116"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="55"/>
+      <c r="O23" s="116"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="55"/>
       <c r="R23" s="31"/>
       <c r="S23" s="31"/>
       <c r="T23" s="32"/>
@@ -9715,23 +9730,23 @@
       <c r="Z23" s="33"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="114"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="115"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="115"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="120"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="120"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="118"/>
-      <c r="M24" s="44"/>
-      <c r="N24" s="45"/>
-      <c r="O24" s="118"/>
-      <c r="P24" s="44"/>
-      <c r="Q24" s="45"/>
+      <c r="A24" s="119"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="120"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="120"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="114"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="55"/>
+      <c r="J24" s="114"/>
+      <c r="K24" s="55"/>
+      <c r="L24" s="116"/>
+      <c r="M24" s="54"/>
+      <c r="N24" s="55"/>
+      <c r="O24" s="116"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="55"/>
       <c r="R24" s="31"/>
       <c r="S24" s="31"/>
       <c r="T24" s="32"/>
@@ -9743,23 +9758,23 @@
       <c r="Z24" s="33"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="114"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="115"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="115"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="120"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="120"/>
-      <c r="K25" s="45"/>
-      <c r="L25" s="118"/>
-      <c r="M25" s="44"/>
-      <c r="N25" s="45"/>
-      <c r="O25" s="118"/>
-      <c r="P25" s="44"/>
-      <c r="Q25" s="45"/>
+      <c r="A25" s="119"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="120"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="120"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="114"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="55"/>
+      <c r="J25" s="114"/>
+      <c r="K25" s="55"/>
+      <c r="L25" s="116"/>
+      <c r="M25" s="54"/>
+      <c r="N25" s="55"/>
+      <c r="O25" s="116"/>
+      <c r="P25" s="54"/>
+      <c r="Q25" s="55"/>
       <c r="R25" s="31"/>
       <c r="S25" s="31"/>
       <c r="T25" s="32"/>
@@ -9771,23 +9786,23 @@
       <c r="Z25" s="33"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="114"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="115"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="115"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="120"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="120"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="118"/>
-      <c r="M26" s="44"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="118"/>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="45"/>
+      <c r="A26" s="119"/>
+      <c r="B26" s="55"/>
+      <c r="C26" s="120"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="120"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="114"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="55"/>
+      <c r="J26" s="114"/>
+      <c r="K26" s="55"/>
+      <c r="L26" s="116"/>
+      <c r="M26" s="54"/>
+      <c r="N26" s="55"/>
+      <c r="O26" s="116"/>
+      <c r="P26" s="54"/>
+      <c r="Q26" s="55"/>
       <c r="R26" s="31"/>
       <c r="S26" s="31"/>
       <c r="T26" s="32"/>
@@ -9799,23 +9814,23 @@
       <c r="Z26" s="33"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="114"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="115"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="120"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="120"/>
-      <c r="K27" s="45"/>
-      <c r="L27" s="118"/>
-      <c r="M27" s="44"/>
-      <c r="N27" s="45"/>
-      <c r="O27" s="118"/>
-      <c r="P27" s="44"/>
-      <c r="Q27" s="45"/>
+      <c r="A27" s="119"/>
+      <c r="B27" s="55"/>
+      <c r="C27" s="120"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="120"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="114"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="55"/>
+      <c r="J27" s="114"/>
+      <c r="K27" s="55"/>
+      <c r="L27" s="116"/>
+      <c r="M27" s="54"/>
+      <c r="N27" s="55"/>
+      <c r="O27" s="116"/>
+      <c r="P27" s="54"/>
+      <c r="Q27" s="55"/>
       <c r="R27" s="31"/>
       <c r="S27" s="31"/>
       <c r="T27" s="32"/>
@@ -9827,23 +9842,23 @@
       <c r="Z27" s="33"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="114"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="115"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="115"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="120"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="120"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="118"/>
-      <c r="M28" s="44"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="118"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="45"/>
+      <c r="A28" s="119"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="120"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="120"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="114"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="114"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="116"/>
+      <c r="M28" s="54"/>
+      <c r="N28" s="55"/>
+      <c r="O28" s="116"/>
+      <c r="P28" s="54"/>
+      <c r="Q28" s="55"/>
       <c r="R28" s="31"/>
       <c r="S28" s="31"/>
       <c r="T28" s="32"/>
@@ -9855,23 +9870,23 @@
       <c r="Z28" s="33"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="114"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="115"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="115"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="120"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="120"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="118"/>
-      <c r="M29" s="44"/>
-      <c r="N29" s="45"/>
-      <c r="O29" s="118"/>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="45"/>
+      <c r="A29" s="119"/>
+      <c r="B29" s="55"/>
+      <c r="C29" s="120"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="120"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="114"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="55"/>
+      <c r="J29" s="114"/>
+      <c r="K29" s="55"/>
+      <c r="L29" s="116"/>
+      <c r="M29" s="54"/>
+      <c r="N29" s="55"/>
+      <c r="O29" s="116"/>
+      <c r="P29" s="54"/>
+      <c r="Q29" s="55"/>
       <c r="R29" s="31"/>
       <c r="S29" s="31"/>
       <c r="T29" s="32"/>
@@ -9883,23 +9898,23 @@
       <c r="Z29" s="33"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="114"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="115"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="115"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="120"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="120"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="118"/>
-      <c r="M30" s="44"/>
-      <c r="N30" s="45"/>
-      <c r="O30" s="118"/>
-      <c r="P30" s="44"/>
-      <c r="Q30" s="45"/>
+      <c r="A30" s="119"/>
+      <c r="B30" s="55"/>
+      <c r="C30" s="120"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="120"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="114"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="55"/>
+      <c r="J30" s="114"/>
+      <c r="K30" s="55"/>
+      <c r="L30" s="116"/>
+      <c r="M30" s="54"/>
+      <c r="N30" s="55"/>
+      <c r="O30" s="116"/>
+      <c r="P30" s="54"/>
+      <c r="Q30" s="55"/>
       <c r="R30" s="31"/>
       <c r="S30" s="31"/>
       <c r="T30" s="32"/>
@@ -9911,23 +9926,23 @@
       <c r="Z30" s="33"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="116"/>
-      <c r="B31" s="99"/>
-      <c r="C31" s="117"/>
-      <c r="D31" s="99"/>
-      <c r="E31" s="117"/>
-      <c r="F31" s="99"/>
-      <c r="G31" s="123"/>
-      <c r="H31" s="94"/>
-      <c r="I31" s="99"/>
-      <c r="J31" s="123"/>
-      <c r="K31" s="99"/>
-      <c r="L31" s="119"/>
-      <c r="M31" s="94"/>
-      <c r="N31" s="99"/>
-      <c r="O31" s="119"/>
-      <c r="P31" s="94"/>
-      <c r="Q31" s="99"/>
+      <c r="A31" s="122"/>
+      <c r="B31" s="102"/>
+      <c r="C31" s="123"/>
+      <c r="D31" s="102"/>
+      <c r="E31" s="123"/>
+      <c r="F31" s="102"/>
+      <c r="G31" s="115"/>
+      <c r="H31" s="101"/>
+      <c r="I31" s="102"/>
+      <c r="J31" s="115"/>
+      <c r="K31" s="102"/>
+      <c r="L31" s="117"/>
+      <c r="M31" s="101"/>
+      <c r="N31" s="102"/>
+      <c r="O31" s="117"/>
+      <c r="P31" s="101"/>
+      <c r="Q31" s="102"/>
       <c r="R31" s="34"/>
       <c r="S31" s="34"/>
       <c r="T31" s="35"/>
@@ -10925,62 +10940,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -11005,62 +11020,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_タスク詳細画面.xlsx
+++ b/document/成果物ドキュメント_タスク詳細画面.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-14\Documents\project\TaskManager62\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7AA67B-0DDE-42BD-A5CD-1E9B634DF8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46E3D51D-27E2-4FEC-9173-75FD6023B111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -34,9 +34,6 @@
   </si>
   <si>
     <t>YYYY/MM/DD</t>
-  </si>
-  <si>
-    <t>チーム名</t>
   </si>
   <si>
     <t>ユースケース記述</t>
@@ -353,45 +350,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>1.ユーザーがタスク一覧画面からタスク詳細を選択する
-2.システムが押下されたタスクの詳細画面を表示する
-3.システムがタスクの名前、カテゴリ、期限、担当者情報、ステータス情報、メモ、コメントを表示する</t>
-    <rPh sb="10" eb="14">
-      <t>イチランガメン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="43" eb="47">
-      <t>ショウサイガメン</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="72" eb="74">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="75" eb="80">
-      <t>タントウシャジョウホウ</t>
-    </rPh>
-    <rPh sb="86" eb="88">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="97" eb="99">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>システムは詳細画面の時点でタスクの担当者以外は編集、削除を選択できないようにする</t>
     <rPh sb="5" eb="9">
       <t>ショウサイガメン</t>
@@ -478,6 +436,55 @@
   </si>
   <si>
     <t>④</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>チーム名 62期</t>
+    <rPh sb="7" eb="8">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.ユーザーが詳細を確認したいタスクを選択する
+2.システムが選択されたタスクの詳細画面を表示する
+3.システムが選択されたタスクの名前・カテゴリ・期限・担当者情報・ステータス情報・メモ・コメントを表示する</t>
+    <rPh sb="7" eb="9">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="40" eb="44">
+      <t>ショウサイガメン</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="77" eb="82">
+      <t>タントウシャジョウホウ</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>ヒョウジ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1530,141 +1537,141 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1680,98 +1687,98 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2213,67 +2220,67 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="77"/>
-      <c r="L3" s="77"/>
-      <c r="M3" s="77"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+      <c r="O3" s="71"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="77"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="71"/>
+      <c r="O4" s="71"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
-      <c r="L5" s="77"/>
-      <c r="M5" s="77"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="77"/>
-      <c r="D6" s="77"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
-      <c r="J6" s="77"/>
-      <c r="K6" s="77"/>
-      <c r="L6" s="77"/>
-      <c r="M6" s="77"/>
-      <c r="N6" s="77"/>
-      <c r="O6" s="77"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="71"/>
+      <c r="O6" s="71"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2294,16 +2301,16 @@
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
       <c r="E8" s="92" t="s">
-        <v>85</v>
-      </c>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="77"/>
-      <c r="K8" s="77"/>
-      <c r="L8" s="77"/>
-      <c r="M8" s="77"/>
+        <v>84</v>
+      </c>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="71"/>
+      <c r="K8" s="71"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="71"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
@@ -2313,26 +2320,26 @@
       <c r="G13" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="55"/>
+      <c r="H13" s="45"/>
       <c r="I13" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="54"/>
-      <c r="K13" s="55"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="45"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="88"/>
-      <c r="H14" s="55"/>
+      <c r="H14" s="45"/>
       <c r="I14" s="88"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="55"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="45"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="88"/>
-      <c r="H15" s="55"/>
+      <c r="H15" s="45"/>
       <c r="I15" s="88"/>
-      <c r="J15" s="54"/>
-      <c r="K15" s="55"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="45"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2342,12 +2349,12 @@
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
       <c r="G17" s="89" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="77"/>
-      <c r="I17" s="77"/>
-      <c r="J17" s="77"/>
-      <c r="K17" s="77"/>
+        <v>98</v>
+      </c>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3361,218 +3368,218 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="100" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="81" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="81" t="s">
+      <c r="G1" s="83"/>
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="80"/>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="62"/>
+      <c r="F2" s="61" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="62"/>
+      <c r="H2" s="113">
+        <v>46126</v>
+      </c>
+      <c r="I2" s="75" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2" s="76"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="104" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="64" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="64" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="65"/>
-      <c r="H2" s="95">
-        <v>46126</v>
-      </c>
-      <c r="I2" s="70" t="s">
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="96" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="71"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="72"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="104"/>
-      <c r="B4" s="105"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="97"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="106" t="s">
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="87"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="112" t="s">
+      <c r="B6" s="44"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="83"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="99" t="s">
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="47"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="59" t="s">
+      <c r="B7" s="44"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="57"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="99" t="s">
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="47"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="59" t="s">
+      <c r="B8" s="44"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="57"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="99" t="s">
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="47"/>
+    </row>
+    <row r="9" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A9" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="59" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="57"/>
-    </row>
-    <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="107" t="s">
+      <c r="B9" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="98" t="s">
+      <c r="C9" s="45"/>
+      <c r="D9" s="97" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="47"/>
+    </row>
+    <row r="10" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A10" s="107"/>
+      <c r="B10" s="109" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="55"/>
-      <c r="D9" s="113" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="57"/>
-    </row>
-    <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="108"/>
-      <c r="B10" s="98" t="s">
+      <c r="C10" s="45"/>
+      <c r="D10" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="47"/>
+    </row>
+    <row r="11" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A11" s="108"/>
+      <c r="B11" s="109" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="55"/>
-      <c r="D10" s="59" t="s">
+      <c r="C11" s="45"/>
+      <c r="D11" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="47"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="105" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="44"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="57"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="109"/>
-      <c r="B11" s="98" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="55"/>
-      <c r="D11" s="59" t="s">
-        <v>86</v>
-      </c>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="57"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="99" t="s">
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="47"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A13" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="54"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="59" t="s">
+      <c r="B13" s="94"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="57"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="100" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="101"/>
-      <c r="C13" s="102"/>
-      <c r="D13" s="110" t="s">
-        <v>89</v>
-      </c>
-      <c r="E13" s="101"/>
-      <c r="F13" s="101"/>
-      <c r="G13" s="101"/>
-      <c r="H13" s="101"/>
-      <c r="I13" s="101"/>
-      <c r="J13" s="111"/>
+      <c r="E13" s="94"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="95"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4563,6 +4570,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -4571,25 +4597,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4608,72 +4615,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="73" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="81" t="s">
+      <c r="A1" s="78" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="83"/>
+      <c r="F1" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="81" t="s">
+      <c r="G1" s="83"/>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="80"/>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="64" t="s">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="62"/>
+      <c r="F2" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="64" t="s">
+      <c r="G2" s="62"/>
+      <c r="H2" s="73">
+        <v>46120</v>
+      </c>
+      <c r="I2" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="65"/>
-      <c r="H2" s="68">
-        <v>46120</v>
-      </c>
-      <c r="I2" s="70" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="71"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="72"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="104"/>
-      <c r="B4" s="105"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="97"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6028,72 +6035,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="73" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="81" t="s">
+      <c r="A1" s="78" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="83"/>
+      <c r="F1" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="81" t="s">
+      <c r="G1" s="83"/>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="80"/>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="64" t="s">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="62"/>
+      <c r="F2" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="64" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="65"/>
-      <c r="H2" s="68">
+      <c r="G2" s="62"/>
+      <c r="H2" s="73">
         <v>46122</v>
       </c>
-      <c r="I2" s="70" t="s">
-        <v>69</v>
-      </c>
-      <c r="J2" s="71"/>
+      <c r="I2" s="75" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="72"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="104"/>
-      <c r="B4" s="105"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="97"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7444,484 +7451,484 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="78" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="83"/>
+      <c r="F1" s="84" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="83"/>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="62"/>
+      <c r="F2" s="61" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="62"/>
+      <c r="H2" s="73">
+        <v>46122</v>
+      </c>
+      <c r="I2" s="75" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2" s="76"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="81" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="81" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="80"/>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="64" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="64" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="65"/>
-      <c r="H2" s="68">
-        <v>46122</v>
-      </c>
-      <c r="I2" s="70" t="s">
-        <v>69</v>
-      </c>
-      <c r="J2" s="71"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="72"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="76"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="72"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="78" t="s">
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="86" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="87"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="82" t="s">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="47"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="67"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="69"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="70"/>
+      <c r="B8" s="71"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="72"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="70"/>
+      <c r="B9" s="71"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="70"/>
+      <c r="B10" s="71"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="70"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="70"/>
+      <c r="B12" s="71"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="72"/>
+    </row>
+    <row r="13" spans="1:10" ht="102" customHeight="1">
+      <c r="A13" s="70"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="59" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="47"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="44"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="83"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="57"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="84"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
-      <c r="J7" s="86"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="76"/>
-      <c r="B8" s="77"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="87"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="76"/>
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="87"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="76"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="87"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="76"/>
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="87"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="76"/>
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="87"/>
-    </row>
-    <row r="13" spans="1:10" ht="102" customHeight="1">
-      <c r="A13" s="76"/>
-      <c r="B13" s="77"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="87"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="53" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="57"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="53" t="s">
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="59" t="s">
+      <c r="J15" s="16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="59" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="44"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="44"/>
+      <c r="J16" s="47"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A17" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="54"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="H16" s="56" t="s">
-        <v>19</v>
-      </c>
-      <c r="I16" s="54"/>
-      <c r="J16" s="57"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="58" t="s">
+      <c r="B17" s="44"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="54"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="17" t="s">
+      <c r="E17" s="17" t="s">
         <v>78</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>79</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H17" s="59" t="s">
-        <v>98</v>
-      </c>
-      <c r="I17" s="54"/>
-      <c r="J17" s="57"/>
+        <v>77</v>
+      </c>
+      <c r="H17" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="I17" s="44"/>
+      <c r="J17" s="47"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A18" s="51"/>
+      <c r="A18" s="48"/>
       <c r="B18" s="49"/>
-      <c r="C18" s="52"/>
+      <c r="C18" s="50"/>
       <c r="D18" s="39"/>
       <c r="E18" s="39"/>
       <c r="F18" s="40"/>
       <c r="G18" s="40"/>
-      <c r="H18" s="48"/>
+      <c r="H18" s="51"/>
       <c r="I18" s="49"/>
-      <c r="J18" s="50"/>
+      <c r="J18" s="52"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="60"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="61"/>
+      <c r="A19" s="85"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="66"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="61"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="66"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="43" t="s">
+      <c r="A20" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="54"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="63" t="s">
+      <c r="B21" s="56"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="58" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="46"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="37" t="s">
+      <c r="J21" s="38" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="J21" s="38" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="53" t="s">
+      <c r="B22" s="44"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="54"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="15" t="s">
+      <c r="E22" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="F22" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="G22" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G22" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22" s="56" t="s">
-        <v>19</v>
-      </c>
-      <c r="I22" s="54"/>
-      <c r="J22" s="57"/>
+      <c r="H22" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="44"/>
+      <c r="J22" s="47"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="58" t="s">
+      <c r="A23" s="43" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="44"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="54"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="17" t="s">
-        <v>81</v>
-      </c>
       <c r="E23" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F23" s="18"/>
       <c r="G23" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="H23" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="I23" s="54"/>
-      <c r="J23" s="57"/>
+        <v>80</v>
+      </c>
+      <c r="H23" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="I23" s="44"/>
+      <c r="J23" s="47"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A24" s="51"/>
+      <c r="A24" s="48"/>
       <c r="B24" s="49"/>
-      <c r="C24" s="52"/>
+      <c r="C24" s="50"/>
       <c r="D24" s="39"/>
       <c r="E24" s="39"/>
       <c r="F24" s="40"/>
       <c r="G24" s="40"/>
-      <c r="H24" s="48"/>
+      <c r="H24" s="51"/>
       <c r="I24" s="49"/>
-      <c r="J24" s="50"/>
+      <c r="J24" s="52"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="60"/>
-      <c r="B25" s="61"/>
-      <c r="C25" s="61"/>
+      <c r="A25" s="85"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="66"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="61"/>
-      <c r="J25" s="61"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="66"/>
+      <c r="J25" s="66"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="43" t="s">
+      <c r="A26" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="54"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
+    </row>
+    <row r="27" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A27" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="44"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="44"/>
-      <c r="J26" s="44"/>
-    </row>
-    <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="63" t="s">
+      <c r="B27" s="56"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" s="56"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="46"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="37" t="s">
+      <c r="J27" s="38" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A28" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="J27" s="38" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="53" t="s">
+      <c r="B28" s="44"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="54"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="15" t="s">
+      <c r="E28" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="F28" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F28" s="15" t="s">
+      <c r="G28" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G28" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="H28" s="56" t="s">
-        <v>19</v>
-      </c>
-      <c r="I28" s="54"/>
-      <c r="J28" s="57"/>
+      <c r="H28" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="44"/>
+      <c r="J28" s="47"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="58" t="s">
-        <v>82</v>
-      </c>
-      <c r="B29" s="54"/>
-      <c r="C29" s="55"/>
+      <c r="A29" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="44"/>
+      <c r="C29" s="45"/>
       <c r="D29" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="H29" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="I29" s="54"/>
-      <c r="J29" s="57"/>
+        <v>94</v>
+      </c>
+      <c r="H29" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="I29" s="44"/>
+      <c r="J29" s="47"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="51"/>
+      <c r="A30" s="48"/>
       <c r="B30" s="49"/>
-      <c r="C30" s="52"/>
+      <c r="C30" s="50"/>
       <c r="D30" s="39"/>
       <c r="E30" s="39"/>
       <c r="F30" s="40"/>
       <c r="G30" s="40"/>
-      <c r="H30" s="48"/>
+      <c r="H30" s="51"/>
       <c r="I30" s="49"/>
-      <c r="J30" s="50"/>
+      <c r="J30" s="52"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1">
       <c r="A31" s="3"/>
@@ -7936,96 +7943,96 @@
       <c r="J31" s="41"/>
     </row>
     <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="43" t="s">
+      <c r="A32" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="54"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="54"/>
+    </row>
+    <row r="33" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A33" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="44"/>
-      <c r="C32" s="44"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="44"/>
-      <c r="H32" s="44"/>
-      <c r="I32" s="44"/>
-      <c r="J32" s="44"/>
-    </row>
-    <row r="33" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A33" s="63" t="s">
+      <c r="B33" s="56"/>
+      <c r="C33" s="57"/>
+      <c r="D33" s="58" t="s">
+        <v>91</v>
+      </c>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="46"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="45" t="s">
-        <v>93</v>
-      </c>
-      <c r="E33" s="46"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="47"/>
-      <c r="I33" s="37" t="s">
+      <c r="J33" s="38" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A34" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="J33" s="38" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A34" s="53" t="s">
+      <c r="B34" s="44"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="54"/>
-      <c r="C34" s="55"/>
-      <c r="D34" s="15" t="s">
+      <c r="E34" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="F34" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="G34" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G34" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="H34" s="56" t="s">
-        <v>19</v>
-      </c>
-      <c r="I34" s="54"/>
-      <c r="J34" s="57"/>
+      <c r="H34" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="44"/>
+      <c r="J34" s="47"/>
     </row>
     <row r="35" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A35" s="58" t="s">
-        <v>99</v>
-      </c>
-      <c r="B35" s="54"/>
-      <c r="C35" s="55"/>
+      <c r="A35" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" s="44"/>
+      <c r="C35" s="45"/>
       <c r="D35" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F35" s="18"/>
       <c r="G35" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="H35" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="I35" s="54"/>
-      <c r="J35" s="57"/>
+        <v>82</v>
+      </c>
+      <c r="H35" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="I35" s="44"/>
+      <c r="J35" s="47"/>
     </row>
     <row r="36" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A36" s="51"/>
+      <c r="A36" s="48"/>
       <c r="B36" s="49"/>
-      <c r="C36" s="52"/>
+      <c r="C36" s="50"/>
       <c r="D36" s="39"/>
       <c r="E36" s="39"/>
       <c r="F36" s="40"/>
       <c r="G36" s="40"/>
-      <c r="H36" s="48"/>
+      <c r="H36" s="51"/>
       <c r="I36" s="49"/>
-      <c r="J36" s="50"/>
+      <c r="J36" s="52"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="38" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8991,29 +8998,19 @@
     <row r="998" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="F2:G4"/>
@@ -9030,19 +9027,29 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="D21:H21"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="H34:J34"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9062,182 +9069,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="100" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="84" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="82"/>
+      <c r="M1" s="82"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="84" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="84" t="s">
+        <v>7</v>
+      </c>
+      <c r="R1" s="83"/>
+      <c r="S1" s="84" t="s">
+        <v>8</v>
+      </c>
+      <c r="T1" s="87"/>
+    </row>
+    <row r="2" spans="1:26" ht="18" customHeight="1">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="69"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="63"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="72"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1">
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="102"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="103"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="103"/>
+      <c r="Q4" s="112"/>
+      <c r="R4" s="103"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="122"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="81" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="81" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="81" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="81" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" s="80"/>
-      <c r="Q1" s="81" t="s">
-        <v>8</v>
-      </c>
-      <c r="R1" s="80"/>
-      <c r="S1" s="81" t="s">
-        <v>9</v>
-      </c>
-      <c r="T1" s="83"/>
-    </row>
-    <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="64"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="64"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="64"/>
-      <c r="T2" s="86"/>
-    </row>
-    <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="66"/>
-      <c r="L3" s="77"/>
-      <c r="M3" s="77"/>
-      <c r="N3" s="67"/>
-      <c r="O3" s="66"/>
-      <c r="P3" s="67"/>
-      <c r="Q3" s="66"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="66"/>
-      <c r="T3" s="87"/>
-    </row>
-    <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="104"/>
-      <c r="B4" s="105"/>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="94"/>
-      <c r="K4" s="93"/>
-      <c r="L4" s="105"/>
-      <c r="M4" s="105"/>
-      <c r="N4" s="94"/>
-      <c r="O4" s="93"/>
-      <c r="P4" s="94"/>
-      <c r="Q4" s="93"/>
-      <c r="R4" s="94"/>
-      <c r="S4" s="93"/>
-      <c r="T4" s="118"/>
-    </row>
-    <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="78" t="s">
+      <c r="B5" s="82"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="112" t="s">
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
+      <c r="L5" s="82"/>
+      <c r="M5" s="82"/>
+      <c r="N5" s="82"/>
+      <c r="O5" s="82"/>
+      <c r="P5" s="82"/>
+      <c r="Q5" s="82"/>
+      <c r="R5" s="82"/>
+      <c r="S5" s="82"/>
+      <c r="T5" s="87"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="79"/>
-      <c r="K5" s="79"/>
-      <c r="L5" s="79"/>
-      <c r="M5" s="79"/>
-      <c r="N5" s="79"/>
-      <c r="O5" s="79"/>
-      <c r="P5" s="79"/>
-      <c r="Q5" s="79"/>
-      <c r="R5" s="79"/>
-      <c r="S5" s="79"/>
-      <c r="T5" s="83"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="53" t="s">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="44"/>
+      <c r="R6" s="44"/>
+      <c r="S6" s="44"/>
+      <c r="T6" s="47"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="59" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="54"/>
-      <c r="M6" s="54"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="54"/>
-      <c r="P6" s="54"/>
-      <c r="Q6" s="54"/>
-      <c r="R6" s="54"/>
-      <c r="S6" s="54"/>
-      <c r="T6" s="57"/>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="53" t="s">
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="59" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="54"/>
-      <c r="K7" s="54"/>
-      <c r="L7" s="54"/>
-      <c r="M7" s="54"/>
-      <c r="N7" s="54"/>
-      <c r="O7" s="54"/>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54"/>
-      <c r="R7" s="54"/>
-      <c r="S7" s="54"/>
-      <c r="T7" s="57"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="44"/>
+      <c r="N7" s="44"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="44"/>
+      <c r="Q7" s="44"/>
+      <c r="R7" s="44"/>
+      <c r="S7" s="44"/>
+      <c r="T7" s="47"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9265,11 +9272,11 @@
       <c r="A9" s="19"/>
       <c r="B9" s="20"/>
       <c r="C9" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" s="22"/>
       <c r="E9" s="22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F9" s="22"/>
       <c r="G9" s="23"/>
@@ -9299,7 +9306,7 @@
       <c r="C10" s="25"/>
       <c r="D10" s="20"/>
       <c r="E10" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F10" s="20"/>
       <c r="G10" s="26"/>
@@ -9329,7 +9336,7 @@
       <c r="C11" s="25"/>
       <c r="D11" s="20"/>
       <c r="E11" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" s="20"/>
       <c r="G11" s="26"/>
@@ -9359,7 +9366,7 @@
       <c r="C12" s="25"/>
       <c r="D12" s="20"/>
       <c r="E12" s="20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F12" s="20"/>
       <c r="G12" s="26"/>
@@ -9389,7 +9396,7 @@
       <c r="C13" s="27"/>
       <c r="D13" s="28"/>
       <c r="E13" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F13" s="28"/>
       <c r="G13" s="29"/>
@@ -9436,79 +9443,79 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="59" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="45"/>
+      <c r="C15" s="121" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="45"/>
+      <c r="E15" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="55"/>
-      <c r="C15" s="121" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="55"/>
-      <c r="E15" s="56" t="s">
+      <c r="F15" s="45"/>
+      <c r="G15" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="55"/>
-      <c r="G15" s="56" t="s">
+      <c r="H15" s="44"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="54"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="56" t="s">
+      <c r="K15" s="45"/>
+      <c r="L15" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="55"/>
-      <c r="L15" s="56" t="s">
+      <c r="M15" s="44"/>
+      <c r="N15" s="45"/>
+      <c r="O15" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="54"/>
-      <c r="N15" s="55"/>
-      <c r="O15" s="56" t="s">
+      <c r="P15" s="44"/>
+      <c r="Q15" s="45"/>
+      <c r="R15" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="54"/>
-      <c r="Q15" s="55"/>
-      <c r="R15" s="15" t="s">
+      <c r="S15" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="S15" s="15" t="s">
+      <c r="T15" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="T15" s="30" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="114">
+        <v>1</v>
+      </c>
+      <c r="B16" s="45"/>
+      <c r="C16" s="115" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="119">
-        <v>1</v>
-      </c>
-      <c r="B16" s="55"/>
-      <c r="C16" s="120" t="s">
+      <c r="D16" s="45"/>
+      <c r="E16" s="115" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="55"/>
-      <c r="E16" s="120" t="s">
+      <c r="F16" s="45"/>
+      <c r="G16" s="120" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="55"/>
-      <c r="G16" s="114" t="s">
+      <c r="H16" s="44"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="120" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="54"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="114" t="s">
+      <c r="K16" s="45"/>
+      <c r="L16" s="118" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="55"/>
-      <c r="L16" s="116" t="s">
+      <c r="M16" s="44"/>
+      <c r="N16" s="45"/>
+      <c r="O16" s="118" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="54"/>
-      <c r="N16" s="55"/>
-      <c r="O16" s="116" t="s">
-        <v>59</v>
-      </c>
-      <c r="P16" s="54"/>
-      <c r="Q16" s="55"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="45"/>
       <c r="R16" s="31"/>
       <c r="S16" s="31"/>
       <c r="T16" s="32"/>
@@ -9520,37 +9527,37 @@
       <c r="Z16" s="33"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="119">
+      <c r="A17" s="114">
         <v>2</v>
       </c>
-      <c r="B17" s="55"/>
-      <c r="C17" s="120" t="s">
+      <c r="B17" s="45"/>
+      <c r="C17" s="115" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="45"/>
+      <c r="E17" s="115" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="55"/>
-      <c r="E17" s="120" t="s">
+      <c r="F17" s="45"/>
+      <c r="G17" s="120" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="55"/>
-      <c r="G17" s="114" t="s">
+      <c r="H17" s="44"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="120" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="54"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="114" t="s">
+      <c r="K17" s="45"/>
+      <c r="L17" s="118" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="55"/>
-      <c r="L17" s="116" t="s">
+      <c r="M17" s="44"/>
+      <c r="N17" s="45"/>
+      <c r="O17" s="118" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="54"/>
-      <c r="N17" s="55"/>
-      <c r="O17" s="116" t="s">
-        <v>65</v>
-      </c>
-      <c r="P17" s="54"/>
-      <c r="Q17" s="55"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="45"/>
       <c r="R17" s="31"/>
       <c r="S17" s="31"/>
       <c r="T17" s="32"/>
@@ -9562,23 +9569,23 @@
       <c r="Z17" s="33"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="119"/>
-      <c r="B18" s="55"/>
-      <c r="C18" s="120"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="120"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="114"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="114"/>
-      <c r="K18" s="55"/>
-      <c r="L18" s="116"/>
-      <c r="M18" s="54"/>
-      <c r="N18" s="55"/>
-      <c r="O18" s="116"/>
-      <c r="P18" s="54"/>
-      <c r="Q18" s="55"/>
+      <c r="A18" s="114"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="115"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="115"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="120"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="120"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="118"/>
+      <c r="M18" s="44"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="44"/>
+      <c r="Q18" s="45"/>
       <c r="R18" s="31"/>
       <c r="S18" s="31"/>
       <c r="T18" s="32"/>
@@ -9590,23 +9597,23 @@
       <c r="Z18" s="33"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="119"/>
-      <c r="B19" s="55"/>
-      <c r="C19" s="120"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="120"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="114"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="114"/>
-      <c r="K19" s="55"/>
-      <c r="L19" s="116"/>
-      <c r="M19" s="54"/>
-      <c r="N19" s="55"/>
-      <c r="O19" s="116"/>
-      <c r="P19" s="54"/>
-      <c r="Q19" s="55"/>
+      <c r="A19" s="114"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="115"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="115"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="120"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="120"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="118"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="45"/>
+      <c r="O19" s="118"/>
+      <c r="P19" s="44"/>
+      <c r="Q19" s="45"/>
       <c r="R19" s="31"/>
       <c r="S19" s="31"/>
       <c r="T19" s="32"/>
@@ -9618,23 +9625,23 @@
       <c r="Z19" s="33"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="119"/>
-      <c r="B20" s="55"/>
-      <c r="C20" s="120"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="120"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="114"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="114"/>
-      <c r="K20" s="55"/>
-      <c r="L20" s="116"/>
-      <c r="M20" s="54"/>
-      <c r="N20" s="55"/>
-      <c r="O20" s="116"/>
-      <c r="P20" s="54"/>
-      <c r="Q20" s="55"/>
+      <c r="A20" s="114"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="115"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="115"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="120"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="118"/>
+      <c r="M20" s="44"/>
+      <c r="N20" s="45"/>
+      <c r="O20" s="118"/>
+      <c r="P20" s="44"/>
+      <c r="Q20" s="45"/>
       <c r="R20" s="31"/>
       <c r="S20" s="31"/>
       <c r="T20" s="32"/>
@@ -9646,23 +9653,23 @@
       <c r="Z20" s="33"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="119"/>
-      <c r="B21" s="55"/>
-      <c r="C21" s="120"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="120"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="114"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="114"/>
-      <c r="K21" s="55"/>
-      <c r="L21" s="116"/>
-      <c r="M21" s="54"/>
-      <c r="N21" s="55"/>
-      <c r="O21" s="116"/>
-      <c r="P21" s="54"/>
-      <c r="Q21" s="55"/>
+      <c r="A21" s="114"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="115"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="115"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="120"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="120"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="118"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="45"/>
+      <c r="O21" s="118"/>
+      <c r="P21" s="44"/>
+      <c r="Q21" s="45"/>
       <c r="R21" s="31"/>
       <c r="S21" s="31"/>
       <c r="T21" s="32"/>
@@ -9674,23 +9681,23 @@
       <c r="Z21" s="33"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="119"/>
-      <c r="B22" s="55"/>
-      <c r="C22" s="120"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="120"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="114"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="114"/>
-      <c r="K22" s="55"/>
-      <c r="L22" s="116"/>
-      <c r="M22" s="54"/>
-      <c r="N22" s="55"/>
-      <c r="O22" s="116"/>
-      <c r="P22" s="54"/>
-      <c r="Q22" s="55"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="115"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="115"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="120"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="120"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="118"/>
+      <c r="M22" s="44"/>
+      <c r="N22" s="45"/>
+      <c r="O22" s="118"/>
+      <c r="P22" s="44"/>
+      <c r="Q22" s="45"/>
       <c r="R22" s="31"/>
       <c r="S22" s="31"/>
       <c r="T22" s="32"/>
@@ -9702,23 +9709,23 @@
       <c r="Z22" s="33"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="119"/>
-      <c r="B23" s="55"/>
-      <c r="C23" s="120"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="120"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="114"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="55"/>
-      <c r="J23" s="114"/>
-      <c r="K23" s="55"/>
-      <c r="L23" s="116"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="55"/>
-      <c r="O23" s="116"/>
-      <c r="P23" s="54"/>
-      <c r="Q23" s="55"/>
+      <c r="A23" s="114"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="115"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="115"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="120"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="120"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="118"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="118"/>
+      <c r="P23" s="44"/>
+      <c r="Q23" s="45"/>
       <c r="R23" s="31"/>
       <c r="S23" s="31"/>
       <c r="T23" s="32"/>
@@ -9730,23 +9737,23 @@
       <c r="Z23" s="33"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="119"/>
-      <c r="B24" s="55"/>
-      <c r="C24" s="120"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="120"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="114"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="55"/>
-      <c r="J24" s="114"/>
-      <c r="K24" s="55"/>
-      <c r="L24" s="116"/>
-      <c r="M24" s="54"/>
-      <c r="N24" s="55"/>
-      <c r="O24" s="116"/>
-      <c r="P24" s="54"/>
-      <c r="Q24" s="55"/>
+      <c r="A24" s="114"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="115"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="115"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="120"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="120"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="118"/>
+      <c r="M24" s="44"/>
+      <c r="N24" s="45"/>
+      <c r="O24" s="118"/>
+      <c r="P24" s="44"/>
+      <c r="Q24" s="45"/>
       <c r="R24" s="31"/>
       <c r="S24" s="31"/>
       <c r="T24" s="32"/>
@@ -9758,23 +9765,23 @@
       <c r="Z24" s="33"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="119"/>
-      <c r="B25" s="55"/>
-      <c r="C25" s="120"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="120"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="114"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="55"/>
-      <c r="J25" s="114"/>
-      <c r="K25" s="55"/>
-      <c r="L25" s="116"/>
-      <c r="M25" s="54"/>
-      <c r="N25" s="55"/>
-      <c r="O25" s="116"/>
-      <c r="P25" s="54"/>
-      <c r="Q25" s="55"/>
+      <c r="A25" s="114"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="115"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="115"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="120"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="120"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="118"/>
+      <c r="M25" s="44"/>
+      <c r="N25" s="45"/>
+      <c r="O25" s="118"/>
+      <c r="P25" s="44"/>
+      <c r="Q25" s="45"/>
       <c r="R25" s="31"/>
       <c r="S25" s="31"/>
       <c r="T25" s="32"/>
@@ -9786,23 +9793,23 @@
       <c r="Z25" s="33"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="119"/>
-      <c r="B26" s="55"/>
-      <c r="C26" s="120"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="120"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="114"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="55"/>
-      <c r="J26" s="114"/>
-      <c r="K26" s="55"/>
-      <c r="L26" s="116"/>
-      <c r="M26" s="54"/>
-      <c r="N26" s="55"/>
-      <c r="O26" s="116"/>
-      <c r="P26" s="54"/>
-      <c r="Q26" s="55"/>
+      <c r="A26" s="114"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="115"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="115"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="120"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="120"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="118"/>
+      <c r="M26" s="44"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="118"/>
+      <c r="P26" s="44"/>
+      <c r="Q26" s="45"/>
       <c r="R26" s="31"/>
       <c r="S26" s="31"/>
       <c r="T26" s="32"/>
@@ -9814,23 +9821,23 @@
       <c r="Z26" s="33"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="119"/>
-      <c r="B27" s="55"/>
-      <c r="C27" s="120"/>
-      <c r="D27" s="55"/>
-      <c r="E27" s="120"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="114"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="55"/>
-      <c r="J27" s="114"/>
-      <c r="K27" s="55"/>
-      <c r="L27" s="116"/>
-      <c r="M27" s="54"/>
-      <c r="N27" s="55"/>
-      <c r="O27" s="116"/>
-      <c r="P27" s="54"/>
-      <c r="Q27" s="55"/>
+      <c r="A27" s="114"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="115"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="120"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="120"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="118"/>
+      <c r="M27" s="44"/>
+      <c r="N27" s="45"/>
+      <c r="O27" s="118"/>
+      <c r="P27" s="44"/>
+      <c r="Q27" s="45"/>
       <c r="R27" s="31"/>
       <c r="S27" s="31"/>
       <c r="T27" s="32"/>
@@ -9842,23 +9849,23 @@
       <c r="Z27" s="33"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="119"/>
-      <c r="B28" s="55"/>
-      <c r="C28" s="120"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="120"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="114"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="114"/>
-      <c r="K28" s="55"/>
-      <c r="L28" s="116"/>
-      <c r="M28" s="54"/>
-      <c r="N28" s="55"/>
-      <c r="O28" s="116"/>
-      <c r="P28" s="54"/>
-      <c r="Q28" s="55"/>
+      <c r="A28" s="114"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="115"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="115"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="120"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="118"/>
+      <c r="M28" s="44"/>
+      <c r="N28" s="45"/>
+      <c r="O28" s="118"/>
+      <c r="P28" s="44"/>
+      <c r="Q28" s="45"/>
       <c r="R28" s="31"/>
       <c r="S28" s="31"/>
       <c r="T28" s="32"/>
@@ -9870,23 +9877,23 @@
       <c r="Z28" s="33"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="119"/>
-      <c r="B29" s="55"/>
-      <c r="C29" s="120"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="120"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="114"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="55"/>
-      <c r="J29" s="114"/>
-      <c r="K29" s="55"/>
-      <c r="L29" s="116"/>
-      <c r="M29" s="54"/>
-      <c r="N29" s="55"/>
-      <c r="O29" s="116"/>
-      <c r="P29" s="54"/>
-      <c r="Q29" s="55"/>
+      <c r="A29" s="114"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="115"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="115"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="120"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="120"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="118"/>
+      <c r="M29" s="44"/>
+      <c r="N29" s="45"/>
+      <c r="O29" s="118"/>
+      <c r="P29" s="44"/>
+      <c r="Q29" s="45"/>
       <c r="R29" s="31"/>
       <c r="S29" s="31"/>
       <c r="T29" s="32"/>
@@ -9898,23 +9905,23 @@
       <c r="Z29" s="33"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="119"/>
-      <c r="B30" s="55"/>
-      <c r="C30" s="120"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="120"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="114"/>
-      <c r="H30" s="54"/>
-      <c r="I30" s="55"/>
-      <c r="J30" s="114"/>
-      <c r="K30" s="55"/>
-      <c r="L30" s="116"/>
-      <c r="M30" s="54"/>
-      <c r="N30" s="55"/>
-      <c r="O30" s="116"/>
-      <c r="P30" s="54"/>
-      <c r="Q30" s="55"/>
+      <c r="A30" s="114"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="115"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="115"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="120"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="120"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="118"/>
+      <c r="M30" s="44"/>
+      <c r="N30" s="45"/>
+      <c r="O30" s="118"/>
+      <c r="P30" s="44"/>
+      <c r="Q30" s="45"/>
       <c r="R30" s="31"/>
       <c r="S30" s="31"/>
       <c r="T30" s="32"/>
@@ -9926,23 +9933,23 @@
       <c r="Z30" s="33"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="122"/>
-      <c r="B31" s="102"/>
-      <c r="C31" s="123"/>
-      <c r="D31" s="102"/>
-      <c r="E31" s="123"/>
-      <c r="F31" s="102"/>
-      <c r="G31" s="115"/>
-      <c r="H31" s="101"/>
-      <c r="I31" s="102"/>
-      <c r="J31" s="115"/>
-      <c r="K31" s="102"/>
-      <c r="L31" s="117"/>
-      <c r="M31" s="101"/>
-      <c r="N31" s="102"/>
-      <c r="O31" s="117"/>
-      <c r="P31" s="101"/>
-      <c r="Q31" s="102"/>
+      <c r="A31" s="116"/>
+      <c r="B31" s="99"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="99"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="99"/>
+      <c r="G31" s="123"/>
+      <c r="H31" s="94"/>
+      <c r="I31" s="99"/>
+      <c r="J31" s="123"/>
+      <c r="K31" s="99"/>
+      <c r="L31" s="119"/>
+      <c r="M31" s="94"/>
+      <c r="N31" s="99"/>
+      <c r="O31" s="119"/>
+      <c r="P31" s="94"/>
+      <c r="Q31" s="99"/>
       <c r="R31" s="34"/>
       <c r="S31" s="34"/>
       <c r="T31" s="35"/>
@@ -10940,6 +10947,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -10964,118 +11083,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_タスク詳細画面.xlsx
+++ b/document/成果物ドキュメント_タスク詳細画面.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-14\Documents\project\TaskManager62\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7AA67B-0DDE-42BD-A5CD-1E9B634DF8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8455083-22C8-48ED-BBD0-C7E03B45EADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -25,18 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="99">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
   <si>
     <t>初版</t>
-  </si>
-  <si>
-    <t>YYYY/MM/DD</t>
-  </si>
-  <si>
-    <t>チーム名</t>
   </si>
   <si>
     <t>ユースケース記述</t>
@@ -254,31 +248,7 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク詳細画面</t>
-    <rPh sb="3" eb="7">
-      <t>ショウサイガメン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスクの詳細を表示する</t>
-    <rPh sb="4" eb="6">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>商品企画部の従業員(ユーザー)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスクが登録済みであること</t>
-    <rPh sb="4" eb="7">
-      <t>トウロクズ</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -350,45 +320,6 @@
   </si>
   <si>
     <t>システムがタスク詳細を表示し編集、削除、コメント投稿、コメント削除画面へのボタンを表示すること</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1.ユーザーがタスク一覧画面からタスク詳細を選択する
-2.システムが押下されたタスクの詳細画面を表示する
-3.システムがタスクの名前、カテゴリ、期限、担当者情報、ステータス情報、メモ、コメントを表示する</t>
-    <rPh sb="10" eb="14">
-      <t>イチランガメン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="43" eb="47">
-      <t>ショウサイガメン</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="72" eb="74">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="75" eb="80">
-      <t>タントウシャジョウホウ</t>
-    </rPh>
-    <rPh sb="86" eb="88">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="97" eb="99">
-      <t>ヒョウジ</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -478,6 +409,69 @@
   </si>
   <si>
     <t>④</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>チーム名 62期</t>
+    <rPh sb="7" eb="8">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクがシステムに登録されていること</t>
+    <rPh sb="9" eb="11">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザーが選択したタスクの詳細を確認する</t>
+    <rPh sb="5" eb="7">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクの詳細を確認する</t>
+    <rPh sb="4" eb="6">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1．ユーザーがタスク一覧画面で詳細を確認したいタスクを選択する
+2．システムがユーザーの選択したタスクの詳細画面を表示する</t>
+    <rPh sb="10" eb="14">
+      <t>イチランガメン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="52" eb="56">
+      <t>ショウサイガメン</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ヒョウジ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1400,7 +1394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1530,141 +1524,141 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1680,98 +1674,101 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2213,67 +2210,67 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="77"/>
-      <c r="L3" s="77"/>
-      <c r="M3" s="77"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+      <c r="O3" s="71"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="77"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="71"/>
+      <c r="O4" s="71"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
-      <c r="L5" s="77"/>
-      <c r="M5" s="77"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="77"/>
-      <c r="D6" s="77"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
-      <c r="J6" s="77"/>
-      <c r="K6" s="77"/>
-      <c r="L6" s="77"/>
-      <c r="M6" s="77"/>
-      <c r="N6" s="77"/>
-      <c r="O6" s="77"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="71"/>
+      <c r="O6" s="71"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2294,16 +2291,16 @@
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
       <c r="E8" s="92" t="s">
-        <v>85</v>
-      </c>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="77"/>
-      <c r="K8" s="77"/>
-      <c r="L8" s="77"/>
-      <c r="M8" s="77"/>
+        <v>80</v>
+      </c>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="71"/>
+      <c r="K8" s="71"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="71"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
@@ -2313,26 +2310,26 @@
       <c r="G13" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="55"/>
-      <c r="I13" s="88" t="s">
-        <v>2</v>
-      </c>
-      <c r="J13" s="54"/>
-      <c r="K13" s="55"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="124">
+        <v>46129</v>
+      </c>
+      <c r="J13" s="44"/>
+      <c r="K13" s="45"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="88"/>
-      <c r="H14" s="55"/>
+      <c r="H14" s="45"/>
       <c r="I14" s="88"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="55"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="45"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="88"/>
-      <c r="H15" s="55"/>
+      <c r="H15" s="45"/>
       <c r="I15" s="88"/>
-      <c r="J15" s="54"/>
-      <c r="K15" s="55"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="45"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2342,12 +2339,12 @@
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
       <c r="G17" s="89" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="77"/>
-      <c r="I17" s="77"/>
-      <c r="J17" s="77"/>
-      <c r="K17" s="77"/>
+        <v>94</v>
+      </c>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3361,218 +3358,218 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="100" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="84" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="83"/>
+      <c r="F1" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="81" t="s">
+      <c r="G1" s="83"/>
+      <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="81" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="80"/>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="62"/>
+      <c r="F2" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="62"/>
+      <c r="H2" s="113">
+        <v>46126</v>
+      </c>
+      <c r="I2" s="75" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="76"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="96" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="87"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="105" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="64" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="64" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="65"/>
-      <c r="H2" s="95">
-        <v>46126</v>
-      </c>
-      <c r="I2" s="70" t="s">
-        <v>69</v>
-      </c>
-      <c r="J2" s="71"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="72"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="104"/>
-      <c r="B4" s="105"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="97"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="106" t="s">
+      <c r="B6" s="44"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="47"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="112" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="83"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="99" t="s">
+      <c r="B7" s="44"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="47"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="59" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="57"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="99" t="s">
+      <c r="B8" s="44"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="47"/>
+    </row>
+    <row r="9" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A9" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="59" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="57"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="99" t="s">
+      <c r="B9" s="109" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="59" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="57"/>
-    </row>
-    <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="107" t="s">
+      <c r="C9" s="45"/>
+      <c r="D9" s="97" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="47"/>
+    </row>
+    <row r="10" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A10" s="107"/>
+      <c r="B10" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="98" t="s">
+      <c r="C10" s="45"/>
+      <c r="D10" s="46" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="47"/>
+    </row>
+    <row r="11" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A11" s="108"/>
+      <c r="B11" s="109" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="55"/>
-      <c r="D9" s="113" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="57"/>
-    </row>
-    <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="108"/>
-      <c r="B10" s="98" t="s">
+      <c r="C11" s="45"/>
+      <c r="D11" s="46" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="47"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="105" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="55"/>
-      <c r="D10" s="59" t="s">
-        <v>86</v>
-      </c>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="57"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="109"/>
-      <c r="B11" s="98" t="s">
+      <c r="B12" s="44"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="47"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A13" s="98" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="55"/>
-      <c r="D11" s="59" t="s">
-        <v>86</v>
-      </c>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="57"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="99" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="54"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="59" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="57"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="100" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="101"/>
-      <c r="C13" s="102"/>
-      <c r="D13" s="110" t="s">
-        <v>89</v>
-      </c>
-      <c r="E13" s="101"/>
-      <c r="F13" s="101"/>
-      <c r="G13" s="101"/>
-      <c r="H13" s="101"/>
-      <c r="I13" s="101"/>
-      <c r="J13" s="111"/>
+      <c r="B13" s="94"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="93" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="94"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="95"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4563,6 +4560,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -4571,25 +4587,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4608,72 +4605,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="73" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="81" t="s">
+      <c r="A1" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="84" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="83"/>
+      <c r="F1" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="83"/>
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="81" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="80"/>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="64" t="s">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="62"/>
+      <c r="F2" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="62"/>
+      <c r="H2" s="73">
+        <v>46120</v>
+      </c>
+      <c r="I2" s="75" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="64" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="65"/>
-      <c r="H2" s="68">
-        <v>46120</v>
-      </c>
-      <c r="I2" s="70" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="71"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="72"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="104"/>
-      <c r="B4" s="105"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="97"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6028,72 +6025,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="73" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="81" t="s">
+      <c r="A1" s="78" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="84" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="83"/>
+      <c r="F1" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="83"/>
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="81" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="80"/>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="64" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="64" t="s">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="62"/>
+      <c r="F2" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="62"/>
+      <c r="H2" s="73">
+        <v>46122</v>
+      </c>
+      <c r="I2" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="65"/>
-      <c r="H2" s="68">
-        <v>46122</v>
-      </c>
-      <c r="I2" s="70" t="s">
-        <v>69</v>
-      </c>
-      <c r="J2" s="71"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="72"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="104"/>
-      <c r="B4" s="105"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="97"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7444,484 +7441,484 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="78" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="84" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="83"/>
+      <c r="F1" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="83"/>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="62"/>
+      <c r="F2" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="62"/>
+      <c r="H2" s="73">
+        <v>46122</v>
+      </c>
+      <c r="I2" s="75" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="76"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="81" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="86" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="87"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="81" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="81" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="80"/>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="64" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="64" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="65"/>
-      <c r="H2" s="68">
-        <v>46122</v>
-      </c>
-      <c r="I2" s="70" t="s">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="47"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="67"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="69"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="70"/>
+      <c r="B8" s="71"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="72"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="70"/>
+      <c r="B9" s="71"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="70"/>
+      <c r="B10" s="71"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="70"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="70"/>
+      <c r="B12" s="71"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="72"/>
+    </row>
+    <row r="13" spans="1:10" ht="102" customHeight="1">
+      <c r="A13" s="70"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="59" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="47"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="44"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="46" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="71"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="72"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="76"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="72"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="82" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="83"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="57"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="84"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
-      <c r="J7" s="86"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="76"/>
-      <c r="B8" s="77"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="87"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="76"/>
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="87"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="76"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="87"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="76"/>
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="87"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="76"/>
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="87"/>
-    </row>
-    <row r="13" spans="1:10" ht="102" customHeight="1">
-      <c r="A13" s="76"/>
-      <c r="B13" s="77"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="87"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="53" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="57"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="53" t="s">
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="59" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="15" t="s">
+      <c r="B16" s="44"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="J15" s="16" t="s">
+      <c r="E16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="44"/>
+      <c r="J16" s="47"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A17" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="44"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="17" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="54"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="H16" s="56" t="s">
-        <v>19</v>
-      </c>
-      <c r="I16" s="54"/>
-      <c r="J16" s="57"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="58" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" s="54"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>79</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H17" s="59" t="s">
-        <v>98</v>
-      </c>
-      <c r="I17" s="54"/>
-      <c r="J17" s="57"/>
+        <v>73</v>
+      </c>
+      <c r="H17" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="I17" s="44"/>
+      <c r="J17" s="47"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A18" s="51"/>
+      <c r="A18" s="48"/>
       <c r="B18" s="49"/>
-      <c r="C18" s="52"/>
+      <c r="C18" s="50"/>
       <c r="D18" s="39"/>
       <c r="E18" s="39"/>
       <c r="F18" s="40"/>
       <c r="G18" s="40"/>
-      <c r="H18" s="48"/>
+      <c r="H18" s="51"/>
       <c r="I18" s="49"/>
-      <c r="J18" s="50"/>
+      <c r="J18" s="52"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="60"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="61"/>
+      <c r="A19" s="85"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="66"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="61"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="66"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="43" t="s">
+      <c r="A20" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="54"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="56"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="58" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="63" t="s">
+      <c r="J21" s="38" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="46"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="37" t="s">
+      <c r="B22" s="44"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="J21" s="38" t="s">
+      <c r="E22" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="44"/>
+      <c r="J22" s="47"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="43" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="44"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" s="17" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="54"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22" s="56" t="s">
-        <v>19</v>
-      </c>
-      <c r="I22" s="54"/>
-      <c r="J22" s="57"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="58" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23" s="54"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>79</v>
       </c>
       <c r="F23" s="18"/>
       <c r="G23" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="H23" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="I23" s="54"/>
-      <c r="J23" s="57"/>
+        <v>76</v>
+      </c>
+      <c r="H23" s="46" t="s">
+        <v>84</v>
+      </c>
+      <c r="I23" s="44"/>
+      <c r="J23" s="47"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A24" s="51"/>
+      <c r="A24" s="48"/>
       <c r="B24" s="49"/>
-      <c r="C24" s="52"/>
+      <c r="C24" s="50"/>
       <c r="D24" s="39"/>
       <c r="E24" s="39"/>
       <c r="F24" s="40"/>
       <c r="G24" s="40"/>
-      <c r="H24" s="48"/>
+      <c r="H24" s="51"/>
       <c r="I24" s="49"/>
-      <c r="J24" s="50"/>
+      <c r="J24" s="52"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="60"/>
-      <c r="B25" s="61"/>
-      <c r="C25" s="61"/>
+      <c r="A25" s="85"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="66"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="61"/>
-      <c r="J25" s="61"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="66"/>
+      <c r="J25" s="66"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="43" t="s">
+      <c r="A26" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="54"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
+    </row>
+    <row r="27" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A27" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="56"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="58" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" s="56"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="44"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="44"/>
-      <c r="J26" s="44"/>
-    </row>
-    <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="63" t="s">
+      <c r="J27" s="38" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A28" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="46"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="37" t="s">
+      <c r="B28" s="44"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="J27" s="38" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="53" t="s">
+      <c r="E28" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="54"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="15" t="s">
+      <c r="F28" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="G28" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F28" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G28" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="H28" s="56" t="s">
-        <v>19</v>
-      </c>
-      <c r="I28" s="54"/>
-      <c r="J28" s="57"/>
+      <c r="H28" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" s="44"/>
+      <c r="J28" s="47"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="58" t="s">
-        <v>82</v>
-      </c>
-      <c r="B29" s="54"/>
-      <c r="C29" s="55"/>
+      <c r="A29" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" s="44"/>
+      <c r="C29" s="45"/>
       <c r="D29" s="17" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="H29" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="I29" s="54"/>
-      <c r="J29" s="57"/>
+        <v>90</v>
+      </c>
+      <c r="H29" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="I29" s="44"/>
+      <c r="J29" s="47"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="51"/>
+      <c r="A30" s="48"/>
       <c r="B30" s="49"/>
-      <c r="C30" s="52"/>
+      <c r="C30" s="50"/>
       <c r="D30" s="39"/>
       <c r="E30" s="39"/>
       <c r="F30" s="40"/>
       <c r="G30" s="40"/>
-      <c r="H30" s="48"/>
+      <c r="H30" s="51"/>
       <c r="I30" s="49"/>
-      <c r="J30" s="50"/>
+      <c r="J30" s="52"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1">
       <c r="A31" s="3"/>
@@ -7936,96 +7933,96 @@
       <c r="J31" s="41"/>
     </row>
     <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="43" t="s">
+      <c r="A32" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="54"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="54"/>
+    </row>
+    <row r="33" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A33" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="56"/>
+      <c r="C33" s="57"/>
+      <c r="D33" s="58" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="44"/>
-      <c r="C32" s="44"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="44"/>
-      <c r="H32" s="44"/>
-      <c r="I32" s="44"/>
-      <c r="J32" s="44"/>
-    </row>
-    <row r="33" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A33" s="63" t="s">
+      <c r="J33" s="38" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A34" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="46"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="45" t="s">
+      <c r="B34" s="44"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G34" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H34" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" s="44"/>
+      <c r="J34" s="47"/>
+    </row>
+    <row r="35" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A35" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="E33" s="46"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="47"/>
-      <c r="I33" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="J33" s="38" t="s">
+      <c r="B35" s="44"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="17" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A34" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="B34" s="54"/>
-      <c r="C34" s="55"/>
-      <c r="D34" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G34" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="H34" s="56" t="s">
-        <v>19</v>
-      </c>
-      <c r="I34" s="54"/>
-      <c r="J34" s="57"/>
-    </row>
-    <row r="35" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A35" s="58" t="s">
-        <v>99</v>
-      </c>
-      <c r="B35" s="54"/>
-      <c r="C35" s="55"/>
-      <c r="D35" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>79</v>
       </c>
       <c r="F35" s="18"/>
       <c r="G35" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="H35" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="I35" s="54"/>
-      <c r="J35" s="57"/>
+        <v>78</v>
+      </c>
+      <c r="H35" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="I35" s="44"/>
+      <c r="J35" s="47"/>
     </row>
     <row r="36" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A36" s="51"/>
+      <c r="A36" s="48"/>
       <c r="B36" s="49"/>
-      <c r="C36" s="52"/>
+      <c r="C36" s="50"/>
       <c r="D36" s="39"/>
       <c r="E36" s="39"/>
       <c r="F36" s="40"/>
       <c r="G36" s="40"/>
-      <c r="H36" s="48"/>
+      <c r="H36" s="51"/>
       <c r="I36" s="49"/>
-      <c r="J36" s="50"/>
+      <c r="J36" s="52"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="38" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8991,29 +8988,19 @@
     <row r="998" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="F2:G4"/>
@@ -9030,19 +9017,29 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="D21:H21"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="H34:J34"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9062,182 +9059,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="100" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="84" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="82"/>
+      <c r="M1" s="82"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="84" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="84" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1" s="83"/>
+      <c r="S1" s="84" t="s">
+        <v>7</v>
+      </c>
+      <c r="T1" s="87"/>
+    </row>
+    <row r="2" spans="1:26" ht="18" customHeight="1">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="69"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="63"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="72"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1">
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="102"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="103"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="103"/>
+      <c r="Q4" s="112"/>
+      <c r="R4" s="103"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="122"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="82"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="81" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="81" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="81" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" s="80"/>
-      <c r="Q1" s="81" t="s">
-        <v>8</v>
-      </c>
-      <c r="R1" s="80"/>
-      <c r="S1" s="81" t="s">
-        <v>9</v>
-      </c>
-      <c r="T1" s="83"/>
-    </row>
-    <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="64"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="64"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="64"/>
-      <c r="T2" s="86"/>
-    </row>
-    <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="66"/>
-      <c r="L3" s="77"/>
-      <c r="M3" s="77"/>
-      <c r="N3" s="67"/>
-      <c r="O3" s="66"/>
-      <c r="P3" s="67"/>
-      <c r="Q3" s="66"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="66"/>
-      <c r="T3" s="87"/>
-    </row>
-    <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="104"/>
-      <c r="B4" s="105"/>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="94"/>
-      <c r="K4" s="93"/>
-      <c r="L4" s="105"/>
-      <c r="M4" s="105"/>
-      <c r="N4" s="94"/>
-      <c r="O4" s="93"/>
-      <c r="P4" s="94"/>
-      <c r="Q4" s="93"/>
-      <c r="R4" s="94"/>
-      <c r="S4" s="93"/>
-      <c r="T4" s="118"/>
-    </row>
-    <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="78" t="s">
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
+      <c r="L5" s="82"/>
+      <c r="M5" s="82"/>
+      <c r="N5" s="82"/>
+      <c r="O5" s="82"/>
+      <c r="P5" s="82"/>
+      <c r="Q5" s="82"/>
+      <c r="R5" s="82"/>
+      <c r="S5" s="82"/>
+      <c r="T5" s="87"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="112" t="s">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="44"/>
+      <c r="R6" s="44"/>
+      <c r="S6" s="44"/>
+      <c r="T6" s="47"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="79"/>
-      <c r="K5" s="79"/>
-      <c r="L5" s="79"/>
-      <c r="M5" s="79"/>
-      <c r="N5" s="79"/>
-      <c r="O5" s="79"/>
-      <c r="P5" s="79"/>
-      <c r="Q5" s="79"/>
-      <c r="R5" s="79"/>
-      <c r="S5" s="79"/>
-      <c r="T5" s="83"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="53" t="s">
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="59" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="54"/>
-      <c r="M6" s="54"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="54"/>
-      <c r="P6" s="54"/>
-      <c r="Q6" s="54"/>
-      <c r="R6" s="54"/>
-      <c r="S6" s="54"/>
-      <c r="T6" s="57"/>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="53" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="59" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="54"/>
-      <c r="K7" s="54"/>
-      <c r="L7" s="54"/>
-      <c r="M7" s="54"/>
-      <c r="N7" s="54"/>
-      <c r="O7" s="54"/>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54"/>
-      <c r="R7" s="54"/>
-      <c r="S7" s="54"/>
-      <c r="T7" s="57"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="44"/>
+      <c r="N7" s="44"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="44"/>
+      <c r="Q7" s="44"/>
+      <c r="R7" s="44"/>
+      <c r="S7" s="44"/>
+      <c r="T7" s="47"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9265,11 +9262,11 @@
       <c r="A9" s="19"/>
       <c r="B9" s="20"/>
       <c r="C9" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D9" s="22"/>
       <c r="E9" s="22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F9" s="22"/>
       <c r="G9" s="23"/>
@@ -9299,7 +9296,7 @@
       <c r="C10" s="25"/>
       <c r="D10" s="20"/>
       <c r="E10" s="20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F10" s="20"/>
       <c r="G10" s="26"/>
@@ -9329,7 +9326,7 @@
       <c r="C11" s="25"/>
       <c r="D11" s="20"/>
       <c r="E11" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F11" s="20"/>
       <c r="G11" s="26"/>
@@ -9359,7 +9356,7 @@
       <c r="C12" s="25"/>
       <c r="D12" s="20"/>
       <c r="E12" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F12" s="20"/>
       <c r="G12" s="26"/>
@@ -9389,7 +9386,7 @@
       <c r="C13" s="27"/>
       <c r="D13" s="28"/>
       <c r="E13" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F13" s="28"/>
       <c r="G13" s="29"/>
@@ -9436,79 +9433,79 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="45"/>
+      <c r="C15" s="121" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="45"/>
+      <c r="E15" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="45"/>
+      <c r="G15" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="55"/>
-      <c r="C15" s="121" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="55"/>
-      <c r="E15" s="56" t="s">
+      <c r="H15" s="44"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="55"/>
-      <c r="G15" s="56" t="s">
+      <c r="K15" s="45"/>
+      <c r="L15" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="54"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="56" t="s">
+      <c r="M15" s="44"/>
+      <c r="N15" s="45"/>
+      <c r="O15" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="55"/>
-      <c r="L15" s="56" t="s">
+      <c r="P15" s="44"/>
+      <c r="Q15" s="45"/>
+      <c r="R15" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="54"/>
-      <c r="N15" s="55"/>
-      <c r="O15" s="56" t="s">
+      <c r="S15" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="54"/>
-      <c r="Q15" s="55"/>
-      <c r="R15" s="15" t="s">
+      <c r="T15" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="S15" s="15" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="114">
+        <v>1</v>
+      </c>
+      <c r="B16" s="45"/>
+      <c r="C16" s="115" t="s">
         <v>52</v>
       </c>
-      <c r="T15" s="30" t="s">
+      <c r="D16" s="45"/>
+      <c r="E16" s="115" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="119">
-        <v>1</v>
-      </c>
-      <c r="B16" s="55"/>
-      <c r="C16" s="120" t="s">
+      <c r="F16" s="45"/>
+      <c r="G16" s="120" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="55"/>
-      <c r="E16" s="120" t="s">
+      <c r="H16" s="44"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="120" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="55"/>
-      <c r="G16" s="114" t="s">
+      <c r="K16" s="45"/>
+      <c r="L16" s="118" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="54"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="114" t="s">
+      <c r="M16" s="44"/>
+      <c r="N16" s="45"/>
+      <c r="O16" s="118" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="55"/>
-      <c r="L16" s="116" t="s">
-        <v>58</v>
-      </c>
-      <c r="M16" s="54"/>
-      <c r="N16" s="55"/>
-      <c r="O16" s="116" t="s">
-        <v>59</v>
-      </c>
-      <c r="P16" s="54"/>
-      <c r="Q16" s="55"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="45"/>
       <c r="R16" s="31"/>
       <c r="S16" s="31"/>
       <c r="T16" s="32"/>
@@ -9520,37 +9517,37 @@
       <c r="Z16" s="33"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="119">
+      <c r="A17" s="114">
         <v>2</v>
       </c>
-      <c r="B17" s="55"/>
-      <c r="C17" s="120" t="s">
+      <c r="B17" s="45"/>
+      <c r="C17" s="115" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="45"/>
+      <c r="E17" s="115" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="45"/>
+      <c r="G17" s="120" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="55"/>
-      <c r="E17" s="120" t="s">
+      <c r="H17" s="44"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="120" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="55"/>
-      <c r="G17" s="114" t="s">
+      <c r="K17" s="45"/>
+      <c r="L17" s="118" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="54"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="114" t="s">
+      <c r="M17" s="44"/>
+      <c r="N17" s="45"/>
+      <c r="O17" s="118" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="55"/>
-      <c r="L17" s="116" t="s">
-        <v>64</v>
-      </c>
-      <c r="M17" s="54"/>
-      <c r="N17" s="55"/>
-      <c r="O17" s="116" t="s">
-        <v>65</v>
-      </c>
-      <c r="P17" s="54"/>
-      <c r="Q17" s="55"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="45"/>
       <c r="R17" s="31"/>
       <c r="S17" s="31"/>
       <c r="T17" s="32"/>
@@ -9562,23 +9559,23 @@
       <c r="Z17" s="33"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="119"/>
-      <c r="B18" s="55"/>
-      <c r="C18" s="120"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="120"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="114"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="114"/>
-      <c r="K18" s="55"/>
-      <c r="L18" s="116"/>
-      <c r="M18" s="54"/>
-      <c r="N18" s="55"/>
-      <c r="O18" s="116"/>
-      <c r="P18" s="54"/>
-      <c r="Q18" s="55"/>
+      <c r="A18" s="114"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="115"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="115"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="120"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="120"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="118"/>
+      <c r="M18" s="44"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="44"/>
+      <c r="Q18" s="45"/>
       <c r="R18" s="31"/>
       <c r="S18" s="31"/>
       <c r="T18" s="32"/>
@@ -9590,23 +9587,23 @@
       <c r="Z18" s="33"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="119"/>
-      <c r="B19" s="55"/>
-      <c r="C19" s="120"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="120"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="114"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="114"/>
-      <c r="K19" s="55"/>
-      <c r="L19" s="116"/>
-      <c r="M19" s="54"/>
-      <c r="N19" s="55"/>
-      <c r="O19" s="116"/>
-      <c r="P19" s="54"/>
-      <c r="Q19" s="55"/>
+      <c r="A19" s="114"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="115"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="115"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="120"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="120"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="118"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="45"/>
+      <c r="O19" s="118"/>
+      <c r="P19" s="44"/>
+      <c r="Q19" s="45"/>
       <c r="R19" s="31"/>
       <c r="S19" s="31"/>
       <c r="T19" s="32"/>
@@ -9618,23 +9615,23 @@
       <c r="Z19" s="33"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="119"/>
-      <c r="B20" s="55"/>
-      <c r="C20" s="120"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="120"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="114"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="114"/>
-      <c r="K20" s="55"/>
-      <c r="L20" s="116"/>
-      <c r="M20" s="54"/>
-      <c r="N20" s="55"/>
-      <c r="O20" s="116"/>
-      <c r="P20" s="54"/>
-      <c r="Q20" s="55"/>
+      <c r="A20" s="114"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="115"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="115"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="120"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="118"/>
+      <c r="M20" s="44"/>
+      <c r="N20" s="45"/>
+      <c r="O20" s="118"/>
+      <c r="P20" s="44"/>
+      <c r="Q20" s="45"/>
       <c r="R20" s="31"/>
       <c r="S20" s="31"/>
       <c r="T20" s="32"/>
@@ -9646,23 +9643,23 @@
       <c r="Z20" s="33"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="119"/>
-      <c r="B21" s="55"/>
-      <c r="C21" s="120"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="120"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="114"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="114"/>
-      <c r="K21" s="55"/>
-      <c r="L21" s="116"/>
-      <c r="M21" s="54"/>
-      <c r="N21" s="55"/>
-      <c r="O21" s="116"/>
-      <c r="P21" s="54"/>
-      <c r="Q21" s="55"/>
+      <c r="A21" s="114"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="115"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="115"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="120"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="120"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="118"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="45"/>
+      <c r="O21" s="118"/>
+      <c r="P21" s="44"/>
+      <c r="Q21" s="45"/>
       <c r="R21" s="31"/>
       <c r="S21" s="31"/>
       <c r="T21" s="32"/>
@@ -9674,23 +9671,23 @@
       <c r="Z21" s="33"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="119"/>
-      <c r="B22" s="55"/>
-      <c r="C22" s="120"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="120"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="114"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="114"/>
-      <c r="K22" s="55"/>
-      <c r="L22" s="116"/>
-      <c r="M22" s="54"/>
-      <c r="N22" s="55"/>
-      <c r="O22" s="116"/>
-      <c r="P22" s="54"/>
-      <c r="Q22" s="55"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="115"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="115"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="120"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="120"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="118"/>
+      <c r="M22" s="44"/>
+      <c r="N22" s="45"/>
+      <c r="O22" s="118"/>
+      <c r="P22" s="44"/>
+      <c r="Q22" s="45"/>
       <c r="R22" s="31"/>
       <c r="S22" s="31"/>
       <c r="T22" s="32"/>
@@ -9702,23 +9699,23 @@
       <c r="Z22" s="33"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="119"/>
-      <c r="B23" s="55"/>
-      <c r="C23" s="120"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="120"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="114"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="55"/>
-      <c r="J23" s="114"/>
-      <c r="K23" s="55"/>
-      <c r="L23" s="116"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="55"/>
-      <c r="O23" s="116"/>
-      <c r="P23" s="54"/>
-      <c r="Q23" s="55"/>
+      <c r="A23" s="114"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="115"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="115"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="120"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="120"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="118"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="118"/>
+      <c r="P23" s="44"/>
+      <c r="Q23" s="45"/>
       <c r="R23" s="31"/>
       <c r="S23" s="31"/>
       <c r="T23" s="32"/>
@@ -9730,23 +9727,23 @@
       <c r="Z23" s="33"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="119"/>
-      <c r="B24" s="55"/>
-      <c r="C24" s="120"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="120"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="114"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="55"/>
-      <c r="J24" s="114"/>
-      <c r="K24" s="55"/>
-      <c r="L24" s="116"/>
-      <c r="M24" s="54"/>
-      <c r="N24" s="55"/>
-      <c r="O24" s="116"/>
-      <c r="P24" s="54"/>
-      <c r="Q24" s="55"/>
+      <c r="A24" s="114"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="115"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="115"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="120"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="120"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="118"/>
+      <c r="M24" s="44"/>
+      <c r="N24" s="45"/>
+      <c r="O24" s="118"/>
+      <c r="P24" s="44"/>
+      <c r="Q24" s="45"/>
       <c r="R24" s="31"/>
       <c r="S24" s="31"/>
       <c r="T24" s="32"/>
@@ -9758,23 +9755,23 @@
       <c r="Z24" s="33"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="119"/>
-      <c r="B25" s="55"/>
-      <c r="C25" s="120"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="120"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="114"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="55"/>
-      <c r="J25" s="114"/>
-      <c r="K25" s="55"/>
-      <c r="L25" s="116"/>
-      <c r="M25" s="54"/>
-      <c r="N25" s="55"/>
-      <c r="O25" s="116"/>
-      <c r="P25" s="54"/>
-      <c r="Q25" s="55"/>
+      <c r="A25" s="114"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="115"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="115"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="120"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="120"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="118"/>
+      <c r="M25" s="44"/>
+      <c r="N25" s="45"/>
+      <c r="O25" s="118"/>
+      <c r="P25" s="44"/>
+      <c r="Q25" s="45"/>
       <c r="R25" s="31"/>
       <c r="S25" s="31"/>
       <c r="T25" s="32"/>
@@ -9786,23 +9783,23 @@
       <c r="Z25" s="33"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="119"/>
-      <c r="B26" s="55"/>
-      <c r="C26" s="120"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="120"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="114"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="55"/>
-      <c r="J26" s="114"/>
-      <c r="K26" s="55"/>
-      <c r="L26" s="116"/>
-      <c r="M26" s="54"/>
-      <c r="N26" s="55"/>
-      <c r="O26" s="116"/>
-      <c r="P26" s="54"/>
-      <c r="Q26" s="55"/>
+      <c r="A26" s="114"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="115"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="115"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="120"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="120"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="118"/>
+      <c r="M26" s="44"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="118"/>
+      <c r="P26" s="44"/>
+      <c r="Q26" s="45"/>
       <c r="R26" s="31"/>
       <c r="S26" s="31"/>
       <c r="T26" s="32"/>
@@ -9814,23 +9811,23 @@
       <c r="Z26" s="33"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="119"/>
-      <c r="B27" s="55"/>
-      <c r="C27" s="120"/>
-      <c r="D27" s="55"/>
-      <c r="E27" s="120"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="114"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="55"/>
-      <c r="J27" s="114"/>
-      <c r="K27" s="55"/>
-      <c r="L27" s="116"/>
-      <c r="M27" s="54"/>
-      <c r="N27" s="55"/>
-      <c r="O27" s="116"/>
-      <c r="P27" s="54"/>
-      <c r="Q27" s="55"/>
+      <c r="A27" s="114"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="115"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="120"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="120"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="118"/>
+      <c r="M27" s="44"/>
+      <c r="N27" s="45"/>
+      <c r="O27" s="118"/>
+      <c r="P27" s="44"/>
+      <c r="Q27" s="45"/>
       <c r="R27" s="31"/>
       <c r="S27" s="31"/>
       <c r="T27" s="32"/>
@@ -9842,23 +9839,23 @@
       <c r="Z27" s="33"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="119"/>
-      <c r="B28" s="55"/>
-      <c r="C28" s="120"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="120"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="114"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="114"/>
-      <c r="K28" s="55"/>
-      <c r="L28" s="116"/>
-      <c r="M28" s="54"/>
-      <c r="N28" s="55"/>
-      <c r="O28" s="116"/>
-      <c r="P28" s="54"/>
-      <c r="Q28" s="55"/>
+      <c r="A28" s="114"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="115"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="115"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="120"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="118"/>
+      <c r="M28" s="44"/>
+      <c r="N28" s="45"/>
+      <c r="O28" s="118"/>
+      <c r="P28" s="44"/>
+      <c r="Q28" s="45"/>
       <c r="R28" s="31"/>
       <c r="S28" s="31"/>
       <c r="T28" s="32"/>
@@ -9870,23 +9867,23 @@
       <c r="Z28" s="33"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="119"/>
-      <c r="B29" s="55"/>
-      <c r="C29" s="120"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="120"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="114"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="55"/>
-      <c r="J29" s="114"/>
-      <c r="K29" s="55"/>
-      <c r="L29" s="116"/>
-      <c r="M29" s="54"/>
-      <c r="N29" s="55"/>
-      <c r="O29" s="116"/>
-      <c r="P29" s="54"/>
-      <c r="Q29" s="55"/>
+      <c r="A29" s="114"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="115"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="115"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="120"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="120"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="118"/>
+      <c r="M29" s="44"/>
+      <c r="N29" s="45"/>
+      <c r="O29" s="118"/>
+      <c r="P29" s="44"/>
+      <c r="Q29" s="45"/>
       <c r="R29" s="31"/>
       <c r="S29" s="31"/>
       <c r="T29" s="32"/>
@@ -9898,23 +9895,23 @@
       <c r="Z29" s="33"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="119"/>
-      <c r="B30" s="55"/>
-      <c r="C30" s="120"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="120"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="114"/>
-      <c r="H30" s="54"/>
-      <c r="I30" s="55"/>
-      <c r="J30" s="114"/>
-      <c r="K30" s="55"/>
-      <c r="L30" s="116"/>
-      <c r="M30" s="54"/>
-      <c r="N30" s="55"/>
-      <c r="O30" s="116"/>
-      <c r="P30" s="54"/>
-      <c r="Q30" s="55"/>
+      <c r="A30" s="114"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="115"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="115"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="120"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="120"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="118"/>
+      <c r="M30" s="44"/>
+      <c r="N30" s="45"/>
+      <c r="O30" s="118"/>
+      <c r="P30" s="44"/>
+      <c r="Q30" s="45"/>
       <c r="R30" s="31"/>
       <c r="S30" s="31"/>
       <c r="T30" s="32"/>
@@ -9926,23 +9923,23 @@
       <c r="Z30" s="33"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="122"/>
-      <c r="B31" s="102"/>
-      <c r="C31" s="123"/>
-      <c r="D31" s="102"/>
-      <c r="E31" s="123"/>
-      <c r="F31" s="102"/>
-      <c r="G31" s="115"/>
-      <c r="H31" s="101"/>
-      <c r="I31" s="102"/>
-      <c r="J31" s="115"/>
-      <c r="K31" s="102"/>
-      <c r="L31" s="117"/>
-      <c r="M31" s="101"/>
-      <c r="N31" s="102"/>
-      <c r="O31" s="117"/>
-      <c r="P31" s="101"/>
-      <c r="Q31" s="102"/>
+      <c r="A31" s="116"/>
+      <c r="B31" s="99"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="99"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="99"/>
+      <c r="G31" s="123"/>
+      <c r="H31" s="94"/>
+      <c r="I31" s="99"/>
+      <c r="J31" s="123"/>
+      <c r="K31" s="99"/>
+      <c r="L31" s="119"/>
+      <c r="M31" s="94"/>
+      <c r="N31" s="99"/>
+      <c r="O31" s="119"/>
+      <c r="P31" s="94"/>
+      <c r="Q31" s="99"/>
       <c r="R31" s="34"/>
       <c r="S31" s="34"/>
       <c r="T31" s="35"/>
@@ -10940,6 +10937,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -10964,118 +11073,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_タスク詳細画面.xlsx
+++ b/document/成果物ドキュメント_タスク詳細画面.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8455083-22C8-48ED-BBD0-C7E03B45EADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A0D65C-9636-4772-A00E-F423A2C3F540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -381,10 +381,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>１～</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>ログインユーザーと投稿者が一致していた場合表示する</t>
     <rPh sb="9" eb="12">
       <t>トウコウシャ</t>
@@ -472,6 +468,10 @@
     <rPh sb="57" eb="59">
       <t>ヒョウジ</t>
     </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>(コメントのID)</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1524,77 +1524,209 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1605,137 +1737,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1743,32 +1761,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2192,21 +2192,21 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="90" t="s">
+      <c r="C2" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="91"/>
-      <c r="L2" s="91"/>
-      <c r="M2" s="91"/>
-      <c r="N2" s="91"/>
-      <c r="O2" s="91"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="87"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
@@ -2290,7 +2290,7 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="92" t="s">
+      <c r="E8" s="88" t="s">
         <v>80</v>
       </c>
       <c r="F8" s="71"/>
@@ -2307,29 +2307,29 @@
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="88" t="s">
+      <c r="G13" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="45"/>
-      <c r="I13" s="124">
+      <c r="H13" s="59"/>
+      <c r="I13" s="89">
         <v>46129</v>
       </c>
-      <c r="J13" s="44"/>
-      <c r="K13" s="45"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="59"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="88"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="88"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="45"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="84"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="59"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="88"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="88"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="45"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="59"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2338,8 +2338,8 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="89" t="s">
-        <v>94</v>
+      <c r="G17" s="85" t="s">
+        <v>93</v>
       </c>
       <c r="H17" s="71"/>
       <c r="I17" s="71"/>
@@ -3358,19 +3358,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="84" t="s">
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="83"/>
+      <c r="G1" s="44"/>
       <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
@@ -3384,192 +3384,192 @@
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="70"/>
       <c r="B2" s="71"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="61" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="61" t="s">
+      <c r="E2" s="46"/>
+      <c r="F2" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="62"/>
-      <c r="H2" s="113">
+      <c r="G2" s="46"/>
+      <c r="H2" s="51">
         <v>46126</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="70"/>
       <c r="B3" s="71"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="57"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="104" t="s">
+      <c r="A5" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="96" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="81" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="82"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="61"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="62" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="63"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="60" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="61"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="63"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="61"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="62" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="63"/>
+    </row>
+    <row r="9" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A9" s="76" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="58" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="59"/>
+      <c r="D9" s="83" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="87"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="105" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="47"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="105" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="46" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="47"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="105" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="46" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="47"/>
-    </row>
-    <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="106" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="109" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="97" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="47"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="63"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="107"/>
-      <c r="B10" s="109" t="s">
+      <c r="A10" s="77"/>
+      <c r="B10" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="46" t="s">
+      <c r="C10" s="59"/>
+      <c r="D10" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="47"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="63"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="108"/>
-      <c r="B11" s="109" t="s">
+      <c r="A11" s="78"/>
+      <c r="B11" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="46" t="s">
+      <c r="C11" s="59"/>
+      <c r="D11" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="47"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="63"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="105" t="s">
+      <c r="A12" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="44"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="46" t="s">
+      <c r="B12" s="61"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="47"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="63"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="98" t="s">
+      <c r="A13" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="94"/>
-      <c r="C13" s="99"/>
-      <c r="D13" s="93" t="s">
+      <c r="B13" s="65"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="95"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="80"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4560,17 +4560,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4579,14 +4576,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4605,19 +4605,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="84" t="s">
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="83"/>
+      <c r="G1" s="44"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -4631,46 +4631,46 @@
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="70"/>
       <c r="B2" s="71"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="61" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="61" t="s">
+      <c r="E2" s="46"/>
+      <c r="F2" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="62"/>
-      <c r="H2" s="73">
+      <c r="G2" s="46"/>
+      <c r="H2" s="90">
         <v>46120</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="70"/>
       <c r="B3" s="71"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="57"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6025,19 +6025,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="84" t="s">
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="83"/>
+      <c r="G1" s="44"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -6051,46 +6051,46 @@
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="70"/>
       <c r="B2" s="71"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="61" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="61" t="s">
+      <c r="E2" s="46"/>
+      <c r="F2" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="62"/>
-      <c r="H2" s="73">
+      <c r="G2" s="46"/>
+      <c r="H2" s="90">
         <v>46122</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="70"/>
       <c r="B3" s="71"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="57"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7441,19 +7441,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="84" t="s">
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="83"/>
+      <c r="G1" s="44"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -7467,88 +7467,88 @@
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="70"/>
       <c r="B2" s="71"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="61" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="61" t="s">
+      <c r="E2" s="46"/>
+      <c r="F2" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="62"/>
-      <c r="H2" s="73">
+      <c r="G2" s="46"/>
+      <c r="H2" s="90">
         <v>46122</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="70"/>
       <c r="B3" s="71"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
       <c r="A4" s="70"/>
       <c r="B4" s="71"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="56"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="109" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="86" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="110" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="87"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="82"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="47"/>
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="63"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="67"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="69"/>
+      <c r="A7" s="111"/>
+      <c r="B7" s="112"/>
+      <c r="C7" s="112"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="112"/>
+      <c r="F7" s="112"/>
+      <c r="G7" s="112"/>
+      <c r="H7" s="112"/>
+      <c r="I7" s="112"/>
+      <c r="J7" s="113"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="70"/>
@@ -7560,7 +7560,7 @@
       <c r="G8" s="71"/>
       <c r="H8" s="71"/>
       <c r="I8" s="71"/>
-      <c r="J8" s="72"/>
+      <c r="J8" s="114"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="70"/>
@@ -7572,7 +7572,7 @@
       <c r="G9" s="71"/>
       <c r="H9" s="71"/>
       <c r="I9" s="71"/>
-      <c r="J9" s="72"/>
+      <c r="J9" s="114"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="70"/>
@@ -7584,7 +7584,7 @@
       <c r="G10" s="71"/>
       <c r="H10" s="71"/>
       <c r="I10" s="71"/>
-      <c r="J10" s="72"/>
+      <c r="J10" s="114"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="70"/>
@@ -7596,7 +7596,7 @@
       <c r="G11" s="71"/>
       <c r="H11" s="71"/>
       <c r="I11" s="71"/>
-      <c r="J11" s="72"/>
+      <c r="J11" s="114"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="70"/>
@@ -7608,7 +7608,7 @@
       <c r="G12" s="71"/>
       <c r="H12" s="71"/>
       <c r="I12" s="71"/>
-      <c r="J12" s="72"/>
+      <c r="J12" s="114"/>
     </row>
     <row r="13" spans="1:10" ht="102" customHeight="1">
       <c r="A13" s="70"/>
@@ -7620,35 +7620,35 @@
       <c r="G13" s="71"/>
       <c r="H13" s="71"/>
       <c r="I13" s="71"/>
-      <c r="J13" s="72"/>
+      <c r="J13" s="114"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="59" t="s">
+      <c r="A14" s="102" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="47"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="63"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="59" t="s">
+      <c r="A15" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="44"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="46" t="s">
+      <c r="B15" s="61"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="45"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="59"/>
       <c r="I15" s="15" t="s">
         <v>25</v>
       </c>
@@ -7657,11 +7657,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="45"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="59"/>
       <c r="D16" s="15" t="s">
         <v>27</v>
       </c>
@@ -7674,18 +7674,18 @@
       <c r="G16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="60" t="s">
+      <c r="H16" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="44"/>
-      <c r="J16" s="47"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="63"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="43" t="s">
+      <c r="A17" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="45"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="59"/>
       <c r="D17" s="17" t="s">
         <v>73</v>
       </c>
@@ -7696,63 +7696,63 @@
       <c r="G17" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H17" s="46" t="s">
-        <v>92</v>
-      </c>
-      <c r="I17" s="44"/>
-      <c r="J17" s="47"/>
+      <c r="H17" s="62" t="s">
+        <v>91</v>
+      </c>
+      <c r="I17" s="61"/>
+      <c r="J17" s="63"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A18" s="48"/>
-      <c r="B18" s="49"/>
-      <c r="C18" s="50"/>
+      <c r="A18" s="100"/>
+      <c r="B18" s="98"/>
+      <c r="C18" s="101"/>
       <c r="D18" s="39"/>
       <c r="E18" s="39"/>
       <c r="F18" s="40"/>
       <c r="G18" s="40"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="52"/>
+      <c r="H18" s="97"/>
+      <c r="I18" s="98"/>
+      <c r="J18" s="99"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="85"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="66"/>
+      <c r="A19" s="105"/>
+      <c r="B19" s="106"/>
+      <c r="C19" s="106"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
-      <c r="H19" s="65"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="66"/>
+      <c r="H19" s="107"/>
+      <c r="I19" s="106"/>
+      <c r="J19" s="106"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="53" t="s">
+      <c r="A20" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="54"/>
+      <c r="B20" s="93"/>
+      <c r="C20" s="93"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="93"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="93"/>
+      <c r="J20" s="93"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="55" t="s">
+      <c r="A21" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="56"/>
-      <c r="C21" s="57"/>
-      <c r="D21" s="58" t="s">
+      <c r="B21" s="95"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="94" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="57"/>
+      <c r="E21" s="95"/>
+      <c r="F21" s="95"/>
+      <c r="G21" s="95"/>
+      <c r="H21" s="96"/>
       <c r="I21" s="37" t="s">
         <v>25</v>
       </c>
@@ -7761,11 +7761,11 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="44"/>
-      <c r="C22" s="45"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="59"/>
       <c r="D22" s="15" t="s">
         <v>27</v>
       </c>
@@ -7778,18 +7778,18 @@
       <c r="G22" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="H22" s="60" t="s">
+      <c r="H22" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="I22" s="44"/>
-      <c r="J22" s="47"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="63"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="43" t="s">
+      <c r="A23" s="104" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="44"/>
-      <c r="C23" s="45"/>
+      <c r="B23" s="61"/>
+      <c r="C23" s="59"/>
       <c r="D23" s="17" t="s">
         <v>76</v>
       </c>
@@ -7800,63 +7800,63 @@
       <c r="G23" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="H23" s="46" t="s">
+      <c r="H23" s="62" t="s">
         <v>84</v>
       </c>
-      <c r="I23" s="44"/>
-      <c r="J23" s="47"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="63"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A24" s="48"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="50"/>
+      <c r="A24" s="100"/>
+      <c r="B24" s="98"/>
+      <c r="C24" s="101"/>
       <c r="D24" s="39"/>
       <c r="E24" s="39"/>
       <c r="F24" s="40"/>
       <c r="G24" s="40"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="52"/>
+      <c r="H24" s="97"/>
+      <c r="I24" s="98"/>
+      <c r="J24" s="99"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="85"/>
-      <c r="B25" s="66"/>
-      <c r="C25" s="66"/>
+      <c r="A25" s="105"/>
+      <c r="B25" s="106"/>
+      <c r="C25" s="106"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
-      <c r="H25" s="65"/>
-      <c r="I25" s="66"/>
-      <c r="J25" s="66"/>
+      <c r="H25" s="107"/>
+      <c r="I25" s="106"/>
+      <c r="J25" s="106"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="53" t="s">
+      <c r="A26" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="54"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="54"/>
-      <c r="J26" s="54"/>
+      <c r="B26" s="93"/>
+      <c r="C26" s="93"/>
+      <c r="D26" s="93"/>
+      <c r="E26" s="93"/>
+      <c r="F26" s="93"/>
+      <c r="G26" s="93"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="93"/>
+      <c r="J26" s="93"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="55" t="s">
+      <c r="A27" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="56"/>
-      <c r="C27" s="57"/>
-      <c r="D27" s="58" t="s">
+      <c r="B27" s="95"/>
+      <c r="C27" s="96"/>
+      <c r="D27" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="E27" s="56"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="57"/>
+      <c r="E27" s="95"/>
+      <c r="F27" s="95"/>
+      <c r="G27" s="95"/>
+      <c r="H27" s="96"/>
       <c r="I27" s="37" t="s">
         <v>25</v>
       </c>
@@ -7865,11 +7865,11 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="59" t="s">
+      <c r="A28" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="44"/>
-      <c r="C28" s="45"/>
+      <c r="B28" s="61"/>
+      <c r="C28" s="59"/>
       <c r="D28" s="15" t="s">
         <v>27</v>
       </c>
@@ -7882,43 +7882,43 @@
       <c r="G28" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="H28" s="60" t="s">
+      <c r="H28" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="I28" s="44"/>
-      <c r="J28" s="47"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="63"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="43" t="s">
+      <c r="A29" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="B29" s="44"/>
-      <c r="C29" s="45"/>
+      <c r="B29" s="61"/>
+      <c r="C29" s="59"/>
       <c r="D29" s="17" t="s">
         <v>89</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="H29" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="H29" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="I29" s="44"/>
-      <c r="J29" s="47"/>
+      <c r="I29" s="61"/>
+      <c r="J29" s="63"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="48"/>
-      <c r="B30" s="49"/>
-      <c r="C30" s="50"/>
+      <c r="A30" s="100"/>
+      <c r="B30" s="98"/>
+      <c r="C30" s="101"/>
       <c r="D30" s="39"/>
       <c r="E30" s="39"/>
       <c r="F30" s="40"/>
       <c r="G30" s="40"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="52"/>
+      <c r="H30" s="97"/>
+      <c r="I30" s="98"/>
+      <c r="J30" s="99"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1">
       <c r="A31" s="3"/>
@@ -7933,32 +7933,32 @@
       <c r="J31" s="41"/>
     </row>
     <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="53" t="s">
+      <c r="A32" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="54"/>
-      <c r="C32" s="54"/>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="54"/>
-      <c r="J32" s="54"/>
+      <c r="B32" s="93"/>
+      <c r="C32" s="93"/>
+      <c r="D32" s="93"/>
+      <c r="E32" s="93"/>
+      <c r="F32" s="93"/>
+      <c r="G32" s="93"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="93"/>
+      <c r="J32" s="93"/>
     </row>
     <row r="33" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A33" s="55" t="s">
+      <c r="A33" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="56"/>
-      <c r="C33" s="57"/>
-      <c r="D33" s="58" t="s">
+      <c r="B33" s="95"/>
+      <c r="C33" s="96"/>
+      <c r="D33" s="94" t="s">
         <v>87</v>
       </c>
-      <c r="E33" s="56"/>
-      <c r="F33" s="56"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="57"/>
+      <c r="E33" s="95"/>
+      <c r="F33" s="95"/>
+      <c r="G33" s="95"/>
+      <c r="H33" s="96"/>
       <c r="I33" s="37" t="s">
         <v>25</v>
       </c>
@@ -7967,11 +7967,11 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A34" s="59" t="s">
+      <c r="A34" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="44"/>
-      <c r="C34" s="45"/>
+      <c r="B34" s="61"/>
+      <c r="C34" s="59"/>
       <c r="D34" s="15" t="s">
         <v>27</v>
       </c>
@@ -7984,18 +7984,18 @@
       <c r="G34" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="H34" s="60" t="s">
+      <c r="H34" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="I34" s="44"/>
-      <c r="J34" s="47"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="63"/>
     </row>
     <row r="35" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A35" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="B35" s="44"/>
-      <c r="C35" s="45"/>
+      <c r="A35" s="104" t="s">
+        <v>92</v>
+      </c>
+      <c r="B35" s="61"/>
+      <c r="C35" s="59"/>
       <c r="D35" s="17" t="s">
         <v>78</v>
       </c>
@@ -8006,23 +8006,23 @@
       <c r="G35" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H35" s="46" t="s">
+      <c r="H35" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="I35" s="44"/>
-      <c r="J35" s="47"/>
+      <c r="I35" s="61"/>
+      <c r="J35" s="63"/>
     </row>
     <row r="36" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A36" s="48"/>
-      <c r="B36" s="49"/>
-      <c r="C36" s="50"/>
+      <c r="A36" s="100"/>
+      <c r="B36" s="98"/>
+      <c r="C36" s="101"/>
       <c r="D36" s="39"/>
       <c r="E36" s="39"/>
       <c r="F36" s="40"/>
       <c r="G36" s="40"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="49"/>
-      <c r="J36" s="52"/>
+      <c r="H36" s="97"/>
+      <c r="I36" s="98"/>
+      <c r="J36" s="99"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="38" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8988,19 +8988,29 @@
     <row r="998" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="F2:G4"/>
@@ -9017,29 +9027,19 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="D21:H21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A27:C27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9059,38 +9059,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="84" t="s">
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="84" t="s">
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="84" t="s">
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="84" t="s">
+      <c r="P1" s="44"/>
+      <c r="Q1" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="83"/>
-      <c r="S1" s="84" t="s">
+      <c r="R1" s="44"/>
+      <c r="S1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="87"/>
+      <c r="T1" s="82"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="70"/>
@@ -9098,21 +9098,21 @@
       <c r="C2" s="71"/>
       <c r="D2" s="71"/>
       <c r="E2" s="71"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="69"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="112"/>
+      <c r="I2" s="112"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="112"/>
+      <c r="M2" s="112"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="113"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="70"/>
@@ -9120,121 +9120,121 @@
       <c r="C3" s="71"/>
       <c r="D3" s="71"/>
       <c r="E3" s="71"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="63"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="47"/>
       <c r="H3" s="71"/>
       <c r="I3" s="71"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="63"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="47"/>
       <c r="L3" s="71"/>
       <c r="M3" s="71"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="72"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="114"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="103"/>
-      <c r="K4" s="112"/>
-      <c r="L4" s="102"/>
-      <c r="M4" s="102"/>
-      <c r="N4" s="103"/>
-      <c r="O4" s="112"/>
-      <c r="P4" s="103"/>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="103"/>
-      <c r="S4" s="112"/>
-      <c r="T4" s="122"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="50"/>
+      <c r="O4" s="49"/>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="49"/>
+      <c r="R4" s="50"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="119"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="96" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="81" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="82"/>
-      <c r="K5" s="82"/>
-      <c r="L5" s="82"/>
-      <c r="M5" s="82"/>
-      <c r="N5" s="82"/>
-      <c r="O5" s="82"/>
-      <c r="P5" s="82"/>
-      <c r="Q5" s="82"/>
-      <c r="R5" s="82"/>
-      <c r="S5" s="82"/>
-      <c r="T5" s="87"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="75"/>
+      <c r="M5" s="75"/>
+      <c r="N5" s="75"/>
+      <c r="O5" s="75"/>
+      <c r="P5" s="75"/>
+      <c r="Q5" s="75"/>
+      <c r="R5" s="75"/>
+      <c r="S5" s="75"/>
+      <c r="T5" s="82"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="46" t="s">
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="44"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="47"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="61"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="63"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="102" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="46" t="s">
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="44"/>
-      <c r="S7" s="44"/>
-      <c r="T7" s="47"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="61"/>
+      <c r="N7" s="61"/>
+      <c r="O7" s="61"/>
+      <c r="P7" s="61"/>
+      <c r="Q7" s="61"/>
+      <c r="R7" s="61"/>
+      <c r="S7" s="61"/>
+      <c r="T7" s="63"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9433,37 +9433,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="59" t="s">
+      <c r="A15" s="102" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="121" t="s">
+      <c r="B15" s="59"/>
+      <c r="C15" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="45"/>
-      <c r="E15" s="60" t="s">
+      <c r="D15" s="59"/>
+      <c r="E15" s="103" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="45"/>
-      <c r="G15" s="60" t="s">
+      <c r="F15" s="59"/>
+      <c r="G15" s="103" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="44"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="60" t="s">
+      <c r="H15" s="61"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="103" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="45"/>
-      <c r="L15" s="60" t="s">
+      <c r="K15" s="59"/>
+      <c r="L15" s="103" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="44"/>
-      <c r="N15" s="45"/>
-      <c r="O15" s="60" t="s">
+      <c r="M15" s="61"/>
+      <c r="N15" s="59"/>
+      <c r="O15" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="44"/>
-      <c r="Q15" s="45"/>
+      <c r="P15" s="61"/>
+      <c r="Q15" s="59"/>
       <c r="R15" s="15" t="s">
         <v>49</v>
       </c>
@@ -9475,37 +9475,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="114">
+      <c r="A16" s="120">
         <v>1</v>
       </c>
-      <c r="B16" s="45"/>
-      <c r="C16" s="115" t="s">
+      <c r="B16" s="59"/>
+      <c r="C16" s="121" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="45"/>
-      <c r="E16" s="115" t="s">
+      <c r="D16" s="59"/>
+      <c r="E16" s="121" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="45"/>
-      <c r="G16" s="120" t="s">
+      <c r="F16" s="59"/>
+      <c r="G16" s="115" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="44"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="120" t="s">
+      <c r="H16" s="61"/>
+      <c r="I16" s="59"/>
+      <c r="J16" s="115" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="45"/>
-      <c r="L16" s="118" t="s">
+      <c r="K16" s="59"/>
+      <c r="L16" s="117" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="44"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="118" t="s">
+      <c r="M16" s="61"/>
+      <c r="N16" s="59"/>
+      <c r="O16" s="117" t="s">
         <v>57</v>
       </c>
-      <c r="P16" s="44"/>
-      <c r="Q16" s="45"/>
+      <c r="P16" s="61"/>
+      <c r="Q16" s="59"/>
       <c r="R16" s="31"/>
       <c r="S16" s="31"/>
       <c r="T16" s="32"/>
@@ -9517,37 +9517,37 @@
       <c r="Z16" s="33"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="114">
+      <c r="A17" s="120">
         <v>2</v>
       </c>
-      <c r="B17" s="45"/>
-      <c r="C17" s="115" t="s">
+      <c r="B17" s="59"/>
+      <c r="C17" s="121" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="45"/>
-      <c r="E17" s="115" t="s">
+      <c r="D17" s="59"/>
+      <c r="E17" s="121" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="45"/>
-      <c r="G17" s="120" t="s">
+      <c r="F17" s="59"/>
+      <c r="G17" s="115" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="44"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="120" t="s">
+      <c r="H17" s="61"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="115" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="45"/>
-      <c r="L17" s="118" t="s">
+      <c r="K17" s="59"/>
+      <c r="L17" s="117" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="44"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="118" t="s">
+      <c r="M17" s="61"/>
+      <c r="N17" s="59"/>
+      <c r="O17" s="117" t="s">
         <v>63</v>
       </c>
-      <c r="P17" s="44"/>
-      <c r="Q17" s="45"/>
+      <c r="P17" s="61"/>
+      <c r="Q17" s="59"/>
       <c r="R17" s="31"/>
       <c r="S17" s="31"/>
       <c r="T17" s="32"/>
@@ -9559,23 +9559,23 @@
       <c r="Z17" s="33"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="114"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="115"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="115"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="120"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="120"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="44"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="44"/>
-      <c r="Q18" s="45"/>
+      <c r="A18" s="120"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="121"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="115"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="59"/>
+      <c r="J18" s="115"/>
+      <c r="K18" s="59"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="61"/>
+      <c r="N18" s="59"/>
+      <c r="O18" s="117"/>
+      <c r="P18" s="61"/>
+      <c r="Q18" s="59"/>
       <c r="R18" s="31"/>
       <c r="S18" s="31"/>
       <c r="T18" s="32"/>
@@ -9587,23 +9587,23 @@
       <c r="Z18" s="33"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="114"/>
-      <c r="B19" s="45"/>
-      <c r="C19" s="115"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="115"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="120"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="120"/>
-      <c r="K19" s="45"/>
-      <c r="L19" s="118"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="45"/>
-      <c r="O19" s="118"/>
-      <c r="P19" s="44"/>
-      <c r="Q19" s="45"/>
+      <c r="A19" s="120"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="121"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="115"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="115"/>
+      <c r="K19" s="59"/>
+      <c r="L19" s="117"/>
+      <c r="M19" s="61"/>
+      <c r="N19" s="59"/>
+      <c r="O19" s="117"/>
+      <c r="P19" s="61"/>
+      <c r="Q19" s="59"/>
       <c r="R19" s="31"/>
       <c r="S19" s="31"/>
       <c r="T19" s="32"/>
@@ -9615,23 +9615,23 @@
       <c r="Z19" s="33"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="114"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="115"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="115"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="120"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="120"/>
-      <c r="K20" s="45"/>
-      <c r="L20" s="118"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="45"/>
-      <c r="O20" s="118"/>
-      <c r="P20" s="44"/>
-      <c r="Q20" s="45"/>
+      <c r="A20" s="120"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="121"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="121"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="115"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="59"/>
+      <c r="J20" s="115"/>
+      <c r="K20" s="59"/>
+      <c r="L20" s="117"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="59"/>
+      <c r="O20" s="117"/>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="59"/>
       <c r="R20" s="31"/>
       <c r="S20" s="31"/>
       <c r="T20" s="32"/>
@@ -9643,23 +9643,23 @@
       <c r="Z20" s="33"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="114"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="115"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="115"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="120"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="120"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="118"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="45"/>
-      <c r="O21" s="118"/>
-      <c r="P21" s="44"/>
-      <c r="Q21" s="45"/>
+      <c r="A21" s="120"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="121"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="121"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="115"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="59"/>
+      <c r="J21" s="115"/>
+      <c r="K21" s="59"/>
+      <c r="L21" s="117"/>
+      <c r="M21" s="61"/>
+      <c r="N21" s="59"/>
+      <c r="O21" s="117"/>
+      <c r="P21" s="61"/>
+      <c r="Q21" s="59"/>
       <c r="R21" s="31"/>
       <c r="S21" s="31"/>
       <c r="T21" s="32"/>
@@ -9671,23 +9671,23 @@
       <c r="Z21" s="33"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="114"/>
-      <c r="B22" s="45"/>
-      <c r="C22" s="115"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="115"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="120"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="120"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="118"/>
-      <c r="M22" s="44"/>
-      <c r="N22" s="45"/>
-      <c r="O22" s="118"/>
-      <c r="P22" s="44"/>
-      <c r="Q22" s="45"/>
+      <c r="A22" s="120"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="121"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="121"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="115"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="115"/>
+      <c r="K22" s="59"/>
+      <c r="L22" s="117"/>
+      <c r="M22" s="61"/>
+      <c r="N22" s="59"/>
+      <c r="O22" s="117"/>
+      <c r="P22" s="61"/>
+      <c r="Q22" s="59"/>
       <c r="R22" s="31"/>
       <c r="S22" s="31"/>
       <c r="T22" s="32"/>
@@ -9699,23 +9699,23 @@
       <c r="Z22" s="33"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="114"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="115"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="115"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="120"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="120"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="118"/>
-      <c r="M23" s="44"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="118"/>
-      <c r="P23" s="44"/>
-      <c r="Q23" s="45"/>
+      <c r="A23" s="120"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="121"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="121"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="115"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="115"/>
+      <c r="K23" s="59"/>
+      <c r="L23" s="117"/>
+      <c r="M23" s="61"/>
+      <c r="N23" s="59"/>
+      <c r="O23" s="117"/>
+      <c r="P23" s="61"/>
+      <c r="Q23" s="59"/>
       <c r="R23" s="31"/>
       <c r="S23" s="31"/>
       <c r="T23" s="32"/>
@@ -9727,23 +9727,23 @@
       <c r="Z23" s="33"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="114"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="115"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="115"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="120"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="120"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="118"/>
-      <c r="M24" s="44"/>
-      <c r="N24" s="45"/>
-      <c r="O24" s="118"/>
-      <c r="P24" s="44"/>
-      <c r="Q24" s="45"/>
+      <c r="A24" s="120"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="121"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="121"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="115"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="115"/>
+      <c r="K24" s="59"/>
+      <c r="L24" s="117"/>
+      <c r="M24" s="61"/>
+      <c r="N24" s="59"/>
+      <c r="O24" s="117"/>
+      <c r="P24" s="61"/>
+      <c r="Q24" s="59"/>
       <c r="R24" s="31"/>
       <c r="S24" s="31"/>
       <c r="T24" s="32"/>
@@ -9755,23 +9755,23 @@
       <c r="Z24" s="33"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="114"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="115"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="115"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="120"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="120"/>
-      <c r="K25" s="45"/>
-      <c r="L25" s="118"/>
-      <c r="M25" s="44"/>
-      <c r="N25" s="45"/>
-      <c r="O25" s="118"/>
-      <c r="P25" s="44"/>
-      <c r="Q25" s="45"/>
+      <c r="A25" s="120"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="121"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="115"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="115"/>
+      <c r="K25" s="59"/>
+      <c r="L25" s="117"/>
+      <c r="M25" s="61"/>
+      <c r="N25" s="59"/>
+      <c r="O25" s="117"/>
+      <c r="P25" s="61"/>
+      <c r="Q25" s="59"/>
       <c r="R25" s="31"/>
       <c r="S25" s="31"/>
       <c r="T25" s="32"/>
@@ -9783,23 +9783,23 @@
       <c r="Z25" s="33"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="114"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="115"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="115"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="120"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="120"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="118"/>
-      <c r="M26" s="44"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="118"/>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="45"/>
+      <c r="A26" s="120"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="121"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="121"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="115"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="115"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="117"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="59"/>
+      <c r="O26" s="117"/>
+      <c r="P26" s="61"/>
+      <c r="Q26" s="59"/>
       <c r="R26" s="31"/>
       <c r="S26" s="31"/>
       <c r="T26" s="32"/>
@@ -9811,23 +9811,23 @@
       <c r="Z26" s="33"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="114"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="115"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="120"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="120"/>
-      <c r="K27" s="45"/>
-      <c r="L27" s="118"/>
-      <c r="M27" s="44"/>
-      <c r="N27" s="45"/>
-      <c r="O27" s="118"/>
-      <c r="P27" s="44"/>
-      <c r="Q27" s="45"/>
+      <c r="A27" s="120"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="121"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="121"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="115"/>
+      <c r="K27" s="59"/>
+      <c r="L27" s="117"/>
+      <c r="M27" s="61"/>
+      <c r="N27" s="59"/>
+      <c r="O27" s="117"/>
+      <c r="P27" s="61"/>
+      <c r="Q27" s="59"/>
       <c r="R27" s="31"/>
       <c r="S27" s="31"/>
       <c r="T27" s="32"/>
@@ -9839,23 +9839,23 @@
       <c r="Z27" s="33"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="114"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="115"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="115"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="120"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="120"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="118"/>
-      <c r="M28" s="44"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="118"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="45"/>
+      <c r="A28" s="120"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="121"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="121"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="115"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="115"/>
+      <c r="K28" s="59"/>
+      <c r="L28" s="117"/>
+      <c r="M28" s="61"/>
+      <c r="N28" s="59"/>
+      <c r="O28" s="117"/>
+      <c r="P28" s="61"/>
+      <c r="Q28" s="59"/>
       <c r="R28" s="31"/>
       <c r="S28" s="31"/>
       <c r="T28" s="32"/>
@@ -9867,23 +9867,23 @@
       <c r="Z28" s="33"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="114"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="115"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="115"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="120"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="120"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="118"/>
-      <c r="M29" s="44"/>
-      <c r="N29" s="45"/>
-      <c r="O29" s="118"/>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="45"/>
+      <c r="A29" s="120"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="121"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="121"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="115"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="59"/>
+      <c r="J29" s="115"/>
+      <c r="K29" s="59"/>
+      <c r="L29" s="117"/>
+      <c r="M29" s="61"/>
+      <c r="N29" s="59"/>
+      <c r="O29" s="117"/>
+      <c r="P29" s="61"/>
+      <c r="Q29" s="59"/>
       <c r="R29" s="31"/>
       <c r="S29" s="31"/>
       <c r="T29" s="32"/>
@@ -9895,23 +9895,23 @@
       <c r="Z29" s="33"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="114"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="115"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="115"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="120"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="120"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="118"/>
-      <c r="M30" s="44"/>
-      <c r="N30" s="45"/>
-      <c r="O30" s="118"/>
-      <c r="P30" s="44"/>
-      <c r="Q30" s="45"/>
+      <c r="A30" s="120"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="121"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="121"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="115"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="59"/>
+      <c r="J30" s="115"/>
+      <c r="K30" s="59"/>
+      <c r="L30" s="117"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="59"/>
+      <c r="O30" s="117"/>
+      <c r="P30" s="61"/>
+      <c r="Q30" s="59"/>
       <c r="R30" s="31"/>
       <c r="S30" s="31"/>
       <c r="T30" s="32"/>
@@ -9923,23 +9923,23 @@
       <c r="Z30" s="33"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="116"/>
-      <c r="B31" s="99"/>
-      <c r="C31" s="117"/>
-      <c r="D31" s="99"/>
-      <c r="E31" s="117"/>
-      <c r="F31" s="99"/>
-      <c r="G31" s="123"/>
-      <c r="H31" s="94"/>
-      <c r="I31" s="99"/>
-      <c r="J31" s="123"/>
-      <c r="K31" s="99"/>
-      <c r="L31" s="119"/>
-      <c r="M31" s="94"/>
-      <c r="N31" s="99"/>
-      <c r="O31" s="119"/>
-      <c r="P31" s="94"/>
-      <c r="Q31" s="99"/>
+      <c r="A31" s="123"/>
+      <c r="B31" s="66"/>
+      <c r="C31" s="124"/>
+      <c r="D31" s="66"/>
+      <c r="E31" s="124"/>
+      <c r="F31" s="66"/>
+      <c r="G31" s="116"/>
+      <c r="H31" s="65"/>
+      <c r="I31" s="66"/>
+      <c r="J31" s="116"/>
+      <c r="K31" s="66"/>
+      <c r="L31" s="118"/>
+      <c r="M31" s="65"/>
+      <c r="N31" s="66"/>
+      <c r="O31" s="118"/>
+      <c r="P31" s="65"/>
+      <c r="Q31" s="66"/>
       <c r="R31" s="34"/>
       <c r="S31" s="34"/>
       <c r="T31" s="35"/>
@@ -10937,62 +10937,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -11017,62 +11017,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
